--- a/data/Resultados_Simulacro_ICFES.xlsx
+++ b/data/Resultados_Simulacro_ICFES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorios\R_IEOS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2C30E9-51A0-40D4-94B6-81A06D91C982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D99D0E-336C-4E21-B6E2-EC080027D258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7007" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7822" uniqueCount="1458">
   <si>
     <t>Grupo</t>
   </si>
@@ -3472,6 +3472,945 @@
   </si>
   <si>
     <t xml:space="preserve">SERNA CALLE MANOLO </t>
+  </si>
+  <si>
+    <t>1015191331</t>
+  </si>
+  <si>
+    <t>AGUDELO QUICENO EMANUELLE</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>1013463521</t>
+  </si>
+  <si>
+    <t>ALZATE GAVIRIA LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>1138674302</t>
+  </si>
+  <si>
+    <t>BARRAZA MARRUGO ALISON</t>
+  </si>
+  <si>
+    <t>1192463676</t>
+  </si>
+  <si>
+    <t>BEDOYA CARTAGENA MARIANA</t>
+  </si>
+  <si>
+    <t>1023640760</t>
+  </si>
+  <si>
+    <t>BEDOYA TORRES JUAN ESTEBAN</t>
+  </si>
+  <si>
+    <t>1020308860</t>
+  </si>
+  <si>
+    <t>BUSTAMANTE ECHAVARRIA SAMUEL</t>
+  </si>
+  <si>
+    <t>1192465922</t>
+  </si>
+  <si>
+    <t>CANO MATURANA SAMUEL ANDRES</t>
+  </si>
+  <si>
+    <t>1069487080</t>
+  </si>
+  <si>
+    <t>CASTRO OTERO LUISA FERNANDA</t>
+  </si>
+  <si>
+    <t>1150690182</t>
+  </si>
+  <si>
+    <t>CIRO ATEHORTUA MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>1026063129</t>
+  </si>
+  <si>
+    <t>CORREA TABORDA JULIANA</t>
+  </si>
+  <si>
+    <t>1011403301</t>
+  </si>
+  <si>
+    <t>ESCUDERO USUGA GERARD SMITH</t>
+  </si>
+  <si>
+    <t>1032020096</t>
+  </si>
+  <si>
+    <t>ESQUIVEL CAMPO MARIANA SOFIA</t>
+  </si>
+  <si>
+    <t>1025767841</t>
+  </si>
+  <si>
+    <t>GONZALEZ OLIVEROS MARIA ANGEL</t>
+  </si>
+  <si>
+    <t>1017209000</t>
+  </si>
+  <si>
+    <t>GUERRA VANEGAS MARIA PAULINA</t>
+  </si>
+  <si>
+    <t>7922302</t>
+  </si>
+  <si>
+    <t>GUILLEN HERNANDEZ YIRETH VALENTINA</t>
+  </si>
+  <si>
+    <t>1020444376</t>
+  </si>
+  <si>
+    <t>GUTIERREZ AGUDELO MELANY</t>
+  </si>
+  <si>
+    <t>1192465049</t>
+  </si>
+  <si>
+    <t>HIDALGO PATIÑO DARWIN ORBEY</t>
+  </si>
+  <si>
+    <t>1035978615</t>
+  </si>
+  <si>
+    <t>JEREZ RAMIREZ SOFIA</t>
+  </si>
+  <si>
+    <t>1038871578</t>
+  </si>
+  <si>
+    <t>LOPEZ BERMUDEZ SAMANTHA</t>
+  </si>
+  <si>
+    <t>1148954153</t>
+  </si>
+  <si>
+    <t>MENDOZA HERNANDEZ JULIANA RAFAELLY</t>
+  </si>
+  <si>
+    <t>5935715</t>
+  </si>
+  <si>
+    <t>MERCADO OCANTO FREDDY ALEXANDER</t>
+  </si>
+  <si>
+    <t>1013463700</t>
+  </si>
+  <si>
+    <t>MORALES MEZA MICHEL</t>
+  </si>
+  <si>
+    <t>1025767676</t>
+  </si>
+  <si>
+    <t>MORA MORA SIMON</t>
+  </si>
+  <si>
+    <t>1034921832</t>
+  </si>
+  <si>
+    <t>PULIDO ZAPATA LUCIANA</t>
+  </si>
+  <si>
+    <t>7996559</t>
+  </si>
+  <si>
+    <t>RAMIREZ MEDINA GENESIS YERIMAR</t>
+  </si>
+  <si>
+    <t>1094923237</t>
+  </si>
+  <si>
+    <t>REYES RIVERA ADRIANA LUCIA</t>
+  </si>
+  <si>
+    <t>1015192023</t>
+  </si>
+  <si>
+    <t>RIOS TABORDA MARIANGEL</t>
+  </si>
+  <si>
+    <t>1028947791</t>
+  </si>
+  <si>
+    <t>ROMERO SUAREZ SHAROL ISABEL</t>
+  </si>
+  <si>
+    <t>1081282334</t>
+  </si>
+  <si>
+    <t>RONDON ERAZO PAULA ANDREA</t>
+  </si>
+  <si>
+    <t>1045141998</t>
+  </si>
+  <si>
+    <t>RUIZ GIRALDO MARIA JOSE</t>
+  </si>
+  <si>
+    <t>1013463686</t>
+  </si>
+  <si>
+    <t>TABARES MONTOYA SUSANA</t>
+  </si>
+  <si>
+    <t>1192464737</t>
+  </si>
+  <si>
+    <t>TABORDA CIRO MATIAS</t>
+  </si>
+  <si>
+    <t>1013463773</t>
+  </si>
+  <si>
+    <t>TAMAYO SEPULVEDA SAMUEL</t>
+  </si>
+  <si>
+    <t>7550955</t>
+  </si>
+  <si>
+    <t>VALLENILLA ORTIZ DAVID JESUS</t>
+  </si>
+  <si>
+    <t>1015191937</t>
+  </si>
+  <si>
+    <t>VARGAS ARENAS DULCE MARIA</t>
+  </si>
+  <si>
+    <t>1027808001</t>
+  </si>
+  <si>
+    <t>VELEZ SANCHEZ MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>1038871616</t>
+  </si>
+  <si>
+    <t>ARENAS ORTIZ VALENTINA</t>
+  </si>
+  <si>
+    <t>1091983000</t>
+  </si>
+  <si>
+    <t>ARRIETA RONDON ASHLEY NATHALIA</t>
+  </si>
+  <si>
+    <t>1192465062</t>
+  </si>
+  <si>
+    <t>ATEHORTUA TABORDA ALEJANDRO</t>
+  </si>
+  <si>
+    <t>5034830</t>
+  </si>
+  <si>
+    <t>BLANCO BLANCO ASHLY SADAY</t>
+  </si>
+  <si>
+    <t>1038870530</t>
+  </si>
+  <si>
+    <t>BRICEÑO MORALES EMMANUEL</t>
+  </si>
+  <si>
+    <t>1038264600</t>
+  </si>
+  <si>
+    <t>CANO SALDARRIAGA NICOLL</t>
+  </si>
+  <si>
+    <t>1013463786</t>
+  </si>
+  <si>
+    <t>DUQUE ZAPATA MARIA JOSE</t>
+  </si>
+  <si>
+    <t>1020305214</t>
+  </si>
+  <si>
+    <t>ECHEVERRI CARO MARIA CLARA</t>
+  </si>
+  <si>
+    <t>1026143305</t>
+  </si>
+  <si>
+    <t>GARCIA VASQUEZ SARAY</t>
+  </si>
+  <si>
+    <t>1025660665</t>
+  </si>
+  <si>
+    <t>GOEZ ALVAREZ LUCIANA</t>
+  </si>
+  <si>
+    <t>1020307532</t>
+  </si>
+  <si>
+    <t>GOMEZ TAMAYO LUCIANA</t>
+  </si>
+  <si>
+    <t>1038264810</t>
+  </si>
+  <si>
+    <t>GONZALEZ CARMONA MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>1040574518</t>
+  </si>
+  <si>
+    <t>GUTIERREZ AGUDELO MARIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>1033190096</t>
+  </si>
+  <si>
+    <t>LOTERO SANTA JUAN ESTEBAN</t>
+  </si>
+  <si>
+    <t>1039198455</t>
+  </si>
+  <si>
+    <t>MARIN RAMIREZ ALEJANDRO</t>
+  </si>
+  <si>
+    <t>1032019742</t>
+  </si>
+  <si>
+    <t>MESA GIL MARIA JOSE</t>
+  </si>
+  <si>
+    <t>1038264653</t>
+  </si>
+  <si>
+    <t>MIRA ROJAS JUAN FELIPE</t>
+  </si>
+  <si>
+    <t>1032019829</t>
+  </si>
+  <si>
+    <t>MUÑOZ ARBOLEDA SOFIA</t>
+  </si>
+  <si>
+    <t>1145124343</t>
+  </si>
+  <si>
+    <t>MUÑOZ TOBON SOFIA</t>
+  </si>
+  <si>
+    <t>1040574300</t>
+  </si>
+  <si>
+    <t>OROZCO ESTRADA NICOLLE ANDREA</t>
+  </si>
+  <si>
+    <t>1195213605</t>
+  </si>
+  <si>
+    <t>OSPINA CANO MARIANA</t>
+  </si>
+  <si>
+    <t>1040742807</t>
+  </si>
+  <si>
+    <t>PAMPLONA AGUDELO VALERY</t>
+  </si>
+  <si>
+    <t>1025663287</t>
+  </si>
+  <si>
+    <t>POSADA MEJIA SUSANA</t>
+  </si>
+  <si>
+    <t>1038871277</t>
+  </si>
+  <si>
+    <t>QUIROS HERNANDEZ ISABELLA</t>
+  </si>
+  <si>
+    <t>1048074630</t>
+  </si>
+  <si>
+    <t>REBOLLO CASTAÑO DANIEL</t>
+  </si>
+  <si>
+    <t>1033652995</t>
+  </si>
+  <si>
+    <t>RESTREPO MORALES SARA VANESA</t>
+  </si>
+  <si>
+    <t>5896133</t>
+  </si>
+  <si>
+    <t>RINCON MORALES ISABELLA VALENTINA</t>
+  </si>
+  <si>
+    <t>1020306679</t>
+  </si>
+  <si>
+    <t>ROJAS VARGAS MATIAS</t>
+  </si>
+  <si>
+    <t>1021926821</t>
+  </si>
+  <si>
+    <t>SANCHEZ SANCHEZ MARIA JOSE</t>
+  </si>
+  <si>
+    <t>1017201908</t>
+  </si>
+  <si>
+    <t>SUAREZ VELEZ LUCIANA</t>
+  </si>
+  <si>
+    <t>1044151346</t>
+  </si>
+  <si>
+    <t>SUCERQUIA ZAPATA PAULA ANDREA</t>
+  </si>
+  <si>
+    <t>1040574668</t>
+  </si>
+  <si>
+    <t>TABORDA RESTREPO LUCIANA</t>
+  </si>
+  <si>
+    <t>1019077720</t>
+  </si>
+  <si>
+    <t>TAMAYO VARGAS VALERY</t>
+  </si>
+  <si>
+    <t>1033189310</t>
+  </si>
+  <si>
+    <t>TORO RIVERA MARIA PAULA</t>
+  </si>
+  <si>
+    <t>1013347010</t>
+  </si>
+  <si>
+    <t>URIBE GAVIRIA PAULINA</t>
+  </si>
+  <si>
+    <t>1013463101</t>
+  </si>
+  <si>
+    <t>VARGAS RODRIGUEZ MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>1018251807</t>
+  </si>
+  <si>
+    <t>VASQUEZ LOAIZA ANA SOFIA</t>
+  </si>
+  <si>
+    <t>1013348300</t>
+  </si>
+  <si>
+    <t>VELASQUEZ QUIROZ SANTIAGO</t>
+  </si>
+  <si>
+    <t>1027806435</t>
+  </si>
+  <si>
+    <t>YEPES CIRO SARA SOFIA</t>
+  </si>
+  <si>
+    <t>1054558892</t>
+  </si>
+  <si>
+    <t>ZAPATA CORTES SOFIA</t>
+  </si>
+  <si>
+    <t>1035978948</t>
+  </si>
+  <si>
+    <t>AGUDELO ORDOÑEZ SUSANA</t>
+  </si>
+  <si>
+    <t>1039198493</t>
+  </si>
+  <si>
+    <t>ALVAREZ SANCHEZ MAXIMILIANO</t>
+  </si>
+  <si>
+    <t>1045110434</t>
+  </si>
+  <si>
+    <t>ARANGO PINILLA SAMUEL</t>
+  </si>
+  <si>
+    <t>1025767045</t>
+  </si>
+  <si>
+    <t>ARBOLEDA NARANJO SARAY CRISTINA</t>
+  </si>
+  <si>
+    <t>1192465037</t>
+  </si>
+  <si>
+    <t>ARDILA AREIZA JUAN ANDRES</t>
+  </si>
+  <si>
+    <t>5243832</t>
+  </si>
+  <si>
+    <t>ARDILA MORA FABIAN ANDRES</t>
+  </si>
+  <si>
+    <t>1025894542</t>
+  </si>
+  <si>
+    <t>BECERRA BUSTAMANTE SAMUEL DAVID</t>
+  </si>
+  <si>
+    <t>1040574953</t>
+  </si>
+  <si>
+    <t>BEDOYA PANIAGUA SALOME</t>
+  </si>
+  <si>
+    <t>1023530227</t>
+  </si>
+  <si>
+    <t>CARDONA CARDONA JUAN ESTEBAN</t>
+  </si>
+  <si>
+    <t>1020310078</t>
+  </si>
+  <si>
+    <t>CARDONA MELO STEVEN MATIAS</t>
+  </si>
+  <si>
+    <t>1036452896</t>
+  </si>
+  <si>
+    <t>CASTAÑO TORRES KAREN</t>
+  </si>
+  <si>
+    <t>1025660966</t>
+  </si>
+  <si>
+    <t>CUERVO MUÑOZ JERONIMO</t>
+  </si>
+  <si>
+    <t>1026145987</t>
+  </si>
+  <si>
+    <t>CUERVO ZAPATA SOFIA</t>
+  </si>
+  <si>
+    <t>1128225798</t>
+  </si>
+  <si>
+    <t>DIAZ ZULETA SANTIAGO ALEXANDER</t>
+  </si>
+  <si>
+    <t>1038264695</t>
+  </si>
+  <si>
+    <t>FLOREZ SALDARRIAGA MARIA ANGEL</t>
+  </si>
+  <si>
+    <t>1125680850</t>
+  </si>
+  <si>
+    <t>GUTIERREZ RESTREPO NATALY</t>
+  </si>
+  <si>
+    <t>1025662472</t>
+  </si>
+  <si>
+    <t>MARIN ARBOLEDA JULIAN</t>
+  </si>
+  <si>
+    <t>1035979312</t>
+  </si>
+  <si>
+    <t>MONCADA VERA EMMANUEL</t>
+  </si>
+  <si>
+    <t>1035978318</t>
+  </si>
+  <si>
+    <t>MUÑOZ PULGARIN MELANY</t>
+  </si>
+  <si>
+    <t>1035978659</t>
+  </si>
+  <si>
+    <t>MUÑOZ RODRIGUEZ YARELIS DEL SOL</t>
+  </si>
+  <si>
+    <t>6214990</t>
+  </si>
+  <si>
+    <t>NUÑEZ CORRALES ISABELLA VALENTINA</t>
+  </si>
+  <si>
+    <t>1035430111</t>
+  </si>
+  <si>
+    <t>OCAMPO ACEVEDO SOFIA</t>
+  </si>
+  <si>
+    <t>1033261911</t>
+  </si>
+  <si>
+    <t>PABON RESTREPO SALOME</t>
+  </si>
+  <si>
+    <t>1235252908</t>
+  </si>
+  <si>
+    <t>PADRON SAYAGO ANA PAULA</t>
+  </si>
+  <si>
+    <t>1036454343</t>
+  </si>
+  <si>
+    <t>PEREZ LOPEZ MARIA CAMILA</t>
+  </si>
+  <si>
+    <t>4585965</t>
+  </si>
+  <si>
+    <t>PLANCHEZ URDANETA GABRIEL DAVID DE JESUS</t>
+  </si>
+  <si>
+    <t>1034921688</t>
+  </si>
+  <si>
+    <t>QUICENO GOMEZ JULIANA</t>
+  </si>
+  <si>
+    <t>1034306520</t>
+  </si>
+  <si>
+    <t>RAMIREZ AGUIRRE JERONIMO</t>
+  </si>
+  <si>
+    <t>1018247212</t>
+  </si>
+  <si>
+    <t>RAMIREZ MONTOYA ALYNA</t>
+  </si>
+  <si>
+    <t>1015191283</t>
+  </si>
+  <si>
+    <t>RAMIREZ SANCHEZ MARIA PAZ</t>
+  </si>
+  <si>
+    <t>1036647726</t>
+  </si>
+  <si>
+    <t>RIVERA GRISALES MARIA ANGEL</t>
+  </si>
+  <si>
+    <t>1033492877</t>
+  </si>
+  <si>
+    <t>RIVERA RIVERA MATIAS</t>
+  </si>
+  <si>
+    <t>1025662687</t>
+  </si>
+  <si>
+    <t>ROBLES HERNANDEZ MARIA CAMILA</t>
+  </si>
+  <si>
+    <t>1126910095</t>
+  </si>
+  <si>
+    <t>ROJAS MESA KAMILA ALEXANDRA</t>
+  </si>
+  <si>
+    <t>1032021195</t>
+  </si>
+  <si>
+    <t>ROJAS TORRES LADY MARIANA</t>
+  </si>
+  <si>
+    <t>1033188758</t>
+  </si>
+  <si>
+    <t>SUAREZ CARDONA MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>1013463657</t>
+  </si>
+  <si>
+    <t>VASCO PALACIO MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>1092948075</t>
+  </si>
+  <si>
+    <t>ZAPATA QUINTERO SHUESMY NICOLE</t>
+  </si>
+  <si>
+    <t>1025895223</t>
+  </si>
+  <si>
+    <t>ZAPATA TORRES JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>5174139</t>
+  </si>
+  <si>
+    <t>ALVAREZ CASTRO LUISANA ARIANNY</t>
+  </si>
+  <si>
+    <t>1201963119</t>
+  </si>
+  <si>
+    <t>ALVAREZ SALGADO KENIL ANDRES</t>
+  </si>
+  <si>
+    <t>1037856815</t>
+  </si>
+  <si>
+    <t>ARREDONDO TANGARIFE LUCIANA</t>
+  </si>
+  <si>
+    <t>1035978461</t>
+  </si>
+  <si>
+    <t>AVILEZ VILLADA SAMANTA</t>
+  </si>
+  <si>
+    <t>1013370921</t>
+  </si>
+  <si>
+    <t>BARRERA PAVAS CRHISTIAN</t>
+  </si>
+  <si>
+    <t>1033261644</t>
+  </si>
+  <si>
+    <t>CARO PELAEZ JUAN FELIPE</t>
+  </si>
+  <si>
+    <t>1032020828</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA CARDONA KATHERIN SAMARA</t>
+  </si>
+  <si>
+    <t>1038121532</t>
+  </si>
+  <si>
+    <t>CHARRY ANGULO THOMAS</t>
+  </si>
+  <si>
+    <t>1186463683</t>
+  </si>
+  <si>
+    <t>CIFUENTES ZAPATA HENRY ALBERTO</t>
+  </si>
+  <si>
+    <t>1033187284</t>
+  </si>
+  <si>
+    <t>CORREA GARCIA SAMUEL</t>
+  </si>
+  <si>
+    <t>1035978713</t>
+  </si>
+  <si>
+    <t>DAVID VALLEJO DANIEL ANDRES</t>
+  </si>
+  <si>
+    <t>1035977232</t>
+  </si>
+  <si>
+    <t>DAZA BRAVO KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>1038264926</t>
+  </si>
+  <si>
+    <t>ECHEVERRI PICO SANTIAGO</t>
+  </si>
+  <si>
+    <t>1011401508</t>
+  </si>
+  <si>
+    <t>ESTRADA JIMENEZ JUAN JOSE</t>
+  </si>
+  <si>
+    <t>5816845</t>
+  </si>
+  <si>
+    <t>GARCIA GARNICA JOINNELL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>1038264292</t>
+  </si>
+  <si>
+    <t>GARCIA YEPES SAMUEL</t>
+  </si>
+  <si>
+    <t>1127597908</t>
+  </si>
+  <si>
+    <t>GIRALDO CABRERA ANDY GABRIEL</t>
+  </si>
+  <si>
+    <t>1015192060</t>
+  </si>
+  <si>
+    <t>GIRALDO SALAZAR MARIA CAMILA</t>
+  </si>
+  <si>
+    <t>1063364149</t>
+  </si>
+  <si>
+    <t>GOMEZ MENDOZA YOSMAR</t>
+  </si>
+  <si>
+    <t>1013358014</t>
+  </si>
+  <si>
+    <t>GONZALEZ MARIN BECKHAM MOISES</t>
+  </si>
+  <si>
+    <t>1036693846</t>
+  </si>
+  <si>
+    <t>GONZALEZ MERCHAN JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>1040879602</t>
+  </si>
+  <si>
+    <t>GRISALES GARCIA MATHIAS</t>
+  </si>
+  <si>
+    <t>1095311497</t>
+  </si>
+  <si>
+    <t>JIMENEZ ESTRADA JUAN DAVID</t>
+  </si>
+  <si>
+    <t>1036644598</t>
+  </si>
+  <si>
+    <t>JIMENEZ JARAMILLO ISABELA</t>
+  </si>
+  <si>
+    <t>1033428171</t>
+  </si>
+  <si>
+    <t>LORA DURANGO JUAN DAVID</t>
+  </si>
+  <si>
+    <t>1138674510</t>
+  </si>
+  <si>
+    <t>LUNA CABARCAS LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>1038871941</t>
+  </si>
+  <si>
+    <t>MANRIQUE RODRIGUEZ THALIANA</t>
+  </si>
+  <si>
+    <t>1033189918</t>
+  </si>
+  <si>
+    <t>MARULANDA SALDARRIAGA MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>1037675180</t>
+  </si>
+  <si>
+    <t>MEDINA ARAGON SEBASTIAN EMANUEL</t>
+  </si>
+  <si>
+    <t>1034995931</t>
+  </si>
+  <si>
+    <t>MONSALVE JARAMILLO MATIAS</t>
+  </si>
+  <si>
+    <t>1025767652</t>
+  </si>
+  <si>
+    <t>MONTOYA CIFUENTES MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>1013463398</t>
+  </si>
+  <si>
+    <t>ORTEGA SANCHEZ MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>1232590319</t>
+  </si>
+  <si>
+    <t>PIEDRA HINCAPIE JULIO CESAR</t>
+  </si>
+  <si>
+    <t>1013462452</t>
+  </si>
+  <si>
+    <t>PORRAS LOAIZA NICOLAS</t>
+  </si>
+  <si>
+    <t>6236341</t>
+  </si>
+  <si>
+    <t>RAMIREZ ESIS ANDRIW DAVID</t>
+  </si>
+  <si>
+    <t>1027807437</t>
+  </si>
+  <si>
+    <t>SUAREZ MORENO ANA CAMILA</t>
+  </si>
+  <si>
+    <t>1015191322</t>
+  </si>
+  <si>
+    <t>TAMAYO CHICA VALENTINA</t>
+  </si>
+  <si>
+    <t>1036640708</t>
+  </si>
+  <si>
+    <t>TORRES VELASQUEZ SAMUEL</t>
+  </si>
+  <si>
+    <t>N62215523520</t>
+  </si>
+  <si>
+    <t>VALDEZ GUALOTUÑA PAULETTE MICHELLE</t>
+  </si>
+  <si>
+    <t>1038264943</t>
+  </si>
+  <si>
+    <t>VARGAS RESTREPO MARIA PAULINA</t>
+  </si>
+  <si>
+    <t>1030221268</t>
+  </si>
+  <si>
+    <t>WALKER MIELES XANDER FELIPE</t>
   </si>
 </sst>
 </file>
@@ -3840,7 +4779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1923"/>
+  <dimension ref="A1:N2086"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -88461,6 +89400,7178 @@
         <v>4</v>
       </c>
     </row>
+    <row r="1924" spans="1:14" ht="15" customHeight="1">
+      <c r="A1924" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1924" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C1924" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D1924">
+        <v>372</v>
+      </c>
+      <c r="E1924">
+        <v>64</v>
+      </c>
+      <c r="F1924">
+        <v>85.37</v>
+      </c>
+      <c r="G1924">
+        <v>72.41</v>
+      </c>
+      <c r="H1924">
+        <v>70</v>
+      </c>
+      <c r="I1924">
+        <v>90.91</v>
+      </c>
+      <c r="J1924" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1924" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1924">
+        <v>4</v>
+      </c>
+      <c r="M1924">
+        <v>3</v>
+      </c>
+      <c r="N1924">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:14" ht="15" customHeight="1">
+      <c r="A1925" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C1925" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D1925">
+        <v>320</v>
+      </c>
+      <c r="E1925">
+        <v>48</v>
+      </c>
+      <c r="F1925">
+        <v>73.17</v>
+      </c>
+      <c r="G1925">
+        <v>65.52</v>
+      </c>
+      <c r="H1925">
+        <v>60</v>
+      </c>
+      <c r="I1925">
+        <v>90.91</v>
+      </c>
+      <c r="J1925" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1925" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1925">
+        <v>4</v>
+      </c>
+      <c r="M1925">
+        <v>2</v>
+      </c>
+      <c r="N1925">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:14" ht="15" customHeight="1">
+      <c r="A1926" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C1926" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D1926">
+        <v>269</v>
+      </c>
+      <c r="E1926">
+        <v>40</v>
+      </c>
+      <c r="F1926">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G1926">
+        <v>25.86</v>
+      </c>
+      <c r="H1926">
+        <v>80</v>
+      </c>
+      <c r="I1926">
+        <v>61.82</v>
+      </c>
+      <c r="J1926" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1926" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1926">
+        <v>3</v>
+      </c>
+      <c r="M1926">
+        <v>2</v>
+      </c>
+      <c r="N1926">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:14" ht="15" customHeight="1">
+      <c r="A1927" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1927" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C1927" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D1927">
+        <v>105</v>
+      </c>
+      <c r="E1927">
+        <v>30</v>
+      </c>
+      <c r="F1927">
+        <v>17.07</v>
+      </c>
+      <c r="G1927">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="H1927">
+        <v>18</v>
+      </c>
+      <c r="I1927">
+        <v>25.45</v>
+      </c>
+      <c r="J1927" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1927" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1927">
+        <v>1</v>
+      </c>
+      <c r="M1927">
+        <v>1</v>
+      </c>
+      <c r="N1927">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:14" ht="15" customHeight="1">
+      <c r="A1928" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1928" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C1928" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D1928">
+        <v>258</v>
+      </c>
+      <c r="E1928">
+        <v>54</v>
+      </c>
+      <c r="F1928">
+        <v>63.41</v>
+      </c>
+      <c r="G1928">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H1928">
+        <v>58</v>
+      </c>
+      <c r="I1928">
+        <v>40</v>
+      </c>
+      <c r="J1928" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1928" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1928">
+        <v>3</v>
+      </c>
+      <c r="M1928">
+        <v>3</v>
+      </c>
+      <c r="N1928">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:14" ht="15" customHeight="1">
+      <c r="A1929" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1929" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C1929" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D1929">
+        <v>184</v>
+      </c>
+      <c r="E1929">
+        <v>34</v>
+      </c>
+      <c r="F1929">
+        <v>43.9</v>
+      </c>
+      <c r="G1929">
+        <v>32.76</v>
+      </c>
+      <c r="H1929">
+        <v>36</v>
+      </c>
+      <c r="I1929">
+        <v>38.18</v>
+      </c>
+      <c r="J1929" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1929" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1929">
+        <v>2</v>
+      </c>
+      <c r="M1929">
+        <v>1</v>
+      </c>
+      <c r="N1929">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:14" ht="15" customHeight="1">
+      <c r="A1930" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1930" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C1930" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D1930">
+        <v>173</v>
+      </c>
+      <c r="E1930">
+        <v>34</v>
+      </c>
+      <c r="F1930">
+        <v>29.27</v>
+      </c>
+      <c r="G1930">
+        <v>32.76</v>
+      </c>
+      <c r="H1930">
+        <v>38</v>
+      </c>
+      <c r="I1930">
+        <v>45.45</v>
+      </c>
+      <c r="J1930" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1930" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1930">
+        <v>1</v>
+      </c>
+      <c r="M1930">
+        <v>1</v>
+      </c>
+      <c r="N1930">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:14" ht="15" customHeight="1">
+      <c r="A1931" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1931" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C1931" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D1931">
+        <v>182</v>
+      </c>
+      <c r="E1931">
+        <v>40</v>
+      </c>
+      <c r="F1931">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G1931">
+        <v>32.76</v>
+      </c>
+      <c r="H1931">
+        <v>34</v>
+      </c>
+      <c r="I1931">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J1931" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1931" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1931">
+        <v>2</v>
+      </c>
+      <c r="M1931">
+        <v>2</v>
+      </c>
+      <c r="N1931">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:14" ht="15" customHeight="1">
+      <c r="A1932" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1932" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C1932" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D1932">
+        <v>197</v>
+      </c>
+      <c r="E1932">
+        <v>18</v>
+      </c>
+      <c r="F1932">
+        <v>56.1</v>
+      </c>
+      <c r="G1932">
+        <v>32.76</v>
+      </c>
+      <c r="H1932">
+        <v>52</v>
+      </c>
+      <c r="I1932">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J1932" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1932" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1932">
+        <v>3</v>
+      </c>
+      <c r="M1932">
+        <v>1</v>
+      </c>
+      <c r="N1932">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:14" ht="15" customHeight="1">
+      <c r="A1933" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1933" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C1933" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D1933">
+        <v>227</v>
+      </c>
+      <c r="E1933">
+        <v>38</v>
+      </c>
+      <c r="F1933">
+        <v>56.1</v>
+      </c>
+      <c r="G1933">
+        <v>31.03</v>
+      </c>
+      <c r="H1933">
+        <v>60</v>
+      </c>
+      <c r="I1933">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J1933" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1933" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1933">
+        <v>3</v>
+      </c>
+      <c r="M1933">
+        <v>2</v>
+      </c>
+      <c r="N1933">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:14" ht="15" customHeight="1">
+      <c r="A1934" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C1934" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D1934">
+        <v>287</v>
+      </c>
+      <c r="E1934">
+        <v>56</v>
+      </c>
+      <c r="F1934">
+        <v>58.54</v>
+      </c>
+      <c r="G1934">
+        <v>53.45</v>
+      </c>
+      <c r="H1934">
+        <v>70</v>
+      </c>
+      <c r="I1934">
+        <v>30.91</v>
+      </c>
+      <c r="J1934" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1934" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1934">
+        <v>3</v>
+      </c>
+      <c r="M1934">
+        <v>3</v>
+      </c>
+      <c r="N1934">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:14" ht="15" customHeight="1">
+      <c r="A1935" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1935" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C1935" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D1935">
+        <v>354</v>
+      </c>
+      <c r="E1935">
+        <v>50</v>
+      </c>
+      <c r="F1935">
+        <v>75.61</v>
+      </c>
+      <c r="G1935">
+        <v>79.31</v>
+      </c>
+      <c r="H1935">
+        <v>78</v>
+      </c>
+      <c r="I1935">
+        <v>69.09</v>
+      </c>
+      <c r="J1935" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1935" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1935">
+        <v>4</v>
+      </c>
+      <c r="M1935">
+        <v>2</v>
+      </c>
+      <c r="N1935">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:14" ht="15" customHeight="1">
+      <c r="A1936" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1936" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C1936" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D1936">
+        <v>269</v>
+      </c>
+      <c r="E1936">
+        <v>48</v>
+      </c>
+      <c r="F1936">
+        <v>46.34</v>
+      </c>
+      <c r="G1936">
+        <v>68.97</v>
+      </c>
+      <c r="H1936">
+        <v>52</v>
+      </c>
+      <c r="I1936">
+        <v>52.73</v>
+      </c>
+      <c r="J1936" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1936" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1936">
+        <v>2</v>
+      </c>
+      <c r="M1936">
+        <v>2</v>
+      </c>
+      <c r="N1936">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:14" ht="15" customHeight="1">
+      <c r="A1937" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C1937" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D1937">
+        <v>256</v>
+      </c>
+      <c r="E1937">
+        <v>52</v>
+      </c>
+      <c r="F1937">
+        <v>51.22</v>
+      </c>
+      <c r="G1937">
+        <v>43.1</v>
+      </c>
+      <c r="H1937">
+        <v>64</v>
+      </c>
+      <c r="I1937">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J1937" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1937" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1937">
+        <v>3</v>
+      </c>
+      <c r="M1937">
+        <v>3</v>
+      </c>
+      <c r="N1937">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:14" ht="15" customHeight="1">
+      <c r="A1938" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C1938" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D1938">
+        <v>222</v>
+      </c>
+      <c r="E1938">
+        <v>38</v>
+      </c>
+      <c r="F1938">
+        <v>53.66</v>
+      </c>
+      <c r="G1938">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H1938">
+        <v>50</v>
+      </c>
+      <c r="I1938">
+        <v>30.91</v>
+      </c>
+      <c r="J1938" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1938" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1938">
+        <v>3</v>
+      </c>
+      <c r="M1938">
+        <v>2</v>
+      </c>
+      <c r="N1938">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:14" ht="15" customHeight="1">
+      <c r="A1939" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C1939" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D1939">
+        <v>199</v>
+      </c>
+      <c r="E1939">
+        <v>48</v>
+      </c>
+      <c r="F1939">
+        <v>48.78</v>
+      </c>
+      <c r="G1939">
+        <v>29.31</v>
+      </c>
+      <c r="H1939">
+        <v>34</v>
+      </c>
+      <c r="I1939">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J1939" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1939" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1939">
+        <v>2</v>
+      </c>
+      <c r="M1939">
+        <v>2</v>
+      </c>
+      <c r="N1939">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:14" ht="15" customHeight="1">
+      <c r="A1940" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C1940" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D1940">
+        <v>217</v>
+      </c>
+      <c r="E1940">
+        <v>30</v>
+      </c>
+      <c r="F1940">
+        <v>48.78</v>
+      </c>
+      <c r="G1940">
+        <v>36.21</v>
+      </c>
+      <c r="H1940">
+        <v>62</v>
+      </c>
+      <c r="I1940">
+        <v>30.91</v>
+      </c>
+      <c r="J1940" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1940" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1940">
+        <v>2</v>
+      </c>
+      <c r="M1940">
+        <v>1</v>
+      </c>
+      <c r="N1940">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:14" ht="15" customHeight="1">
+      <c r="A1941" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C1941" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D1941">
+        <v>171</v>
+      </c>
+      <c r="E1941">
+        <v>24</v>
+      </c>
+      <c r="F1941">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G1941">
+        <v>32.76</v>
+      </c>
+      <c r="H1941">
+        <v>40</v>
+      </c>
+      <c r="I1941">
+        <v>36.36</v>
+      </c>
+      <c r="J1941" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1941" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1941">
+        <v>2</v>
+      </c>
+      <c r="M1941">
+        <v>1</v>
+      </c>
+      <c r="N1941">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:14" ht="15" customHeight="1">
+      <c r="A1942" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C1942" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D1942">
+        <v>245</v>
+      </c>
+      <c r="E1942">
+        <v>40</v>
+      </c>
+      <c r="F1942">
+        <v>46.34</v>
+      </c>
+      <c r="G1942">
+        <v>44.83</v>
+      </c>
+      <c r="H1942">
+        <v>54</v>
+      </c>
+      <c r="I1942">
+        <v>80</v>
+      </c>
+      <c r="J1942" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1942" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1942">
+        <v>2</v>
+      </c>
+      <c r="M1942">
+        <v>2</v>
+      </c>
+      <c r="N1942">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:14" ht="15" customHeight="1">
+      <c r="A1943" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1943" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C1943" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D1943">
+        <v>198</v>
+      </c>
+      <c r="E1943">
+        <v>28</v>
+      </c>
+      <c r="F1943">
+        <v>48.78</v>
+      </c>
+      <c r="G1943">
+        <v>22.41</v>
+      </c>
+      <c r="H1943">
+        <v>62</v>
+      </c>
+      <c r="I1943">
+        <v>30.91</v>
+      </c>
+      <c r="J1943" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1943" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1943">
+        <v>2</v>
+      </c>
+      <c r="M1943">
+        <v>1</v>
+      </c>
+      <c r="N1943">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:14" ht="15" customHeight="1">
+      <c r="A1944" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1944" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C1944" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D1944">
+        <v>219</v>
+      </c>
+      <c r="E1944">
+        <v>38</v>
+      </c>
+      <c r="F1944">
+        <v>46.34</v>
+      </c>
+      <c r="G1944">
+        <v>32.76</v>
+      </c>
+      <c r="H1944">
+        <v>58</v>
+      </c>
+      <c r="I1944">
+        <v>43.64</v>
+      </c>
+      <c r="J1944" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1944" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1944">
+        <v>2</v>
+      </c>
+      <c r="M1944">
+        <v>2</v>
+      </c>
+      <c r="N1944">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:14" ht="15" customHeight="1">
+      <c r="A1945" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1945" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C1945" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D1945">
+        <v>201</v>
+      </c>
+      <c r="E1945">
+        <v>34</v>
+      </c>
+      <c r="F1945">
+        <v>53.66</v>
+      </c>
+      <c r="G1945">
+        <v>22.41</v>
+      </c>
+      <c r="H1945">
+        <v>48</v>
+      </c>
+      <c r="I1945">
+        <v>47.27</v>
+      </c>
+      <c r="J1945" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1945" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1945">
+        <v>3</v>
+      </c>
+      <c r="M1945">
+        <v>1</v>
+      </c>
+      <c r="N1945">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:14" ht="15" customHeight="1">
+      <c r="A1946" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1946" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C1946" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D1946">
+        <v>343</v>
+      </c>
+      <c r="E1946">
+        <v>62</v>
+      </c>
+      <c r="F1946">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G1946">
+        <v>53.45</v>
+      </c>
+      <c r="H1946">
+        <v>88</v>
+      </c>
+      <c r="I1946">
+        <v>76.36</v>
+      </c>
+      <c r="J1946" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1946" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1946">
+        <v>4</v>
+      </c>
+      <c r="M1946">
+        <v>3</v>
+      </c>
+      <c r="N1946">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:14" ht="15" customHeight="1">
+      <c r="A1947" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1947" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C1947" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D1947">
+        <v>292</v>
+      </c>
+      <c r="E1947">
+        <v>44</v>
+      </c>
+      <c r="F1947">
+        <v>56.1</v>
+      </c>
+      <c r="G1947">
+        <v>74.14</v>
+      </c>
+      <c r="H1947">
+        <v>54</v>
+      </c>
+      <c r="I1947">
+        <v>72.73</v>
+      </c>
+      <c r="J1947" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1947" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1947">
+        <v>3</v>
+      </c>
+      <c r="M1947">
+        <v>2</v>
+      </c>
+      <c r="N1947">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:14" ht="15" customHeight="1">
+      <c r="A1948" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1948" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C1948" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D1948">
+        <v>174</v>
+      </c>
+      <c r="E1948">
+        <v>26</v>
+      </c>
+      <c r="F1948">
+        <v>31.71</v>
+      </c>
+      <c r="G1948">
+        <v>18.97</v>
+      </c>
+      <c r="H1948">
+        <v>60</v>
+      </c>
+      <c r="I1948">
+        <v>40</v>
+      </c>
+      <c r="J1948" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1948" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1948">
+        <v>1</v>
+      </c>
+      <c r="M1948">
+        <v>1</v>
+      </c>
+      <c r="N1948">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:14" ht="15" customHeight="1">
+      <c r="A1949" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C1949" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D1949">
+        <v>289</v>
+      </c>
+      <c r="E1949">
+        <v>62</v>
+      </c>
+      <c r="F1949">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G1949">
+        <v>41.38</v>
+      </c>
+      <c r="H1949">
+        <v>66</v>
+      </c>
+      <c r="I1949">
+        <v>43.64</v>
+      </c>
+      <c r="J1949" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1949" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1949">
+        <v>3</v>
+      </c>
+      <c r="M1949">
+        <v>3</v>
+      </c>
+      <c r="N1949">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:14" ht="15" customHeight="1">
+      <c r="A1950" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1950" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C1950" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D1950">
+        <v>249</v>
+      </c>
+      <c r="E1950">
+        <v>36</v>
+      </c>
+      <c r="F1950">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G1950">
+        <v>43.1</v>
+      </c>
+      <c r="H1950">
+        <v>48</v>
+      </c>
+      <c r="I1950">
+        <v>60</v>
+      </c>
+      <c r="J1950" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1950" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1950">
+        <v>4</v>
+      </c>
+      <c r="M1950">
+        <v>2</v>
+      </c>
+      <c r="N1950">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:14" ht="15" customHeight="1">
+      <c r="A1951" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1951" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C1951" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D1951">
+        <v>251</v>
+      </c>
+      <c r="E1951">
+        <v>36</v>
+      </c>
+      <c r="F1951">
+        <v>63.41</v>
+      </c>
+      <c r="G1951">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H1951">
+        <v>52</v>
+      </c>
+      <c r="I1951">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J1951" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1951" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1951">
+        <v>3</v>
+      </c>
+      <c r="M1951">
+        <v>2</v>
+      </c>
+      <c r="N1951">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:14" ht="15" customHeight="1">
+      <c r="A1952" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1952" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C1952" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D1952">
+        <v>220</v>
+      </c>
+      <c r="E1952">
+        <v>36</v>
+      </c>
+      <c r="F1952">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G1952">
+        <v>29.31</v>
+      </c>
+      <c r="H1952">
+        <v>60</v>
+      </c>
+      <c r="I1952">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J1952" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1952" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1952">
+        <v>2</v>
+      </c>
+      <c r="M1952">
+        <v>2</v>
+      </c>
+      <c r="N1952">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:14" ht="15" customHeight="1">
+      <c r="A1953" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1953" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C1953" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D1953">
+        <v>277</v>
+      </c>
+      <c r="E1953">
+        <v>34</v>
+      </c>
+      <c r="F1953">
+        <v>58.54</v>
+      </c>
+      <c r="G1953">
+        <v>53.45</v>
+      </c>
+      <c r="H1953">
+        <v>66</v>
+      </c>
+      <c r="I1953">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="J1953" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1953" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1953">
+        <v>3</v>
+      </c>
+      <c r="M1953">
+        <v>1</v>
+      </c>
+      <c r="N1953">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:14" ht="15" customHeight="1">
+      <c r="A1954" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1954" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C1954" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D1954">
+        <v>222</v>
+      </c>
+      <c r="E1954">
+        <v>34</v>
+      </c>
+      <c r="F1954">
+        <v>31.71</v>
+      </c>
+      <c r="G1954">
+        <v>50</v>
+      </c>
+      <c r="H1954">
+        <v>56</v>
+      </c>
+      <c r="I1954">
+        <v>60</v>
+      </c>
+      <c r="J1954" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1954" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1954">
+        <v>1</v>
+      </c>
+      <c r="M1954">
+        <v>1</v>
+      </c>
+      <c r="N1954">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:14" ht="15" customHeight="1">
+      <c r="A1955" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1955" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C1955" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D1955">
+        <v>131</v>
+      </c>
+      <c r="E1955">
+        <v>16</v>
+      </c>
+      <c r="F1955">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="G1955">
+        <v>13.79</v>
+      </c>
+      <c r="H1955">
+        <v>38</v>
+      </c>
+      <c r="I1955">
+        <v>27.27</v>
+      </c>
+      <c r="J1955" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1955" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1955">
+        <v>2</v>
+      </c>
+      <c r="M1955">
+        <v>1</v>
+      </c>
+      <c r="N1955">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:14" ht="15" customHeight="1">
+      <c r="A1956" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1956" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C1956" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D1956">
+        <v>253</v>
+      </c>
+      <c r="E1956">
+        <v>38</v>
+      </c>
+      <c r="F1956">
+        <v>56.1</v>
+      </c>
+      <c r="G1956">
+        <v>43.1</v>
+      </c>
+      <c r="H1956">
+        <v>56</v>
+      </c>
+      <c r="I1956">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J1956" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1956" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1956">
+        <v>3</v>
+      </c>
+      <c r="M1956">
+        <v>2</v>
+      </c>
+      <c r="N1956">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:14" ht="15" customHeight="1">
+      <c r="A1957" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1957" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C1957" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D1957">
+        <v>227</v>
+      </c>
+      <c r="E1957">
+        <v>34</v>
+      </c>
+      <c r="F1957">
+        <v>63.41</v>
+      </c>
+      <c r="G1957">
+        <v>25.86</v>
+      </c>
+      <c r="H1957">
+        <v>52</v>
+      </c>
+      <c r="I1957">
+        <v>61.82</v>
+      </c>
+      <c r="J1957" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1957" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1957">
+        <v>3</v>
+      </c>
+      <c r="M1957">
+        <v>1</v>
+      </c>
+      <c r="N1957">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:14" ht="15" customHeight="1">
+      <c r="A1958" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1958" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C1958" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D1958">
+        <v>266</v>
+      </c>
+      <c r="E1958">
+        <v>44</v>
+      </c>
+      <c r="F1958">
+        <v>56.1</v>
+      </c>
+      <c r="G1958">
+        <v>41.38</v>
+      </c>
+      <c r="H1958">
+        <v>68</v>
+      </c>
+      <c r="I1958">
+        <v>61.82</v>
+      </c>
+      <c r="J1958" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1958" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1958">
+        <v>3</v>
+      </c>
+      <c r="M1958">
+        <v>2</v>
+      </c>
+      <c r="N1958">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:14" ht="15" customHeight="1">
+      <c r="A1959" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1959" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C1959" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D1959">
+        <v>284</v>
+      </c>
+      <c r="E1959">
+        <v>48</v>
+      </c>
+      <c r="F1959">
+        <v>70.73</v>
+      </c>
+      <c r="G1959">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H1959">
+        <v>66</v>
+      </c>
+      <c r="I1959">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J1959" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1959" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1959">
+        <v>4</v>
+      </c>
+      <c r="M1959">
+        <v>2</v>
+      </c>
+      <c r="N1959">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:14" ht="15" customHeight="1">
+      <c r="A1960" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1960" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C1960" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D1960">
+        <v>151</v>
+      </c>
+      <c r="E1960">
+        <v>22</v>
+      </c>
+      <c r="F1960">
+        <v>26.83</v>
+      </c>
+      <c r="G1960">
+        <v>29.31</v>
+      </c>
+      <c r="H1960">
+        <v>44</v>
+      </c>
+      <c r="I1960">
+        <v>25.45</v>
+      </c>
+      <c r="J1960" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1960" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1960">
+        <v>1</v>
+      </c>
+      <c r="M1960">
+        <v>1</v>
+      </c>
+      <c r="N1960">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:14" ht="15" customHeight="1">
+      <c r="A1961" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1961" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C1961" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D1961">
+        <v>165</v>
+      </c>
+      <c r="E1961">
+        <v>28</v>
+      </c>
+      <c r="F1961">
+        <v>48.78</v>
+      </c>
+      <c r="G1961">
+        <v>25.86</v>
+      </c>
+      <c r="H1961">
+        <v>28</v>
+      </c>
+      <c r="I1961">
+        <v>36.36</v>
+      </c>
+      <c r="J1961" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1961" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1961">
+        <v>2</v>
+      </c>
+      <c r="M1961">
+        <v>1</v>
+      </c>
+      <c r="N1961">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:14" ht="15" customHeight="1">
+      <c r="A1962" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1962" t="s">
+        <v>825</v>
+      </c>
+      <c r="C1962" t="s">
+        <v>988</v>
+      </c>
+      <c r="D1962">
+        <v>365</v>
+      </c>
+      <c r="E1962">
+        <v>70</v>
+      </c>
+      <c r="F1962">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G1962">
+        <v>94.83</v>
+      </c>
+      <c r="H1962">
+        <v>66</v>
+      </c>
+      <c r="I1962">
+        <v>49.09</v>
+      </c>
+      <c r="J1962" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1962" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1962">
+        <v>4</v>
+      </c>
+      <c r="M1962">
+        <v>3</v>
+      </c>
+      <c r="N1962">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:14" ht="15" customHeight="1">
+      <c r="A1963" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1963" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D1963">
+        <v>192</v>
+      </c>
+      <c r="E1963">
+        <v>34</v>
+      </c>
+      <c r="F1963">
+        <v>51.22</v>
+      </c>
+      <c r="G1963">
+        <v>29.31</v>
+      </c>
+      <c r="H1963">
+        <v>36</v>
+      </c>
+      <c r="I1963">
+        <v>45.45</v>
+      </c>
+      <c r="J1963" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1963" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1963">
+        <v>3</v>
+      </c>
+      <c r="M1963">
+        <v>1</v>
+      </c>
+      <c r="N1963">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:14" ht="15" customHeight="1">
+      <c r="A1964" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1964" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C1964" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D1964">
+        <v>203</v>
+      </c>
+      <c r="E1964">
+        <v>30</v>
+      </c>
+      <c r="F1964">
+        <v>56.1</v>
+      </c>
+      <c r="G1964">
+        <v>24.14</v>
+      </c>
+      <c r="H1964">
+        <v>46</v>
+      </c>
+      <c r="I1964">
+        <v>58.18</v>
+      </c>
+      <c r="J1964" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1964" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1964">
+        <v>3</v>
+      </c>
+      <c r="M1964">
+        <v>1</v>
+      </c>
+      <c r="N1964">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:14" ht="15" customHeight="1">
+      <c r="A1965" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1965" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C1965" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D1965">
+        <v>204</v>
+      </c>
+      <c r="E1965">
+        <v>44</v>
+      </c>
+      <c r="F1965">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="G1965">
+        <v>43.1</v>
+      </c>
+      <c r="H1965">
+        <v>42</v>
+      </c>
+      <c r="I1965">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J1965" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1965" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1965">
+        <v>2</v>
+      </c>
+      <c r="M1965">
+        <v>2</v>
+      </c>
+      <c r="N1965">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:14" ht="15" customHeight="1">
+      <c r="A1966" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1966" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C1966" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D1966">
+        <v>203</v>
+      </c>
+      <c r="E1966">
+        <v>22</v>
+      </c>
+      <c r="F1966">
+        <v>63.41</v>
+      </c>
+      <c r="G1966">
+        <v>29.31</v>
+      </c>
+      <c r="H1966">
+        <v>46</v>
+      </c>
+      <c r="I1966">
+        <v>45.45</v>
+      </c>
+      <c r="J1966" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1966" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1966">
+        <v>3</v>
+      </c>
+      <c r="M1966">
+        <v>1</v>
+      </c>
+      <c r="N1966">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:14" ht="15" customHeight="1">
+      <c r="A1967" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C1967" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D1967">
+        <v>314</v>
+      </c>
+      <c r="E1967">
+        <v>48</v>
+      </c>
+      <c r="F1967">
+        <v>73.17</v>
+      </c>
+      <c r="G1967">
+        <v>48.28</v>
+      </c>
+      <c r="H1967">
+        <v>80</v>
+      </c>
+      <c r="I1967">
+        <v>67.27</v>
+      </c>
+      <c r="J1967" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1967" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1967">
+        <v>4</v>
+      </c>
+      <c r="M1967">
+        <v>2</v>
+      </c>
+      <c r="N1967">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:14" ht="15" customHeight="1">
+      <c r="A1968" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1968" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C1968" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D1968">
+        <v>170</v>
+      </c>
+      <c r="E1968">
+        <v>30</v>
+      </c>
+      <c r="F1968">
+        <v>46.34</v>
+      </c>
+      <c r="G1968">
+        <v>12.07</v>
+      </c>
+      <c r="H1968">
+        <v>46</v>
+      </c>
+      <c r="I1968">
+        <v>38.18</v>
+      </c>
+      <c r="J1968" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1968" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1968">
+        <v>2</v>
+      </c>
+      <c r="M1968">
+        <v>1</v>
+      </c>
+      <c r="N1968">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:14" ht="15" customHeight="1">
+      <c r="A1969" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1969" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C1969" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D1969">
+        <v>170</v>
+      </c>
+      <c r="E1969">
+        <v>38</v>
+      </c>
+      <c r="F1969">
+        <v>34.15</v>
+      </c>
+      <c r="G1969">
+        <v>27.59</v>
+      </c>
+      <c r="H1969">
+        <v>34</v>
+      </c>
+      <c r="I1969">
+        <v>40</v>
+      </c>
+      <c r="J1969" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1969" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1969">
+        <v>1</v>
+      </c>
+      <c r="M1969">
+        <v>2</v>
+      </c>
+      <c r="N1969">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:14" ht="15" customHeight="1">
+      <c r="A1970" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1970" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C1970" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D1970">
+        <v>218</v>
+      </c>
+      <c r="E1970">
+        <v>28</v>
+      </c>
+      <c r="F1970">
+        <v>56.1</v>
+      </c>
+      <c r="G1970">
+        <v>37.93</v>
+      </c>
+      <c r="H1970">
+        <v>56</v>
+      </c>
+      <c r="I1970">
+        <v>30.91</v>
+      </c>
+      <c r="J1970" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1970" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1970">
+        <v>3</v>
+      </c>
+      <c r="M1970">
+        <v>1</v>
+      </c>
+      <c r="N1970">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:14" ht="15" customHeight="1">
+      <c r="A1971" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1971" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C1971" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D1971">
+        <v>216</v>
+      </c>
+      <c r="E1971">
+        <v>38</v>
+      </c>
+      <c r="F1971">
+        <v>43.9</v>
+      </c>
+      <c r="G1971">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H1971">
+        <v>52</v>
+      </c>
+      <c r="I1971">
+        <v>56.36</v>
+      </c>
+      <c r="J1971" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1971" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1971">
+        <v>2</v>
+      </c>
+      <c r="M1971">
+        <v>2</v>
+      </c>
+      <c r="N1971">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:14" ht="15" customHeight="1">
+      <c r="A1972" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1972" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C1972" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D1972">
+        <v>204</v>
+      </c>
+      <c r="E1972">
+        <v>28</v>
+      </c>
+      <c r="F1972">
+        <v>34.15</v>
+      </c>
+      <c r="G1972">
+        <v>36.21</v>
+      </c>
+      <c r="H1972">
+        <v>56</v>
+      </c>
+      <c r="I1972">
+        <v>67.27</v>
+      </c>
+      <c r="J1972" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1972" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1972">
+        <v>1</v>
+      </c>
+      <c r="M1972">
+        <v>1</v>
+      </c>
+      <c r="N1972">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:14" ht="15" customHeight="1">
+      <c r="A1973" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1973" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C1973" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D1973">
+        <v>167</v>
+      </c>
+      <c r="E1973">
+        <v>40</v>
+      </c>
+      <c r="F1973">
+        <v>41.46</v>
+      </c>
+      <c r="G1973">
+        <v>20.69</v>
+      </c>
+      <c r="H1973">
+        <v>28</v>
+      </c>
+      <c r="I1973">
+        <v>41.82</v>
+      </c>
+      <c r="J1973" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1973" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1973">
+        <v>2</v>
+      </c>
+      <c r="M1973">
+        <v>2</v>
+      </c>
+      <c r="N1973">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:14" ht="15" customHeight="1">
+      <c r="A1974" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1974" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C1974" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D1974">
+        <v>242</v>
+      </c>
+      <c r="E1974">
+        <v>34</v>
+      </c>
+      <c r="F1974">
+        <v>58.54</v>
+      </c>
+      <c r="G1974">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H1974">
+        <v>54</v>
+      </c>
+      <c r="I1974">
+        <v>69.09</v>
+      </c>
+      <c r="J1974" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1974" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1974">
+        <v>3</v>
+      </c>
+      <c r="M1974">
+        <v>1</v>
+      </c>
+      <c r="N1974">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:14" ht="15" customHeight="1">
+      <c r="A1975" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1975" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C1975" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D1975">
+        <v>223</v>
+      </c>
+      <c r="E1975">
+        <v>30</v>
+      </c>
+      <c r="F1975">
+        <v>60.98</v>
+      </c>
+      <c r="G1975">
+        <v>43.1</v>
+      </c>
+      <c r="H1975">
+        <v>44</v>
+      </c>
+      <c r="I1975">
+        <v>43.64</v>
+      </c>
+      <c r="J1975" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1975" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1975">
+        <v>3</v>
+      </c>
+      <c r="M1975">
+        <v>1</v>
+      </c>
+      <c r="N1975">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:14" ht="15" customHeight="1">
+      <c r="A1976" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1976" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C1976" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D1976">
+        <v>248</v>
+      </c>
+      <c r="E1976">
+        <v>28</v>
+      </c>
+      <c r="F1976">
+        <v>60.98</v>
+      </c>
+      <c r="G1976">
+        <v>37.93</v>
+      </c>
+      <c r="H1976">
+        <v>74</v>
+      </c>
+      <c r="I1976">
+        <v>40</v>
+      </c>
+      <c r="J1976" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1976" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1976">
+        <v>3</v>
+      </c>
+      <c r="M1976">
+        <v>1</v>
+      </c>
+      <c r="N1976">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:14" ht="15" customHeight="1">
+      <c r="A1977" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1977" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C1977" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D1977">
+        <v>260</v>
+      </c>
+      <c r="E1977">
+        <v>44</v>
+      </c>
+      <c r="F1977">
+        <v>48.78</v>
+      </c>
+      <c r="G1977">
+        <v>70.69</v>
+      </c>
+      <c r="H1977">
+        <v>46</v>
+      </c>
+      <c r="I1977">
+        <v>47.27</v>
+      </c>
+      <c r="J1977" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1977" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1977">
+        <v>2</v>
+      </c>
+      <c r="M1977">
+        <v>2</v>
+      </c>
+      <c r="N1977">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:14" ht="15" customHeight="1">
+      <c r="A1978" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1978" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C1978" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D1978">
+        <v>295</v>
+      </c>
+      <c r="E1978">
+        <v>38</v>
+      </c>
+      <c r="F1978">
+        <v>51.22</v>
+      </c>
+      <c r="G1978">
+        <v>77.59</v>
+      </c>
+      <c r="H1978">
+        <v>70</v>
+      </c>
+      <c r="I1978">
+        <v>56.36</v>
+      </c>
+      <c r="J1978" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1978" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1978">
+        <v>3</v>
+      </c>
+      <c r="M1978">
+        <v>2</v>
+      </c>
+      <c r="N1978">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:14" ht="15" customHeight="1">
+      <c r="A1979" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1979" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C1979" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D1979">
+        <v>259</v>
+      </c>
+      <c r="E1979">
+        <v>42</v>
+      </c>
+      <c r="F1979">
+        <v>48.78</v>
+      </c>
+      <c r="G1979">
+        <v>60.34</v>
+      </c>
+      <c r="H1979">
+        <v>58</v>
+      </c>
+      <c r="I1979">
+        <v>45.45</v>
+      </c>
+      <c r="J1979" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1979" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1979">
+        <v>2</v>
+      </c>
+      <c r="M1979">
+        <v>2</v>
+      </c>
+      <c r="N1979">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:14" ht="15" customHeight="1">
+      <c r="A1980" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1980" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C1980" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D1980">
+        <v>252</v>
+      </c>
+      <c r="E1980">
+        <v>42</v>
+      </c>
+      <c r="F1980">
+        <v>41.46</v>
+      </c>
+      <c r="G1980">
+        <v>63.79</v>
+      </c>
+      <c r="H1980">
+        <v>54</v>
+      </c>
+      <c r="I1980">
+        <v>49.09</v>
+      </c>
+      <c r="J1980" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1980" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1980">
+        <v>2</v>
+      </c>
+      <c r="M1980">
+        <v>2</v>
+      </c>
+      <c r="N1980">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:14" ht="15" customHeight="1">
+      <c r="A1981" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1981" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C1981" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D1981">
+        <v>197</v>
+      </c>
+      <c r="E1981">
+        <v>34</v>
+      </c>
+      <c r="F1981">
+        <v>53.66</v>
+      </c>
+      <c r="G1981">
+        <v>32.76</v>
+      </c>
+      <c r="H1981">
+        <v>44</v>
+      </c>
+      <c r="I1981">
+        <v>18.18</v>
+      </c>
+      <c r="J1981" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1981" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1981">
+        <v>3</v>
+      </c>
+      <c r="M1981">
+        <v>1</v>
+      </c>
+      <c r="N1981">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:14" ht="15" customHeight="1">
+      <c r="A1982" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1982" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C1982" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D1982">
+        <v>225</v>
+      </c>
+      <c r="E1982">
+        <v>34</v>
+      </c>
+      <c r="F1982">
+        <v>53.66</v>
+      </c>
+      <c r="G1982">
+        <v>56.9</v>
+      </c>
+      <c r="H1982">
+        <v>36</v>
+      </c>
+      <c r="I1982">
+        <v>41.82</v>
+      </c>
+      <c r="J1982" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1982" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1982">
+        <v>3</v>
+      </c>
+      <c r="M1982">
+        <v>1</v>
+      </c>
+      <c r="N1982">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:14" ht="15" customHeight="1">
+      <c r="A1983" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1983" t="s">
+        <v>908</v>
+      </c>
+      <c r="C1983" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D1983">
+        <v>361</v>
+      </c>
+      <c r="E1983">
+        <v>72</v>
+      </c>
+      <c r="F1983">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G1983">
+        <v>94.83</v>
+      </c>
+      <c r="H1983">
+        <v>64</v>
+      </c>
+      <c r="I1983">
+        <v>47.27</v>
+      </c>
+      <c r="J1983" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1983" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1983">
+        <v>3</v>
+      </c>
+      <c r="M1983">
+        <v>4</v>
+      </c>
+      <c r="N1983">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:14" ht="15" customHeight="1">
+      <c r="A1984" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1984" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C1984" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D1984">
+        <v>274</v>
+      </c>
+      <c r="E1984">
+        <v>44</v>
+      </c>
+      <c r="F1984">
+        <v>56.1</v>
+      </c>
+      <c r="G1984">
+        <v>60.34</v>
+      </c>
+      <c r="H1984">
+        <v>66</v>
+      </c>
+      <c r="I1984">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J1984" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1984" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1984">
+        <v>3</v>
+      </c>
+      <c r="M1984">
+        <v>2</v>
+      </c>
+      <c r="N1984">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:14" ht="15" customHeight="1">
+      <c r="A1985" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1985" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C1985" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D1985">
+        <v>124</v>
+      </c>
+      <c r="E1985">
+        <v>22</v>
+      </c>
+      <c r="F1985">
+        <v>48.78</v>
+      </c>
+      <c r="G1985">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="H1985">
+        <v>28</v>
+      </c>
+      <c r="I1985">
+        <v>0</v>
+      </c>
+      <c r="J1985" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1985" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1985">
+        <v>2</v>
+      </c>
+      <c r="M1985">
+        <v>1</v>
+      </c>
+      <c r="N1985">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:14" ht="15" customHeight="1">
+      <c r="A1986" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1986" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C1986" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D1986">
+        <v>235</v>
+      </c>
+      <c r="E1986">
+        <v>26</v>
+      </c>
+      <c r="F1986">
+        <v>51.22</v>
+      </c>
+      <c r="G1986">
+        <v>36.21</v>
+      </c>
+      <c r="H1986">
+        <v>58</v>
+      </c>
+      <c r="I1986">
+        <v>94.55</v>
+      </c>
+      <c r="J1986" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1986" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1986">
+        <v>3</v>
+      </c>
+      <c r="M1986">
+        <v>1</v>
+      </c>
+      <c r="N1986">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:14" ht="15" customHeight="1">
+      <c r="A1987" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1987" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1987" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D1987">
+        <v>263</v>
+      </c>
+      <c r="E1987">
+        <v>54</v>
+      </c>
+      <c r="F1987">
+        <v>51.22</v>
+      </c>
+      <c r="G1987">
+        <v>44.83</v>
+      </c>
+      <c r="H1987">
+        <v>66</v>
+      </c>
+      <c r="I1987">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J1987" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1987" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1987">
+        <v>3</v>
+      </c>
+      <c r="M1987">
+        <v>3</v>
+      </c>
+      <c r="N1987">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:14" ht="15" customHeight="1">
+      <c r="A1988" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1988" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C1988" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D1988">
+        <v>252</v>
+      </c>
+      <c r="E1988">
+        <v>34</v>
+      </c>
+      <c r="F1988">
+        <v>60.98</v>
+      </c>
+      <c r="G1988">
+        <v>41.38</v>
+      </c>
+      <c r="H1988">
+        <v>62</v>
+      </c>
+      <c r="I1988">
+        <v>58.18</v>
+      </c>
+      <c r="J1988" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1988" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1988">
+        <v>3</v>
+      </c>
+      <c r="M1988">
+        <v>1</v>
+      </c>
+      <c r="N1988">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:14" ht="15" customHeight="1">
+      <c r="A1989" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1989" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C1989" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D1989">
+        <v>283</v>
+      </c>
+      <c r="E1989">
+        <v>38</v>
+      </c>
+      <c r="F1989">
+        <v>53.66</v>
+      </c>
+      <c r="G1989">
+        <v>48.28</v>
+      </c>
+      <c r="H1989">
+        <v>80</v>
+      </c>
+      <c r="I1989">
+        <v>74.55</v>
+      </c>
+      <c r="J1989" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1989" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1989">
+        <v>3</v>
+      </c>
+      <c r="M1989">
+        <v>2</v>
+      </c>
+      <c r="N1989">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:14" ht="15" customHeight="1">
+      <c r="A1990" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1990" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C1990" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D1990">
+        <v>208</v>
+      </c>
+      <c r="E1990">
+        <v>30</v>
+      </c>
+      <c r="F1990">
+        <v>43.9</v>
+      </c>
+      <c r="G1990">
+        <v>43.1</v>
+      </c>
+      <c r="H1990">
+        <v>48</v>
+      </c>
+      <c r="I1990">
+        <v>43.64</v>
+      </c>
+      <c r="J1990" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1990" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1990">
+        <v>2</v>
+      </c>
+      <c r="M1990">
+        <v>1</v>
+      </c>
+      <c r="N1990">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:14" ht="15" customHeight="1">
+      <c r="A1991" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1991" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C1991" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D1991">
+        <v>166</v>
+      </c>
+      <c r="E1991">
+        <v>32</v>
+      </c>
+      <c r="F1991">
+        <v>46.34</v>
+      </c>
+      <c r="G1991">
+        <v>25.86</v>
+      </c>
+      <c r="H1991">
+        <v>26</v>
+      </c>
+      <c r="I1991">
+        <v>40</v>
+      </c>
+      <c r="J1991" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1991" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1991">
+        <v>2</v>
+      </c>
+      <c r="M1991">
+        <v>1</v>
+      </c>
+      <c r="N1991">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:14" ht="15" customHeight="1">
+      <c r="A1992" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1992" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C1992" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D1992">
+        <v>183</v>
+      </c>
+      <c r="E1992">
+        <v>28</v>
+      </c>
+      <c r="F1992">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="G1992">
+        <v>43.1</v>
+      </c>
+      <c r="H1992">
+        <v>38</v>
+      </c>
+      <c r="I1992">
+        <v>38.18</v>
+      </c>
+      <c r="J1992" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1992" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1992">
+        <v>2</v>
+      </c>
+      <c r="M1992">
+        <v>1</v>
+      </c>
+      <c r="N1992">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:14" ht="15" customHeight="1">
+      <c r="A1993" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1993" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C1993" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D1993">
+        <v>266</v>
+      </c>
+      <c r="E1993">
+        <v>38</v>
+      </c>
+      <c r="F1993">
+        <v>63.41</v>
+      </c>
+      <c r="G1993">
+        <v>63.79</v>
+      </c>
+      <c r="H1993">
+        <v>50</v>
+      </c>
+      <c r="I1993">
+        <v>43.64</v>
+      </c>
+      <c r="J1993" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1993" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1993">
+        <v>3</v>
+      </c>
+      <c r="M1993">
+        <v>2</v>
+      </c>
+      <c r="N1993">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:14" ht="15" customHeight="1">
+      <c r="A1994" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1994" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C1994" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D1994">
+        <v>328</v>
+      </c>
+      <c r="E1994">
+        <v>66</v>
+      </c>
+      <c r="F1994">
+        <v>51.22</v>
+      </c>
+      <c r="G1994">
+        <v>94.83</v>
+      </c>
+      <c r="H1994">
+        <v>56</v>
+      </c>
+      <c r="I1994">
+        <v>47.27</v>
+      </c>
+      <c r="J1994" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1994" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1994">
+        <v>3</v>
+      </c>
+      <c r="M1994">
+        <v>3</v>
+      </c>
+      <c r="N1994">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:14" ht="15" customHeight="1">
+      <c r="A1995" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1995" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C1995" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D1995">
+        <v>250</v>
+      </c>
+      <c r="E1995">
+        <v>40</v>
+      </c>
+      <c r="F1995">
+        <v>51.22</v>
+      </c>
+      <c r="G1995">
+        <v>70.69</v>
+      </c>
+      <c r="H1995">
+        <v>38</v>
+      </c>
+      <c r="I1995">
+        <v>49.09</v>
+      </c>
+      <c r="J1995" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1995" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1995">
+        <v>3</v>
+      </c>
+      <c r="M1995">
+        <v>2</v>
+      </c>
+      <c r="N1995">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:14" ht="15" customHeight="1">
+      <c r="A1996" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1996" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C1996" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D1996">
+        <v>233</v>
+      </c>
+      <c r="E1996">
+        <v>32</v>
+      </c>
+      <c r="F1996">
+        <v>46.34</v>
+      </c>
+      <c r="G1996">
+        <v>63.79</v>
+      </c>
+      <c r="H1996">
+        <v>46</v>
+      </c>
+      <c r="I1996">
+        <v>40</v>
+      </c>
+      <c r="J1996" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1996" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1996">
+        <v>2</v>
+      </c>
+      <c r="M1996">
+        <v>1</v>
+      </c>
+      <c r="N1996">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:14" ht="15" customHeight="1">
+      <c r="A1997" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1997" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C1997" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D1997">
+        <v>228</v>
+      </c>
+      <c r="E1997">
+        <v>38</v>
+      </c>
+      <c r="F1997">
+        <v>48.78</v>
+      </c>
+      <c r="G1997">
+        <v>36.21</v>
+      </c>
+      <c r="H1997">
+        <v>56</v>
+      </c>
+      <c r="I1997">
+        <v>54.55</v>
+      </c>
+      <c r="J1997" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1997" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1997">
+        <v>2</v>
+      </c>
+      <c r="M1997">
+        <v>2</v>
+      </c>
+      <c r="N1997">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:14" ht="15" customHeight="1">
+      <c r="A1998" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1998" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C1998" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D1998">
+        <v>224</v>
+      </c>
+      <c r="E1998">
+        <v>34</v>
+      </c>
+      <c r="F1998">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="G1998">
+        <v>60.34</v>
+      </c>
+      <c r="H1998">
+        <v>46</v>
+      </c>
+      <c r="I1998">
+        <v>50.91</v>
+      </c>
+      <c r="J1998" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1998" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1998">
+        <v>2</v>
+      </c>
+      <c r="M1998">
+        <v>1</v>
+      </c>
+      <c r="N1998">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:14" ht="15" customHeight="1">
+      <c r="A1999" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1999" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1999" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D1999">
+        <v>269</v>
+      </c>
+      <c r="E1999">
+        <v>36</v>
+      </c>
+      <c r="F1999">
+        <v>53.66</v>
+      </c>
+      <c r="G1999">
+        <v>70.69</v>
+      </c>
+      <c r="H1999">
+        <v>58</v>
+      </c>
+      <c r="I1999">
+        <v>41.82</v>
+      </c>
+      <c r="J1999" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K1999" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1999">
+        <v>3</v>
+      </c>
+      <c r="M1999">
+        <v>2</v>
+      </c>
+      <c r="N1999">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:14" ht="15" customHeight="1">
+      <c r="A2000" t="s">
+        <v>477</v>
+      </c>
+      <c r="B2000" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C2000" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D2000">
+        <v>206</v>
+      </c>
+      <c r="E2000">
+        <v>32</v>
+      </c>
+      <c r="F2000">
+        <v>51.22</v>
+      </c>
+      <c r="G2000">
+        <v>25.86</v>
+      </c>
+      <c r="H2000">
+        <v>62</v>
+      </c>
+      <c r="I2000">
+        <v>20</v>
+      </c>
+      <c r="J2000" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2000" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2000">
+        <v>3</v>
+      </c>
+      <c r="M2000">
+        <v>1</v>
+      </c>
+      <c r="N2000">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:14" ht="15" customHeight="1">
+      <c r="A2001" t="s">
+        <v>477</v>
+      </c>
+      <c r="B2001" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C2001" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D2001">
+        <v>277</v>
+      </c>
+      <c r="E2001">
+        <v>32</v>
+      </c>
+      <c r="F2001">
+        <v>58.54</v>
+      </c>
+      <c r="G2001">
+        <v>65.52</v>
+      </c>
+      <c r="H2001">
+        <v>68</v>
+      </c>
+      <c r="I2001">
+        <v>47.27</v>
+      </c>
+      <c r="J2001" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2001" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2001">
+        <v>3</v>
+      </c>
+      <c r="M2001">
+        <v>1</v>
+      </c>
+      <c r="N2001">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:14" ht="15" customHeight="1">
+      <c r="A2002" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2002" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C2002" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D2002">
+        <v>199</v>
+      </c>
+      <c r="E2002">
+        <v>38</v>
+      </c>
+      <c r="F2002">
+        <v>48.78</v>
+      </c>
+      <c r="G2002">
+        <v>25.86</v>
+      </c>
+      <c r="H2002">
+        <v>48</v>
+      </c>
+      <c r="I2002">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2002" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2002" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2002">
+        <v>2</v>
+      </c>
+      <c r="M2002">
+        <v>2</v>
+      </c>
+      <c r="N2002">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:14" ht="15" customHeight="1">
+      <c r="A2003" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2003" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C2003" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D2003">
+        <v>174</v>
+      </c>
+      <c r="E2003">
+        <v>44</v>
+      </c>
+      <c r="F2003">
+        <v>41.46</v>
+      </c>
+      <c r="G2003">
+        <v>22.41</v>
+      </c>
+      <c r="H2003">
+        <v>32</v>
+      </c>
+      <c r="I2003">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2003" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2003" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2003">
+        <v>2</v>
+      </c>
+      <c r="M2003">
+        <v>2</v>
+      </c>
+      <c r="N2003">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:14" ht="15" customHeight="1">
+      <c r="A2004" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2004" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C2004" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D2004">
+        <v>147</v>
+      </c>
+      <c r="E2004">
+        <v>28</v>
+      </c>
+      <c r="F2004">
+        <v>31.71</v>
+      </c>
+      <c r="G2004">
+        <v>24.14</v>
+      </c>
+      <c r="H2004">
+        <v>32</v>
+      </c>
+      <c r="I2004">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2004" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2004" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2004">
+        <v>1</v>
+      </c>
+      <c r="M2004">
+        <v>1</v>
+      </c>
+      <c r="N2004">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:14" ht="15" customHeight="1">
+      <c r="A2005" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2005" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C2005" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D2005">
+        <v>172</v>
+      </c>
+      <c r="E2005">
+        <v>28</v>
+      </c>
+      <c r="F2005">
+        <v>29.27</v>
+      </c>
+      <c r="G2005">
+        <v>36.21</v>
+      </c>
+      <c r="H2005">
+        <v>36</v>
+      </c>
+      <c r="I2005">
+        <v>56.36</v>
+      </c>
+      <c r="J2005" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2005" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2005">
+        <v>1</v>
+      </c>
+      <c r="M2005">
+        <v>1</v>
+      </c>
+      <c r="N2005">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:14" ht="15" customHeight="1">
+      <c r="A2006" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2006" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C2006" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D2006">
+        <v>174</v>
+      </c>
+      <c r="E2006">
+        <v>42</v>
+      </c>
+      <c r="F2006">
+        <v>31.71</v>
+      </c>
+      <c r="G2006">
+        <v>24.14</v>
+      </c>
+      <c r="H2006">
+        <v>42</v>
+      </c>
+      <c r="I2006">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2006" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2006" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2006">
+        <v>1</v>
+      </c>
+      <c r="M2006">
+        <v>2</v>
+      </c>
+      <c r="N2006">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:14" ht="15" customHeight="1">
+      <c r="A2007" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2007" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C2007" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D2007">
+        <v>168</v>
+      </c>
+      <c r="E2007">
+        <v>40</v>
+      </c>
+      <c r="F2007">
+        <v>26.83</v>
+      </c>
+      <c r="G2007">
+        <v>31.03</v>
+      </c>
+      <c r="H2007">
+        <v>38</v>
+      </c>
+      <c r="I2007">
+        <v>27.27</v>
+      </c>
+      <c r="J2007" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2007" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2007">
+        <v>1</v>
+      </c>
+      <c r="M2007">
+        <v>2</v>
+      </c>
+      <c r="N2007">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:14" ht="15" customHeight="1">
+      <c r="A2008" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2008" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C2008" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D2008">
+        <v>128</v>
+      </c>
+      <c r="E2008">
+        <v>34</v>
+      </c>
+      <c r="F2008">
+        <v>24.39</v>
+      </c>
+      <c r="G2008">
+        <v>27.59</v>
+      </c>
+      <c r="H2008">
+        <v>14</v>
+      </c>
+      <c r="I2008">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2008" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2008" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2008">
+        <v>1</v>
+      </c>
+      <c r="M2008">
+        <v>1</v>
+      </c>
+      <c r="N2008">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:14" ht="15" customHeight="1">
+      <c r="A2009" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2009" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C2009" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D2009">
+        <v>265</v>
+      </c>
+      <c r="E2009">
+        <v>26</v>
+      </c>
+      <c r="F2009">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2009">
+        <v>41.38</v>
+      </c>
+      <c r="H2009">
+        <v>70</v>
+      </c>
+      <c r="I2009">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2009" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2009" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2009">
+        <v>3</v>
+      </c>
+      <c r="M2009">
+        <v>1</v>
+      </c>
+      <c r="N2009">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:14" ht="15" customHeight="1">
+      <c r="A2010" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2010" t="s">
+        <v>830</v>
+      </c>
+      <c r="C2010" t="s">
+        <v>831</v>
+      </c>
+      <c r="D2010">
+        <v>172</v>
+      </c>
+      <c r="E2010">
+        <v>40</v>
+      </c>
+      <c r="F2010">
+        <v>41.46</v>
+      </c>
+      <c r="G2010">
+        <v>18.97</v>
+      </c>
+      <c r="H2010">
+        <v>30</v>
+      </c>
+      <c r="I2010">
+        <v>54.55</v>
+      </c>
+      <c r="J2010" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2010" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2010">
+        <v>2</v>
+      </c>
+      <c r="M2010">
+        <v>2</v>
+      </c>
+      <c r="N2010">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:14" ht="15" customHeight="1">
+      <c r="A2011" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2011" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C2011" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D2011">
+        <v>171</v>
+      </c>
+      <c r="E2011">
+        <v>52</v>
+      </c>
+      <c r="F2011">
+        <v>29.27</v>
+      </c>
+      <c r="G2011">
+        <v>20.69</v>
+      </c>
+      <c r="H2011">
+        <v>28</v>
+      </c>
+      <c r="I2011">
+        <v>54.55</v>
+      </c>
+      <c r="J2011" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2011" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2011">
+        <v>1</v>
+      </c>
+      <c r="M2011">
+        <v>3</v>
+      </c>
+      <c r="N2011">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:14" ht="15" customHeight="1">
+      <c r="A2012" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2012" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C2012" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D2012">
+        <v>286</v>
+      </c>
+      <c r="E2012">
+        <v>54</v>
+      </c>
+      <c r="F2012">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2012">
+        <v>37.93</v>
+      </c>
+      <c r="H2012">
+        <v>68</v>
+      </c>
+      <c r="I2012">
+        <v>56.36</v>
+      </c>
+      <c r="J2012" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2012" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2012">
+        <v>4</v>
+      </c>
+      <c r="M2012">
+        <v>3</v>
+      </c>
+      <c r="N2012">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:14" ht="15" customHeight="1">
+      <c r="A2013" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2013" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C2013" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D2013">
+        <v>267</v>
+      </c>
+      <c r="E2013">
+        <v>36</v>
+      </c>
+      <c r="F2013">
+        <v>60.98</v>
+      </c>
+      <c r="G2013">
+        <v>46.55</v>
+      </c>
+      <c r="H2013">
+        <v>64</v>
+      </c>
+      <c r="I2013">
+        <v>70.91</v>
+      </c>
+      <c r="J2013" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2013" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2013">
+        <v>3</v>
+      </c>
+      <c r="M2013">
+        <v>2</v>
+      </c>
+      <c r="N2013">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:14" ht="15" customHeight="1">
+      <c r="A2014" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2014" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C2014" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D2014">
+        <v>206</v>
+      </c>
+      <c r="E2014">
+        <v>48</v>
+      </c>
+      <c r="F2014">
+        <v>43.9</v>
+      </c>
+      <c r="G2014">
+        <v>29.31</v>
+      </c>
+      <c r="H2014">
+        <v>40</v>
+      </c>
+      <c r="I2014">
+        <v>50.91</v>
+      </c>
+      <c r="J2014" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2014" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2014">
+        <v>2</v>
+      </c>
+      <c r="M2014">
+        <v>2</v>
+      </c>
+      <c r="N2014">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:14" ht="15" customHeight="1">
+      <c r="A2015" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2015" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C2015" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D2015">
+        <v>268</v>
+      </c>
+      <c r="E2015">
+        <v>26</v>
+      </c>
+      <c r="F2015">
+        <v>78.05</v>
+      </c>
+      <c r="G2015">
+        <v>43.1</v>
+      </c>
+      <c r="H2015">
+        <v>70</v>
+      </c>
+      <c r="I2015">
+        <v>43.64</v>
+      </c>
+      <c r="J2015" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2015" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2015">
+        <v>4</v>
+      </c>
+      <c r="M2015">
+        <v>1</v>
+      </c>
+      <c r="N2015">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:14" ht="15" customHeight="1">
+      <c r="A2016" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2016" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C2016" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D2016">
+        <v>244</v>
+      </c>
+      <c r="E2016">
+        <v>34</v>
+      </c>
+      <c r="F2016">
+        <v>46.34</v>
+      </c>
+      <c r="G2016">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H2016">
+        <v>74</v>
+      </c>
+      <c r="I2016">
+        <v>50.91</v>
+      </c>
+      <c r="J2016" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2016" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2016">
+        <v>2</v>
+      </c>
+      <c r="M2016">
+        <v>1</v>
+      </c>
+      <c r="N2016">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:14" ht="15" customHeight="1">
+      <c r="A2017" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2017" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C2017" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D2017">
+        <v>149</v>
+      </c>
+      <c r="E2017">
+        <v>34</v>
+      </c>
+      <c r="F2017">
+        <v>46.34</v>
+      </c>
+      <c r="G2017">
+        <v>12.07</v>
+      </c>
+      <c r="H2017">
+        <v>28</v>
+      </c>
+      <c r="I2017">
+        <v>23.64</v>
+      </c>
+      <c r="J2017" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2017" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2017">
+        <v>2</v>
+      </c>
+      <c r="M2017">
+        <v>1</v>
+      </c>
+      <c r="N2017">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:14" ht="15" customHeight="1">
+      <c r="A2018" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2018" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C2018" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D2018">
+        <v>277</v>
+      </c>
+      <c r="E2018">
+        <v>32</v>
+      </c>
+      <c r="F2018">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2018">
+        <v>37.93</v>
+      </c>
+      <c r="H2018">
+        <v>76</v>
+      </c>
+      <c r="I2018">
+        <v>76.36</v>
+      </c>
+      <c r="J2018" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2018" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2018">
+        <v>4</v>
+      </c>
+      <c r="M2018">
+        <v>1</v>
+      </c>
+      <c r="N2018">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:14" ht="15" customHeight="1">
+      <c r="A2019" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2019" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C2019" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D2019">
+        <v>320</v>
+      </c>
+      <c r="E2019">
+        <v>68</v>
+      </c>
+      <c r="F2019">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2019">
+        <v>43.1</v>
+      </c>
+      <c r="H2019">
+        <v>76</v>
+      </c>
+      <c r="I2019">
+        <v>65.45</v>
+      </c>
+      <c r="J2019" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2019" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2019">
+        <v>4</v>
+      </c>
+      <c r="M2019">
+        <v>3</v>
+      </c>
+      <c r="N2019">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:14" ht="15" customHeight="1">
+      <c r="A2020" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2020" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C2020" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D2020">
+        <v>180</v>
+      </c>
+      <c r="E2020">
+        <v>26</v>
+      </c>
+      <c r="F2020">
+        <v>53.66</v>
+      </c>
+      <c r="G2020">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="H2020">
+        <v>42</v>
+      </c>
+      <c r="I2020">
+        <v>50.91</v>
+      </c>
+      <c r="J2020" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2020" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2020">
+        <v>3</v>
+      </c>
+      <c r="M2020">
+        <v>1</v>
+      </c>
+      <c r="N2020">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:14" ht="15" customHeight="1">
+      <c r="A2021" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2021" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C2021" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D2021">
+        <v>115</v>
+      </c>
+      <c r="E2021">
+        <v>32</v>
+      </c>
+      <c r="F2021">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="G2021">
+        <v>20.69</v>
+      </c>
+      <c r="H2021">
+        <v>18</v>
+      </c>
+      <c r="I2021">
+        <v>27.27</v>
+      </c>
+      <c r="J2021" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2021" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2021">
+        <v>1</v>
+      </c>
+      <c r="M2021">
+        <v>1</v>
+      </c>
+      <c r="N2021">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:14" ht="15" customHeight="1">
+      <c r="A2022" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2022" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C2022" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D2022">
+        <v>183</v>
+      </c>
+      <c r="E2022">
+        <v>40</v>
+      </c>
+      <c r="F2022">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="G2022">
+        <v>25.86</v>
+      </c>
+      <c r="H2022">
+        <v>46</v>
+      </c>
+      <c r="I2022">
+        <v>29.09</v>
+      </c>
+      <c r="J2022" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2022" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2022">
+        <v>2</v>
+      </c>
+      <c r="M2022">
+        <v>2</v>
+      </c>
+      <c r="N2022">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:14" ht="15" customHeight="1">
+      <c r="A2023" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2023" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C2023" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D2023">
+        <v>187</v>
+      </c>
+      <c r="E2023">
+        <v>44</v>
+      </c>
+      <c r="F2023">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G2023">
+        <v>25.86</v>
+      </c>
+      <c r="H2023">
+        <v>42</v>
+      </c>
+      <c r="I2023">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2023" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2023" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2023">
+        <v>2</v>
+      </c>
+      <c r="M2023">
+        <v>2</v>
+      </c>
+      <c r="N2023">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:14" ht="15" customHeight="1">
+      <c r="A2024" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2024" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C2024" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D2024">
+        <v>178</v>
+      </c>
+      <c r="E2024">
+        <v>30</v>
+      </c>
+      <c r="F2024">
+        <v>43.9</v>
+      </c>
+      <c r="G2024">
+        <v>24.14</v>
+      </c>
+      <c r="H2024">
+        <v>34</v>
+      </c>
+      <c r="I2024">
+        <v>65.45</v>
+      </c>
+      <c r="J2024" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2024" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2024">
+        <v>2</v>
+      </c>
+      <c r="M2024">
+        <v>1</v>
+      </c>
+      <c r="N2024">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:14" ht="15" customHeight="1">
+      <c r="A2025" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2025" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C2025" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D2025">
+        <v>207</v>
+      </c>
+      <c r="E2025">
+        <v>46</v>
+      </c>
+      <c r="F2025">
+        <v>31.71</v>
+      </c>
+      <c r="G2025">
+        <v>31.03</v>
+      </c>
+      <c r="H2025">
+        <v>46</v>
+      </c>
+      <c r="I2025">
+        <v>72.73</v>
+      </c>
+      <c r="J2025" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2025" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2025">
+        <v>1</v>
+      </c>
+      <c r="M2025">
+        <v>2</v>
+      </c>
+      <c r="N2025">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:14" ht="15" customHeight="1">
+      <c r="A2026" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2026" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C2026" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D2026">
+        <v>152</v>
+      </c>
+      <c r="E2026">
+        <v>28</v>
+      </c>
+      <c r="F2026">
+        <v>46.34</v>
+      </c>
+      <c r="G2026">
+        <v>22.41</v>
+      </c>
+      <c r="H2026">
+        <v>26</v>
+      </c>
+      <c r="I2026">
+        <v>25.45</v>
+      </c>
+      <c r="J2026" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2026" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2026">
+        <v>2</v>
+      </c>
+      <c r="M2026">
+        <v>1</v>
+      </c>
+      <c r="N2026">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:14" ht="15" customHeight="1">
+      <c r="A2027" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2027" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C2027" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D2027">
+        <v>228</v>
+      </c>
+      <c r="E2027">
+        <v>20</v>
+      </c>
+      <c r="F2027">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2027">
+        <v>24.14</v>
+      </c>
+      <c r="H2027">
+        <v>68</v>
+      </c>
+      <c r="I2027">
+        <v>50.91</v>
+      </c>
+      <c r="J2027" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2027" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2027">
+        <v>4</v>
+      </c>
+      <c r="M2027">
+        <v>1</v>
+      </c>
+      <c r="N2027">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:14" ht="15" customHeight="1">
+      <c r="A2028" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2028" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C2028" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D2028">
+        <v>161</v>
+      </c>
+      <c r="E2028">
+        <v>26</v>
+      </c>
+      <c r="F2028">
+        <v>43.9</v>
+      </c>
+      <c r="G2028">
+        <v>20.69</v>
+      </c>
+      <c r="H2028">
+        <v>34</v>
+      </c>
+      <c r="I2028">
+        <v>43.64</v>
+      </c>
+      <c r="J2028" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2028" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2028">
+        <v>2</v>
+      </c>
+      <c r="M2028">
+        <v>1</v>
+      </c>
+      <c r="N2028">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:14" ht="15" customHeight="1">
+      <c r="A2029" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2029" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C2029" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D2029">
+        <v>194</v>
+      </c>
+      <c r="E2029">
+        <v>42</v>
+      </c>
+      <c r="F2029">
+        <v>41.46</v>
+      </c>
+      <c r="G2029">
+        <v>29.31</v>
+      </c>
+      <c r="H2029">
+        <v>42</v>
+      </c>
+      <c r="I2029">
+        <v>38.18</v>
+      </c>
+      <c r="J2029" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2029" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2029">
+        <v>2</v>
+      </c>
+      <c r="M2029">
+        <v>2</v>
+      </c>
+      <c r="N2029">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:14" ht="15" customHeight="1">
+      <c r="A2030" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2030" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C2030" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D2030">
+        <v>183</v>
+      </c>
+      <c r="E2030">
+        <v>38</v>
+      </c>
+      <c r="F2030">
+        <v>43.9</v>
+      </c>
+      <c r="G2030">
+        <v>32.76</v>
+      </c>
+      <c r="H2030">
+        <v>36</v>
+      </c>
+      <c r="I2030">
+        <v>23.64</v>
+      </c>
+      <c r="J2030" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2030" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2030">
+        <v>2</v>
+      </c>
+      <c r="M2030">
+        <v>2</v>
+      </c>
+      <c r="N2030">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:14" ht="15" customHeight="1">
+      <c r="A2031" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2031" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C2031" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D2031">
+        <v>168</v>
+      </c>
+      <c r="E2031">
+        <v>34</v>
+      </c>
+      <c r="F2031">
+        <v>53.66</v>
+      </c>
+      <c r="G2031">
+        <v>22.41</v>
+      </c>
+      <c r="H2031">
+        <v>22</v>
+      </c>
+      <c r="I2031">
+        <v>38.18</v>
+      </c>
+      <c r="J2031" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2031" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2031">
+        <v>3</v>
+      </c>
+      <c r="M2031">
+        <v>1</v>
+      </c>
+      <c r="N2031">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:14" ht="15" customHeight="1">
+      <c r="A2032" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2032" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C2032" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D2032">
+        <v>189</v>
+      </c>
+      <c r="E2032">
+        <v>24</v>
+      </c>
+      <c r="F2032">
+        <v>51.22</v>
+      </c>
+      <c r="G2032">
+        <v>31.03</v>
+      </c>
+      <c r="H2032">
+        <v>46</v>
+      </c>
+      <c r="I2032">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2032" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2032" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2032">
+        <v>3</v>
+      </c>
+      <c r="M2032">
+        <v>1</v>
+      </c>
+      <c r="N2032">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:14" ht="15" customHeight="1">
+      <c r="A2033" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2033" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C2033" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D2033">
+        <v>194</v>
+      </c>
+      <c r="E2033">
+        <v>32</v>
+      </c>
+      <c r="F2033">
+        <v>43.9</v>
+      </c>
+      <c r="G2033">
+        <v>27.59</v>
+      </c>
+      <c r="H2033">
+        <v>50</v>
+      </c>
+      <c r="I2033">
+        <v>43.64</v>
+      </c>
+      <c r="J2033" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2033" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2033">
+        <v>2</v>
+      </c>
+      <c r="M2033">
+        <v>1</v>
+      </c>
+      <c r="N2033">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:14" ht="15" customHeight="1">
+      <c r="A2034" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2034" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C2034" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D2034">
+        <v>204</v>
+      </c>
+      <c r="E2034">
+        <v>40</v>
+      </c>
+      <c r="F2034">
+        <v>46.34</v>
+      </c>
+      <c r="G2034">
+        <v>31.03</v>
+      </c>
+      <c r="H2034">
+        <v>44</v>
+      </c>
+      <c r="I2034">
+        <v>45.45</v>
+      </c>
+      <c r="J2034" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2034" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2034">
+        <v>2</v>
+      </c>
+      <c r="M2034">
+        <v>2</v>
+      </c>
+      <c r="N2034">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:14" ht="15" customHeight="1">
+      <c r="A2035" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2035" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C2035" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D2035">
+        <v>212</v>
+      </c>
+      <c r="E2035">
+        <v>36</v>
+      </c>
+      <c r="F2035">
+        <v>46.34</v>
+      </c>
+      <c r="G2035">
+        <v>31.03</v>
+      </c>
+      <c r="H2035">
+        <v>48</v>
+      </c>
+      <c r="I2035">
+        <v>65.45</v>
+      </c>
+      <c r="J2035" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2035" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2035">
+        <v>2</v>
+      </c>
+      <c r="M2035">
+        <v>2</v>
+      </c>
+      <c r="N2035">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:14" ht="15" customHeight="1">
+      <c r="A2036" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2036" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C2036" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D2036">
+        <v>132</v>
+      </c>
+      <c r="E2036">
+        <v>26</v>
+      </c>
+      <c r="F2036">
+        <v>29.27</v>
+      </c>
+      <c r="G2036">
+        <v>24.14</v>
+      </c>
+      <c r="H2036">
+        <v>24</v>
+      </c>
+      <c r="I2036">
+        <v>30.91</v>
+      </c>
+      <c r="J2036" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2036" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2036">
+        <v>1</v>
+      </c>
+      <c r="M2036">
+        <v>1</v>
+      </c>
+      <c r="N2036">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:14" ht="15" customHeight="1">
+      <c r="A2037" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2037" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C2037" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D2037">
+        <v>177</v>
+      </c>
+      <c r="E2037">
+        <v>22</v>
+      </c>
+      <c r="F2037">
+        <v>41.46</v>
+      </c>
+      <c r="G2037">
+        <v>18.97</v>
+      </c>
+      <c r="H2037">
+        <v>60</v>
+      </c>
+      <c r="I2037">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2037" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2037" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2037">
+        <v>2</v>
+      </c>
+      <c r="M2037">
+        <v>1</v>
+      </c>
+      <c r="N2037">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:14" ht="15" customHeight="1">
+      <c r="A2038" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2038" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C2038" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D2038">
+        <v>162</v>
+      </c>
+      <c r="E2038">
+        <v>20</v>
+      </c>
+      <c r="F2038">
+        <v>43.9</v>
+      </c>
+      <c r="G2038">
+        <v>24.14</v>
+      </c>
+      <c r="H2038">
+        <v>40</v>
+      </c>
+      <c r="I2038">
+        <v>36.36</v>
+      </c>
+      <c r="J2038" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2038" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2038">
+        <v>2</v>
+      </c>
+      <c r="M2038">
+        <v>1</v>
+      </c>
+      <c r="N2038">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:14" ht="15" customHeight="1">
+      <c r="A2039" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2039" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C2039" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D2039">
+        <v>277</v>
+      </c>
+      <c r="E2039">
+        <v>52</v>
+      </c>
+      <c r="F2039">
+        <v>73.17</v>
+      </c>
+      <c r="G2039">
+        <v>41.38</v>
+      </c>
+      <c r="H2039">
+        <v>62</v>
+      </c>
+      <c r="I2039">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2039" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2039" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2039">
+        <v>4</v>
+      </c>
+      <c r="M2039">
+        <v>3</v>
+      </c>
+      <c r="N2039">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:14" ht="15" customHeight="1">
+      <c r="A2040" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2040" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C2040" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D2040">
+        <v>191</v>
+      </c>
+      <c r="E2040">
+        <v>30</v>
+      </c>
+      <c r="F2040">
+        <v>51.22</v>
+      </c>
+      <c r="G2040">
+        <v>27.59</v>
+      </c>
+      <c r="H2040">
+        <v>40</v>
+      </c>
+      <c r="I2040">
+        <v>49.09</v>
+      </c>
+      <c r="J2040" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2040" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2040">
+        <v>3</v>
+      </c>
+      <c r="M2040">
+        <v>1</v>
+      </c>
+      <c r="N2040">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:14" ht="15" customHeight="1">
+      <c r="A2041" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2041" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C2041" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D2041">
+        <v>211</v>
+      </c>
+      <c r="E2041">
+        <v>28</v>
+      </c>
+      <c r="F2041">
+        <v>51.22</v>
+      </c>
+      <c r="G2041">
+        <v>31.03</v>
+      </c>
+      <c r="H2041">
+        <v>56</v>
+      </c>
+      <c r="I2041">
+        <v>49.09</v>
+      </c>
+      <c r="J2041" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2041" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2041">
+        <v>3</v>
+      </c>
+      <c r="M2041">
+        <v>1</v>
+      </c>
+      <c r="N2041">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:14" ht="15" customHeight="1">
+      <c r="A2042" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2042" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C2042" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D2042">
+        <v>268</v>
+      </c>
+      <c r="E2042">
+        <v>44</v>
+      </c>
+      <c r="F2042">
+        <v>58.54</v>
+      </c>
+      <c r="G2042">
+        <v>48.28</v>
+      </c>
+      <c r="H2042">
+        <v>60</v>
+      </c>
+      <c r="I2042">
+        <v>61.82</v>
+      </c>
+      <c r="J2042" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2042" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2042">
+        <v>3</v>
+      </c>
+      <c r="M2042">
+        <v>2</v>
+      </c>
+      <c r="N2042">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:14" ht="15" customHeight="1">
+      <c r="A2043" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2043" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C2043" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D2043">
+        <v>192</v>
+      </c>
+      <c r="E2043">
+        <v>48</v>
+      </c>
+      <c r="F2043">
+        <v>43.9</v>
+      </c>
+      <c r="G2043">
+        <v>24.14</v>
+      </c>
+      <c r="H2043">
+        <v>40</v>
+      </c>
+      <c r="I2043">
+        <v>30.91</v>
+      </c>
+      <c r="J2043" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2043" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2043">
+        <v>2</v>
+      </c>
+      <c r="M2043">
+        <v>2</v>
+      </c>
+      <c r="N2043">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:14" ht="15" customHeight="1">
+      <c r="A2044" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2044" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C2044" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D2044">
+        <v>153</v>
+      </c>
+      <c r="E2044">
+        <v>28</v>
+      </c>
+      <c r="F2044">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G2044">
+        <v>20.69</v>
+      </c>
+      <c r="H2044">
+        <v>36</v>
+      </c>
+      <c r="I2044">
+        <v>25.45</v>
+      </c>
+      <c r="J2044" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2044" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2044">
+        <v>2</v>
+      </c>
+      <c r="M2044">
+        <v>1</v>
+      </c>
+      <c r="N2044">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:14" ht="15" customHeight="1">
+      <c r="A2045" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2045" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C2045" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D2045">
+        <v>226</v>
+      </c>
+      <c r="E2045">
+        <v>46</v>
+      </c>
+      <c r="F2045">
+        <v>46.34</v>
+      </c>
+      <c r="G2045">
+        <v>25.86</v>
+      </c>
+      <c r="H2045">
+        <v>52</v>
+      </c>
+      <c r="I2045">
+        <v>76.36</v>
+      </c>
+      <c r="J2045" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2045" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2045">
+        <v>2</v>
+      </c>
+      <c r="M2045">
+        <v>2</v>
+      </c>
+      <c r="N2045">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:14" ht="15" customHeight="1">
+      <c r="A2046" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2046" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C2046" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D2046">
+        <v>197</v>
+      </c>
+      <c r="E2046">
+        <v>40</v>
+      </c>
+      <c r="F2046">
+        <v>43.9</v>
+      </c>
+      <c r="G2046">
+        <v>20.69</v>
+      </c>
+      <c r="H2046">
+        <v>40</v>
+      </c>
+      <c r="I2046">
+        <v>76.36</v>
+      </c>
+      <c r="J2046" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2046" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2046">
+        <v>2</v>
+      </c>
+      <c r="M2046">
+        <v>2</v>
+      </c>
+      <c r="N2046">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:14" ht="15" customHeight="1">
+      <c r="A2047" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2047" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C2047" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D2047">
+        <v>227</v>
+      </c>
+      <c r="E2047">
+        <v>44</v>
+      </c>
+      <c r="F2047">
+        <v>56.1</v>
+      </c>
+      <c r="G2047">
+        <v>32.76</v>
+      </c>
+      <c r="H2047">
+        <v>48</v>
+      </c>
+      <c r="I2047">
+        <v>45.45</v>
+      </c>
+      <c r="J2047" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2047" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2047">
+        <v>3</v>
+      </c>
+      <c r="M2047">
+        <v>2</v>
+      </c>
+      <c r="N2047">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:14" ht="15" customHeight="1">
+      <c r="A2048" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2048" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C2048" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D2048">
+        <v>204</v>
+      </c>
+      <c r="E2048">
+        <v>32</v>
+      </c>
+      <c r="F2048">
+        <v>56.1</v>
+      </c>
+      <c r="G2048">
+        <v>29.31</v>
+      </c>
+      <c r="H2048">
+        <v>44</v>
+      </c>
+      <c r="I2048">
+        <v>45.45</v>
+      </c>
+      <c r="J2048" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2048" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2048">
+        <v>3</v>
+      </c>
+      <c r="M2048">
+        <v>1</v>
+      </c>
+      <c r="N2048">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:14" ht="15" customHeight="1">
+      <c r="A2049" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2049" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C2049" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D2049">
+        <v>196</v>
+      </c>
+      <c r="E2049">
+        <v>16</v>
+      </c>
+      <c r="F2049">
+        <v>53.66</v>
+      </c>
+      <c r="G2049">
+        <v>31.03</v>
+      </c>
+      <c r="H2049">
+        <v>54</v>
+      </c>
+      <c r="I2049">
+        <v>45.45</v>
+      </c>
+      <c r="J2049" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2049" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2049">
+        <v>3</v>
+      </c>
+      <c r="M2049">
+        <v>1</v>
+      </c>
+      <c r="N2049">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:14" ht="15" customHeight="1">
+      <c r="A2050" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2050" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C2050" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D2050">
+        <v>284</v>
+      </c>
+      <c r="E2050">
+        <v>56</v>
+      </c>
+      <c r="F2050">
+        <v>70.73</v>
+      </c>
+      <c r="G2050">
+        <v>53.45</v>
+      </c>
+      <c r="H2050">
+        <v>54</v>
+      </c>
+      <c r="I2050">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2050" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2050" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2050">
+        <v>4</v>
+      </c>
+      <c r="M2050">
+        <v>3</v>
+      </c>
+      <c r="N2050">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:14" ht="15" customHeight="1">
+      <c r="A2051" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2051" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C2051" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D2051">
+        <v>192</v>
+      </c>
+      <c r="E2051">
+        <v>44</v>
+      </c>
+      <c r="F2051">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G2051">
+        <v>27.59</v>
+      </c>
+      <c r="H2051">
+        <v>42</v>
+      </c>
+      <c r="I2051">
+        <v>40</v>
+      </c>
+      <c r="J2051" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2051" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2051">
+        <v>2</v>
+      </c>
+      <c r="M2051">
+        <v>2</v>
+      </c>
+      <c r="N2051">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:14" ht="15" customHeight="1">
+      <c r="A2052" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2052" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C2052" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D2052">
+        <v>249</v>
+      </c>
+      <c r="E2052">
+        <v>38</v>
+      </c>
+      <c r="F2052">
+        <v>53.66</v>
+      </c>
+      <c r="G2052">
+        <v>36.21</v>
+      </c>
+      <c r="H2052">
+        <v>78</v>
+      </c>
+      <c r="I2052">
+        <v>27.27</v>
+      </c>
+      <c r="J2052" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2052" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2052">
+        <v>3</v>
+      </c>
+      <c r="M2052">
+        <v>2</v>
+      </c>
+      <c r="N2052">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:14" ht="15" customHeight="1">
+      <c r="A2053" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2053" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C2053" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D2053">
+        <v>233</v>
+      </c>
+      <c r="E2053">
+        <v>44</v>
+      </c>
+      <c r="F2053">
+        <v>60.98</v>
+      </c>
+      <c r="G2053">
+        <v>31.03</v>
+      </c>
+      <c r="H2053">
+        <v>56</v>
+      </c>
+      <c r="I2053">
+        <v>27.27</v>
+      </c>
+      <c r="J2053" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2053" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2053">
+        <v>3</v>
+      </c>
+      <c r="M2053">
+        <v>2</v>
+      </c>
+      <c r="N2053">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:14" ht="15" customHeight="1">
+      <c r="A2054" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2054" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C2054" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D2054">
+        <v>143</v>
+      </c>
+      <c r="E2054">
+        <v>28</v>
+      </c>
+      <c r="F2054">
+        <v>21.95</v>
+      </c>
+      <c r="G2054">
+        <v>36.21</v>
+      </c>
+      <c r="H2054">
+        <v>26</v>
+      </c>
+      <c r="I2054">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2054" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2054" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2054">
+        <v>1</v>
+      </c>
+      <c r="M2054">
+        <v>1</v>
+      </c>
+      <c r="N2054">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:14" ht="15" customHeight="1">
+      <c r="A2055" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2055" t="s">
+        <v>841</v>
+      </c>
+      <c r="C2055" t="s">
+        <v>842</v>
+      </c>
+      <c r="D2055">
+        <v>259</v>
+      </c>
+      <c r="E2055">
+        <v>34</v>
+      </c>
+      <c r="F2055">
+        <v>58.54</v>
+      </c>
+      <c r="G2055">
+        <v>50</v>
+      </c>
+      <c r="H2055">
+        <v>60</v>
+      </c>
+      <c r="I2055">
+        <v>65.45</v>
+      </c>
+      <c r="J2055" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2055" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2055">
+        <v>3</v>
+      </c>
+      <c r="M2055">
+        <v>1</v>
+      </c>
+      <c r="N2055">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:14" ht="15" customHeight="1">
+      <c r="A2056" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2056" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C2056" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D2056">
+        <v>226</v>
+      </c>
+      <c r="E2056">
+        <v>32</v>
+      </c>
+      <c r="F2056">
+        <v>60.98</v>
+      </c>
+      <c r="G2056">
+        <v>27.59</v>
+      </c>
+      <c r="H2056">
+        <v>56</v>
+      </c>
+      <c r="I2056">
+        <v>56.36</v>
+      </c>
+      <c r="J2056" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2056" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2056">
+        <v>3</v>
+      </c>
+      <c r="M2056">
+        <v>1</v>
+      </c>
+      <c r="N2056">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:14" ht="15" customHeight="1">
+      <c r="A2057" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2057" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C2057" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D2057">
+        <v>202</v>
+      </c>
+      <c r="E2057">
+        <v>32</v>
+      </c>
+      <c r="F2057">
+        <v>31.71</v>
+      </c>
+      <c r="G2057">
+        <v>48.28</v>
+      </c>
+      <c r="H2057">
+        <v>42</v>
+      </c>
+      <c r="I2057">
+        <v>61.82</v>
+      </c>
+      <c r="J2057" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2057" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2057">
+        <v>1</v>
+      </c>
+      <c r="M2057">
+        <v>1</v>
+      </c>
+      <c r="N2057">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:14" ht="15" customHeight="1">
+      <c r="A2058" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2058" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C2058" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D2058">
+        <v>193</v>
+      </c>
+      <c r="E2058">
+        <v>22</v>
+      </c>
+      <c r="F2058">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G2058">
+        <v>44.83</v>
+      </c>
+      <c r="H2058">
+        <v>40</v>
+      </c>
+      <c r="I2058">
+        <v>63.64</v>
+      </c>
+      <c r="J2058" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2058" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2058">
+        <v>2</v>
+      </c>
+      <c r="M2058">
+        <v>1</v>
+      </c>
+      <c r="N2058">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:14" ht="15" customHeight="1">
+      <c r="A2059" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2059" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C2059" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D2059">
+        <v>183</v>
+      </c>
+      <c r="E2059">
+        <v>34</v>
+      </c>
+      <c r="F2059">
+        <v>43.9</v>
+      </c>
+      <c r="G2059">
+        <v>20.69</v>
+      </c>
+      <c r="H2059">
+        <v>48</v>
+      </c>
+      <c r="I2059">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2059" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2059" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2059">
+        <v>2</v>
+      </c>
+      <c r="M2059">
+        <v>1</v>
+      </c>
+      <c r="N2059">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:14" ht="15" customHeight="1">
+      <c r="A2060" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2060" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C2060" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D2060">
+        <v>303</v>
+      </c>
+      <c r="E2060">
+        <v>56</v>
+      </c>
+      <c r="F2060">
+        <v>73.17</v>
+      </c>
+      <c r="G2060">
+        <v>44.83</v>
+      </c>
+      <c r="H2060">
+        <v>74</v>
+      </c>
+      <c r="I2060">
+        <v>41.82</v>
+      </c>
+      <c r="J2060" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2060" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2060">
+        <v>4</v>
+      </c>
+      <c r="M2060">
+        <v>3</v>
+      </c>
+      <c r="N2060">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:14" ht="15" customHeight="1">
+      <c r="A2061" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2061" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C2061" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D2061">
+        <v>160</v>
+      </c>
+      <c r="E2061">
+        <v>30</v>
+      </c>
+      <c r="F2061">
+        <v>43.9</v>
+      </c>
+      <c r="G2061">
+        <v>25.86</v>
+      </c>
+      <c r="H2061">
+        <v>26</v>
+      </c>
+      <c r="I2061">
+        <v>38.18</v>
+      </c>
+      <c r="J2061" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2061" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2061">
+        <v>2</v>
+      </c>
+      <c r="M2061">
+        <v>1</v>
+      </c>
+      <c r="N2061">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:14" ht="15" customHeight="1">
+      <c r="A2062" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2062" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C2062" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D2062">
+        <v>148</v>
+      </c>
+      <c r="E2062">
+        <v>28</v>
+      </c>
+      <c r="F2062">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="G2062">
+        <v>25.86</v>
+      </c>
+      <c r="H2062">
+        <v>28</v>
+      </c>
+      <c r="I2062">
+        <v>29.09</v>
+      </c>
+      <c r="J2062" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2062" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2062">
+        <v>2</v>
+      </c>
+      <c r="M2062">
+        <v>1</v>
+      </c>
+      <c r="N2062">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:14" ht="15" customHeight="1">
+      <c r="A2063" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2063" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C2063" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D2063">
+        <v>209</v>
+      </c>
+      <c r="E2063">
+        <v>24</v>
+      </c>
+      <c r="F2063">
+        <v>53.66</v>
+      </c>
+      <c r="G2063">
+        <v>24.14</v>
+      </c>
+      <c r="H2063">
+        <v>52</v>
+      </c>
+      <c r="I2063">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="J2063" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2063" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2063">
+        <v>3</v>
+      </c>
+      <c r="M2063">
+        <v>1</v>
+      </c>
+      <c r="N2063">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:14" ht="15" customHeight="1">
+      <c r="A2064" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2064" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C2064" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D2064">
+        <v>227</v>
+      </c>
+      <c r="E2064">
+        <v>32</v>
+      </c>
+      <c r="F2064">
+        <v>43.9</v>
+      </c>
+      <c r="G2064">
+        <v>46.55</v>
+      </c>
+      <c r="H2064">
+        <v>60</v>
+      </c>
+      <c r="I2064">
+        <v>41.82</v>
+      </c>
+      <c r="J2064" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2064" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2064">
+        <v>2</v>
+      </c>
+      <c r="M2064">
+        <v>1</v>
+      </c>
+      <c r="N2064">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:14" ht="15" customHeight="1">
+      <c r="A2065" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2065" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C2065" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D2065">
+        <v>154</v>
+      </c>
+      <c r="E2065">
+        <v>26</v>
+      </c>
+      <c r="F2065">
+        <v>31.71</v>
+      </c>
+      <c r="G2065">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H2065">
+        <v>32</v>
+      </c>
+      <c r="I2065">
+        <v>25.45</v>
+      </c>
+      <c r="J2065" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2065" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2065">
+        <v>1</v>
+      </c>
+      <c r="M2065">
+        <v>1</v>
+      </c>
+      <c r="N2065">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:14" ht="15" customHeight="1">
+      <c r="A2066" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2066" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C2066" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D2066">
+        <v>225</v>
+      </c>
+      <c r="E2066">
+        <v>32</v>
+      </c>
+      <c r="F2066">
+        <v>53.66</v>
+      </c>
+      <c r="G2066">
+        <v>32.76</v>
+      </c>
+      <c r="H2066">
+        <v>60</v>
+      </c>
+      <c r="I2066">
+        <v>49.09</v>
+      </c>
+      <c r="J2066" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2066" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2066">
+        <v>3</v>
+      </c>
+      <c r="M2066">
+        <v>1</v>
+      </c>
+      <c r="N2066">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:14" ht="15" customHeight="1">
+      <c r="A2067" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2067" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C2067" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D2067">
+        <v>202</v>
+      </c>
+      <c r="E2067">
+        <v>26</v>
+      </c>
+      <c r="F2067">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G2067">
+        <v>44.83</v>
+      </c>
+      <c r="H2067">
+        <v>44</v>
+      </c>
+      <c r="I2067">
+        <v>63.64</v>
+      </c>
+      <c r="J2067" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2067" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2067">
+        <v>2</v>
+      </c>
+      <c r="M2067">
+        <v>1</v>
+      </c>
+      <c r="N2067">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:14" ht="15" customHeight="1">
+      <c r="A2068" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2068" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C2068" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D2068">
+        <v>197</v>
+      </c>
+      <c r="E2068">
+        <v>26</v>
+      </c>
+      <c r="F2068">
+        <v>43.9</v>
+      </c>
+      <c r="G2068">
+        <v>43.1</v>
+      </c>
+      <c r="H2068">
+        <v>40</v>
+      </c>
+      <c r="I2068">
+        <v>50.91</v>
+      </c>
+      <c r="J2068" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2068" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2068">
+        <v>2</v>
+      </c>
+      <c r="M2068">
+        <v>1</v>
+      </c>
+      <c r="N2068">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:14" ht="15" customHeight="1">
+      <c r="A2069" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2069" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C2069" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D2069">
+        <v>262</v>
+      </c>
+      <c r="E2069">
+        <v>42</v>
+      </c>
+      <c r="F2069">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2069">
+        <v>37.93</v>
+      </c>
+      <c r="H2069">
+        <v>64</v>
+      </c>
+      <c r="I2069">
+        <v>50.91</v>
+      </c>
+      <c r="J2069" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2069" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2069">
+        <v>3</v>
+      </c>
+      <c r="M2069">
+        <v>2</v>
+      </c>
+      <c r="N2069">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:14" ht="15" customHeight="1">
+      <c r="A2070" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2070" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C2070" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D2070">
+        <v>311</v>
+      </c>
+      <c r="E2070">
+        <v>46</v>
+      </c>
+      <c r="F2070">
+        <v>75.61</v>
+      </c>
+      <c r="G2070">
+        <v>41.38</v>
+      </c>
+      <c r="H2070">
+        <v>78</v>
+      </c>
+      <c r="I2070">
+        <v>85.45</v>
+      </c>
+      <c r="J2070" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2070" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2070">
+        <v>4</v>
+      </c>
+      <c r="M2070">
+        <v>2</v>
+      </c>
+      <c r="N2070">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:14" ht="15" customHeight="1">
+      <c r="A2071" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2071" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C2071" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D2071">
+        <v>176</v>
+      </c>
+      <c r="E2071">
+        <v>32</v>
+      </c>
+      <c r="F2071">
+        <v>51.22</v>
+      </c>
+      <c r="G2071">
+        <v>29.31</v>
+      </c>
+      <c r="H2071">
+        <v>26</v>
+      </c>
+      <c r="I2071">
+        <v>41.82</v>
+      </c>
+      <c r="J2071" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2071" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2071">
+        <v>3</v>
+      </c>
+      <c r="M2071">
+        <v>1</v>
+      </c>
+      <c r="N2071">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:14" ht="15" customHeight="1">
+      <c r="A2072" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2072" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C2072" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D2072">
+        <v>182</v>
+      </c>
+      <c r="E2072">
+        <v>26</v>
+      </c>
+      <c r="F2072">
+        <v>51.22</v>
+      </c>
+      <c r="G2072">
+        <v>31.03</v>
+      </c>
+      <c r="H2072">
+        <v>40</v>
+      </c>
+      <c r="I2072">
+        <v>27.27</v>
+      </c>
+      <c r="J2072" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2072" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2072">
+        <v>3</v>
+      </c>
+      <c r="M2072">
+        <v>1</v>
+      </c>
+      <c r="N2072">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:14" ht="15" customHeight="1">
+      <c r="A2073" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2073" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C2073" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D2073">
+        <v>119</v>
+      </c>
+      <c r="E2073">
+        <v>26</v>
+      </c>
+      <c r="F2073">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="G2073">
+        <v>31.03</v>
+      </c>
+      <c r="H2073">
+        <v>18</v>
+      </c>
+      <c r="I2073">
+        <v>25.45</v>
+      </c>
+      <c r="J2073" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2073" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2073">
+        <v>1</v>
+      </c>
+      <c r="M2073">
+        <v>1</v>
+      </c>
+      <c r="N2073">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:14" ht="15" customHeight="1">
+      <c r="A2074" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2074" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C2074" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D2074">
+        <v>224</v>
+      </c>
+      <c r="E2074">
+        <v>50</v>
+      </c>
+      <c r="F2074">
+        <v>29.27</v>
+      </c>
+      <c r="G2074">
+        <v>27.59</v>
+      </c>
+      <c r="H2074">
+        <v>66</v>
+      </c>
+      <c r="I2074">
+        <v>63.64</v>
+      </c>
+      <c r="J2074" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2074" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2074">
+        <v>1</v>
+      </c>
+      <c r="M2074">
+        <v>2</v>
+      </c>
+      <c r="N2074">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:14" ht="15" customHeight="1">
+      <c r="A2075" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2075" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C2075" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D2075">
+        <v>261</v>
+      </c>
+      <c r="E2075">
+        <v>40</v>
+      </c>
+      <c r="F2075">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2075">
+        <v>27.59</v>
+      </c>
+      <c r="H2075">
+        <v>66</v>
+      </c>
+      <c r="I2075">
+        <v>80</v>
+      </c>
+      <c r="J2075" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2075" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2075">
+        <v>3</v>
+      </c>
+      <c r="M2075">
+        <v>2</v>
+      </c>
+      <c r="N2075">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:14" ht="15" customHeight="1">
+      <c r="A2076" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2076" t="s">
+        <v>835</v>
+      </c>
+      <c r="C2076" t="s">
+        <v>836</v>
+      </c>
+      <c r="D2076">
+        <v>258</v>
+      </c>
+      <c r="E2076">
+        <v>28</v>
+      </c>
+      <c r="F2076">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2076">
+        <v>56.9</v>
+      </c>
+      <c r="H2076">
+        <v>54</v>
+      </c>
+      <c r="I2076">
+        <v>56.36</v>
+      </c>
+      <c r="J2076" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2076" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2076">
+        <v>3</v>
+      </c>
+      <c r="M2076">
+        <v>1</v>
+      </c>
+      <c r="N2076">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:14" ht="15" customHeight="1">
+      <c r="A2077" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2077" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C2077" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D2077">
+        <v>172</v>
+      </c>
+      <c r="E2077">
+        <v>44</v>
+      </c>
+      <c r="F2077">
+        <v>29.27</v>
+      </c>
+      <c r="G2077">
+        <v>15.52</v>
+      </c>
+      <c r="H2077">
+        <v>36</v>
+      </c>
+      <c r="I2077">
+        <v>72.73</v>
+      </c>
+      <c r="J2077" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2077" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2077">
+        <v>1</v>
+      </c>
+      <c r="M2077">
+        <v>2</v>
+      </c>
+      <c r="N2077">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:14" ht="15" customHeight="1">
+      <c r="A2078" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2078" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C2078" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D2078">
+        <v>230</v>
+      </c>
+      <c r="E2078">
+        <v>42</v>
+      </c>
+      <c r="F2078">
+        <v>53.66</v>
+      </c>
+      <c r="G2078">
+        <v>43.1</v>
+      </c>
+      <c r="H2078">
+        <v>48</v>
+      </c>
+      <c r="I2078">
+        <v>36.36</v>
+      </c>
+      <c r="J2078" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2078" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2078">
+        <v>3</v>
+      </c>
+      <c r="M2078">
+        <v>2</v>
+      </c>
+      <c r="N2078">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:14" ht="15" customHeight="1">
+      <c r="A2079" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2079" t="s">
+        <v>921</v>
+      </c>
+      <c r="C2079" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D2079">
+        <v>128</v>
+      </c>
+      <c r="E2079">
+        <v>28</v>
+      </c>
+      <c r="F2079">
+        <v>26.83</v>
+      </c>
+      <c r="G2079">
+        <v>25.86</v>
+      </c>
+      <c r="H2079">
+        <v>18</v>
+      </c>
+      <c r="I2079">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2079" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2079" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2079">
+        <v>1</v>
+      </c>
+      <c r="M2079">
+        <v>1</v>
+      </c>
+      <c r="N2079">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:14" ht="15" customHeight="1">
+      <c r="A2080" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2080" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C2080" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D2080">
+        <v>234</v>
+      </c>
+      <c r="E2080">
+        <v>40</v>
+      </c>
+      <c r="F2080">
+        <v>53.66</v>
+      </c>
+      <c r="G2080">
+        <v>32.76</v>
+      </c>
+      <c r="H2080">
+        <v>62</v>
+      </c>
+      <c r="I2080">
+        <v>41.82</v>
+      </c>
+      <c r="J2080" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2080" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2080">
+        <v>3</v>
+      </c>
+      <c r="M2080">
+        <v>2</v>
+      </c>
+      <c r="N2080">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:14" ht="15" customHeight="1">
+      <c r="A2081" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2081" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C2081" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D2081">
+        <v>185</v>
+      </c>
+      <c r="E2081">
+        <v>36</v>
+      </c>
+      <c r="F2081">
+        <v>51.22</v>
+      </c>
+      <c r="G2081">
+        <v>24.14</v>
+      </c>
+      <c r="H2081">
+        <v>38</v>
+      </c>
+      <c r="I2081">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2081" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2081" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2081">
+        <v>3</v>
+      </c>
+      <c r="M2081">
+        <v>2</v>
+      </c>
+      <c r="N2081">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:14" ht="15" customHeight="1">
+      <c r="A2082" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2082" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C2082" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D2082">
+        <v>292</v>
+      </c>
+      <c r="E2082">
+        <v>46</v>
+      </c>
+      <c r="F2082">
+        <v>53.66</v>
+      </c>
+      <c r="G2082">
+        <v>63.79</v>
+      </c>
+      <c r="H2082">
+        <v>72</v>
+      </c>
+      <c r="I2082">
+        <v>50.91</v>
+      </c>
+      <c r="J2082" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2082" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2082">
+        <v>3</v>
+      </c>
+      <c r="M2082">
+        <v>2</v>
+      </c>
+      <c r="N2082">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:14" ht="15" customHeight="1">
+      <c r="A2083" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2083" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C2083" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D2083">
+        <v>174</v>
+      </c>
+      <c r="E2083">
+        <v>48</v>
+      </c>
+      <c r="F2083">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G2083">
+        <v>24.14</v>
+      </c>
+      <c r="H2083">
+        <v>28</v>
+      </c>
+      <c r="I2083">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2083" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2083" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2083">
+        <v>2</v>
+      </c>
+      <c r="M2083">
+        <v>2</v>
+      </c>
+      <c r="N2083">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:14" ht="15" customHeight="1">
+      <c r="A2084" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2084" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C2084" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D2084">
+        <v>146</v>
+      </c>
+      <c r="E2084">
+        <v>22</v>
+      </c>
+      <c r="F2084">
+        <v>29.27</v>
+      </c>
+      <c r="G2084">
+        <v>27.59</v>
+      </c>
+      <c r="H2084">
+        <v>38</v>
+      </c>
+      <c r="I2084">
+        <v>27.27</v>
+      </c>
+      <c r="J2084" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2084" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2084">
+        <v>1</v>
+      </c>
+      <c r="M2084">
+        <v>1</v>
+      </c>
+      <c r="N2084">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:14" ht="15" customHeight="1">
+      <c r="A2085" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2085" t="s">
+        <v>814</v>
+      </c>
+      <c r="C2085" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D2085">
+        <v>250</v>
+      </c>
+      <c r="E2085">
+        <v>40</v>
+      </c>
+      <c r="F2085">
+        <v>56.1</v>
+      </c>
+      <c r="G2085">
+        <v>32.76</v>
+      </c>
+      <c r="H2085">
+        <v>64</v>
+      </c>
+      <c r="I2085">
+        <v>70.91</v>
+      </c>
+      <c r="J2085" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2085" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2085">
+        <v>3</v>
+      </c>
+      <c r="M2085">
+        <v>2</v>
+      </c>
+      <c r="N2085">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:14" ht="15" customHeight="1">
+      <c r="A2086" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2086" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C2086" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D2086">
+        <v>269</v>
+      </c>
+      <c r="E2086">
+        <v>44</v>
+      </c>
+      <c r="F2086">
+        <v>60.98</v>
+      </c>
+      <c r="G2086">
+        <v>46.55</v>
+      </c>
+      <c r="H2086">
+        <v>70</v>
+      </c>
+      <c r="I2086">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2086" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2086" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2086">
+        <v>3</v>
+      </c>
+      <c r="M2086">
+        <v>2</v>
+      </c>
+      <c r="N2086">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1825" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/data/Resultados_Simulacro_ICFES.xlsx
+++ b/data/Resultados_Simulacro_ICFES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorios\R_IEOS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D99D0E-336C-4E21-B6E2-EC080027D258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961CEBA7-9C0B-436C-B546-74B0E2577E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7822" uniqueCount="1458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8427" uniqueCount="1470">
   <si>
     <t>Grupo</t>
   </si>
@@ -4411,6 +4411,42 @@
   </si>
   <si>
     <t>WALKER MIELES XANDER FELIPE</t>
+  </si>
+  <si>
+    <t>1020447424</t>
+  </si>
+  <si>
+    <t>AGUDELO GALEANO SELENY ANDREA</t>
+  </si>
+  <si>
+    <t>1098074984</t>
+  </si>
+  <si>
+    <t>CORDOBA RUEDA JOHAN RENE</t>
+  </si>
+  <si>
+    <t>1115731422</t>
+  </si>
+  <si>
+    <t>LARROTA MANRIQUE KHENNER DANILO</t>
+  </si>
+  <si>
+    <t>1040574487</t>
+  </si>
+  <si>
+    <t>ROSERO JARAMILLO MARIA JOSE</t>
+  </si>
+  <si>
+    <t>1020119375</t>
+  </si>
+  <si>
+    <t>GIL SALAZAR VALERIA</t>
+  </si>
+  <si>
+    <t>1013462894</t>
+  </si>
+  <si>
+    <t>FRANCO CARDONA SANTIAGO</t>
   </si>
 </sst>
 </file>
@@ -4779,7 +4815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2086"/>
+  <dimension ref="A1:N2207"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -96572,6 +96608,5330 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2087" spans="1:14" ht="15" customHeight="1">
+      <c r="A2087" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2087" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C2087" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D2087">
+        <v>334</v>
+      </c>
+      <c r="E2087">
+        <v>60</v>
+      </c>
+      <c r="F2087">
+        <v>82.93</v>
+      </c>
+      <c r="G2087">
+        <v>62.07</v>
+      </c>
+      <c r="H2087">
+        <v>68</v>
+      </c>
+      <c r="I2087">
+        <v>49.09</v>
+      </c>
+      <c r="J2087" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2087" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2087">
+        <v>4</v>
+      </c>
+      <c r="M2087">
+        <v>3</v>
+      </c>
+      <c r="N2087">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:14" ht="15" customHeight="1">
+      <c r="A2088" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2088" t="s">
+        <v>789</v>
+      </c>
+      <c r="C2088" t="s">
+        <v>953</v>
+      </c>
+      <c r="D2088">
+        <v>317</v>
+      </c>
+      <c r="E2088">
+        <v>54</v>
+      </c>
+      <c r="F2088">
+        <v>73.17</v>
+      </c>
+      <c r="G2088">
+        <v>46.55</v>
+      </c>
+      <c r="H2088">
+        <v>74</v>
+      </c>
+      <c r="I2088">
+        <v>80</v>
+      </c>
+      <c r="J2088" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2088" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2088">
+        <v>4</v>
+      </c>
+      <c r="M2088">
+        <v>3</v>
+      </c>
+      <c r="N2088">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:14" ht="15" customHeight="1">
+      <c r="A2089" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2089" t="s">
+        <v>792</v>
+      </c>
+      <c r="C2089" t="s">
+        <v>956</v>
+      </c>
+      <c r="D2089">
+        <v>321</v>
+      </c>
+      <c r="E2089">
+        <v>46</v>
+      </c>
+      <c r="F2089">
+        <v>73.17</v>
+      </c>
+      <c r="G2089">
+        <v>58.62</v>
+      </c>
+      <c r="H2089">
+        <v>78</v>
+      </c>
+      <c r="I2089">
+        <v>65.45</v>
+      </c>
+      <c r="J2089" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2089" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2089">
+        <v>4</v>
+      </c>
+      <c r="M2089">
+        <v>2</v>
+      </c>
+      <c r="N2089">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:14" ht="15" customHeight="1">
+      <c r="A2090" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2090" t="s">
+        <v>864</v>
+      </c>
+      <c r="C2090" t="s">
+        <v>865</v>
+      </c>
+      <c r="D2090">
+        <v>316</v>
+      </c>
+      <c r="E2090">
+        <v>54</v>
+      </c>
+      <c r="F2090">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2090">
+        <v>53.45</v>
+      </c>
+      <c r="H2090">
+        <v>76</v>
+      </c>
+      <c r="I2090">
+        <v>72.73</v>
+      </c>
+      <c r="J2090" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2090" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2090">
+        <v>3</v>
+      </c>
+      <c r="M2090">
+        <v>3</v>
+      </c>
+      <c r="N2090">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:14" ht="15" customHeight="1">
+      <c r="A2091" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2091" t="s">
+        <v>766</v>
+      </c>
+      <c r="C2091" t="s">
+        <v>767</v>
+      </c>
+      <c r="D2091">
+        <v>357</v>
+      </c>
+      <c r="E2091">
+        <v>58</v>
+      </c>
+      <c r="F2091">
+        <v>87.8</v>
+      </c>
+      <c r="G2091">
+        <v>56.9</v>
+      </c>
+      <c r="H2091">
+        <v>84</v>
+      </c>
+      <c r="I2091">
+        <v>67.27</v>
+      </c>
+      <c r="J2091" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2091" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2091">
+        <v>4</v>
+      </c>
+      <c r="M2091">
+        <v>3</v>
+      </c>
+      <c r="N2091">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:14" ht="15" customHeight="1">
+      <c r="A2092" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2092" t="s">
+        <v>636</v>
+      </c>
+      <c r="C2092" t="s">
+        <v>637</v>
+      </c>
+      <c r="D2092">
+        <v>338</v>
+      </c>
+      <c r="E2092">
+        <v>56</v>
+      </c>
+      <c r="F2092">
+        <v>87.8</v>
+      </c>
+      <c r="G2092">
+        <v>46.55</v>
+      </c>
+      <c r="H2092">
+        <v>76</v>
+      </c>
+      <c r="I2092">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2092" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2092" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2092">
+        <v>4</v>
+      </c>
+      <c r="M2092">
+        <v>3</v>
+      </c>
+      <c r="N2092">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:14" ht="15" customHeight="1">
+      <c r="A2093" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2093" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C2093" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D2093">
+        <v>185</v>
+      </c>
+      <c r="E2093">
+        <v>34</v>
+      </c>
+      <c r="F2093">
+        <v>63.41</v>
+      </c>
+      <c r="G2093">
+        <v>22.41</v>
+      </c>
+      <c r="H2093">
+        <v>40</v>
+      </c>
+      <c r="I2093">
+        <v>0</v>
+      </c>
+      <c r="J2093" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2093" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2093">
+        <v>3</v>
+      </c>
+      <c r="M2093">
+        <v>1</v>
+      </c>
+      <c r="N2093">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:14" ht="15" customHeight="1">
+      <c r="A2094" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2094" t="s">
+        <v>784</v>
+      </c>
+      <c r="C2094" t="s">
+        <v>959</v>
+      </c>
+      <c r="D2094">
+        <v>192</v>
+      </c>
+      <c r="E2094">
+        <v>32</v>
+      </c>
+      <c r="F2094">
+        <v>73.17</v>
+      </c>
+      <c r="G2094">
+        <v>20.69</v>
+      </c>
+      <c r="H2094">
+        <v>40</v>
+      </c>
+      <c r="I2094">
+        <v>0</v>
+      </c>
+      <c r="J2094" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2094" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2094">
+        <v>4</v>
+      </c>
+      <c r="M2094">
+        <v>1</v>
+      </c>
+      <c r="N2094">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:14" ht="15" customHeight="1">
+      <c r="A2095" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2095" t="s">
+        <v>763</v>
+      </c>
+      <c r="C2095" t="s">
+        <v>960</v>
+      </c>
+      <c r="D2095">
+        <v>279</v>
+      </c>
+      <c r="E2095">
+        <v>58</v>
+      </c>
+      <c r="F2095">
+        <v>70.73</v>
+      </c>
+      <c r="G2095">
+        <v>13.79</v>
+      </c>
+      <c r="H2095">
+        <v>70</v>
+      </c>
+      <c r="I2095">
+        <v>85.45</v>
+      </c>
+      <c r="J2095" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2095" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2095">
+        <v>4</v>
+      </c>
+      <c r="M2095">
+        <v>3</v>
+      </c>
+      <c r="N2095">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:14" ht="15" customHeight="1">
+      <c r="A2096" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2096" t="s">
+        <v>769</v>
+      </c>
+      <c r="C2096" t="s">
+        <v>961</v>
+      </c>
+      <c r="D2096">
+        <v>333</v>
+      </c>
+      <c r="E2096">
+        <v>62</v>
+      </c>
+      <c r="F2096">
+        <v>75.61</v>
+      </c>
+      <c r="G2096">
+        <v>53.45</v>
+      </c>
+      <c r="H2096">
+        <v>72</v>
+      </c>
+      <c r="I2096">
+        <v>74.55</v>
+      </c>
+      <c r="J2096" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2096" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2096">
+        <v>4</v>
+      </c>
+      <c r="M2096">
+        <v>3</v>
+      </c>
+      <c r="N2096">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:14" ht="15" customHeight="1">
+      <c r="A2097" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2097" t="s">
+        <v>764</v>
+      </c>
+      <c r="C2097" t="s">
+        <v>765</v>
+      </c>
+      <c r="D2097">
+        <v>171</v>
+      </c>
+      <c r="E2097">
+        <v>18</v>
+      </c>
+      <c r="F2097">
+        <v>73.17</v>
+      </c>
+      <c r="G2097">
+        <v>22.41</v>
+      </c>
+      <c r="H2097">
+        <v>34</v>
+      </c>
+      <c r="I2097">
+        <v>0</v>
+      </c>
+      <c r="J2097" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2097" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2097">
+        <v>4</v>
+      </c>
+      <c r="M2097">
+        <v>1</v>
+      </c>
+      <c r="N2097">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:14" ht="15" customHeight="1">
+      <c r="A2098" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2098" t="s">
+        <v>777</v>
+      </c>
+      <c r="C2098" t="s">
+        <v>778</v>
+      </c>
+      <c r="D2098">
+        <v>329</v>
+      </c>
+      <c r="E2098">
+        <v>60</v>
+      </c>
+      <c r="F2098">
+        <v>78.05</v>
+      </c>
+      <c r="G2098">
+        <v>53.45</v>
+      </c>
+      <c r="H2098">
+        <v>74</v>
+      </c>
+      <c r="I2098">
+        <v>56.36</v>
+      </c>
+      <c r="J2098" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2098" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2098">
+        <v>4</v>
+      </c>
+      <c r="M2098">
+        <v>3</v>
+      </c>
+      <c r="N2098">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:14" ht="15" customHeight="1">
+      <c r="A2099" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2099" t="s">
+        <v>762</v>
+      </c>
+      <c r="C2099" t="s">
+        <v>962</v>
+      </c>
+      <c r="D2099">
+        <v>358</v>
+      </c>
+      <c r="E2099">
+        <v>50</v>
+      </c>
+      <c r="F2099">
+        <v>87.8</v>
+      </c>
+      <c r="G2099">
+        <v>67.239999999999995</v>
+      </c>
+      <c r="H2099">
+        <v>80</v>
+      </c>
+      <c r="I2099">
+        <v>74.55</v>
+      </c>
+      <c r="J2099" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2099" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2099">
+        <v>4</v>
+      </c>
+      <c r="M2099">
+        <v>2</v>
+      </c>
+      <c r="N2099">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:14" ht="15" customHeight="1">
+      <c r="A2100" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2100" t="s">
+        <v>785</v>
+      </c>
+      <c r="C2100" t="s">
+        <v>786</v>
+      </c>
+      <c r="D2100">
+        <v>141</v>
+      </c>
+      <c r="E2100">
+        <v>34</v>
+      </c>
+      <c r="F2100">
+        <v>0</v>
+      </c>
+      <c r="G2100">
+        <v>29.31</v>
+      </c>
+      <c r="H2100">
+        <v>38</v>
+      </c>
+      <c r="I2100">
+        <v>61.82</v>
+      </c>
+      <c r="J2100" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2100" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2100">
+        <v>1</v>
+      </c>
+      <c r="M2100">
+        <v>1</v>
+      </c>
+      <c r="N2100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:14" ht="15" customHeight="1">
+      <c r="A2101" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2101" t="s">
+        <v>652</v>
+      </c>
+      <c r="C2101" t="s">
+        <v>653</v>
+      </c>
+      <c r="D2101">
+        <v>70</v>
+      </c>
+      <c r="E2101">
+        <v>16</v>
+      </c>
+      <c r="F2101">
+        <v>0</v>
+      </c>
+      <c r="G2101">
+        <v>12.07</v>
+      </c>
+      <c r="H2101">
+        <v>22</v>
+      </c>
+      <c r="I2101">
+        <v>30.91</v>
+      </c>
+      <c r="J2101" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2101" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2101">
+        <v>1</v>
+      </c>
+      <c r="M2101">
+        <v>1</v>
+      </c>
+      <c r="N2101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:14" ht="15" customHeight="1">
+      <c r="A2102" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2102" t="s">
+        <v>798</v>
+      </c>
+      <c r="C2102" t="s">
+        <v>799</v>
+      </c>
+      <c r="D2102">
+        <v>285</v>
+      </c>
+      <c r="E2102">
+        <v>46</v>
+      </c>
+      <c r="F2102">
+        <v>70.73</v>
+      </c>
+      <c r="G2102">
+        <v>51.72</v>
+      </c>
+      <c r="H2102">
+        <v>62</v>
+      </c>
+      <c r="I2102">
+        <v>49.09</v>
+      </c>
+      <c r="J2102" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2102" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2102">
+        <v>4</v>
+      </c>
+      <c r="M2102">
+        <v>2</v>
+      </c>
+      <c r="N2102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:14" ht="15" customHeight="1">
+      <c r="A2103" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2103" t="s">
+        <v>776</v>
+      </c>
+      <c r="C2103" t="s">
+        <v>965</v>
+      </c>
+      <c r="D2103">
+        <v>262</v>
+      </c>
+      <c r="E2103">
+        <v>52</v>
+      </c>
+      <c r="F2103">
+        <v>60.98</v>
+      </c>
+      <c r="G2103">
+        <v>43.1</v>
+      </c>
+      <c r="H2103">
+        <v>60</v>
+      </c>
+      <c r="I2103">
+        <v>30.91</v>
+      </c>
+      <c r="J2103" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2103" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2103">
+        <v>3</v>
+      </c>
+      <c r="M2103">
+        <v>3</v>
+      </c>
+      <c r="N2103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:14" ht="15" customHeight="1">
+      <c r="A2104" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2104" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C2104" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D2104">
+        <v>180</v>
+      </c>
+      <c r="E2104">
+        <v>34</v>
+      </c>
+      <c r="F2104">
+        <v>60.98</v>
+      </c>
+      <c r="G2104">
+        <v>22.41</v>
+      </c>
+      <c r="H2104">
+        <v>38</v>
+      </c>
+      <c r="I2104">
+        <v>0</v>
+      </c>
+      <c r="J2104" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2104" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2104">
+        <v>3</v>
+      </c>
+      <c r="M2104">
+        <v>1</v>
+      </c>
+      <c r="N2104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:14" ht="15" customHeight="1">
+      <c r="A2105" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2105" t="s">
+        <v>783</v>
+      </c>
+      <c r="C2105" t="s">
+        <v>967</v>
+      </c>
+      <c r="D2105">
+        <v>285</v>
+      </c>
+      <c r="E2105">
+        <v>44</v>
+      </c>
+      <c r="F2105">
+        <v>73.17</v>
+      </c>
+      <c r="G2105">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H2105">
+        <v>70</v>
+      </c>
+      <c r="I2105">
+        <v>74.55</v>
+      </c>
+      <c r="J2105" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2105" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2105">
+        <v>4</v>
+      </c>
+      <c r="M2105">
+        <v>2</v>
+      </c>
+      <c r="N2105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:14" ht="15" customHeight="1">
+      <c r="A2106" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2106" t="s">
+        <v>768</v>
+      </c>
+      <c r="C2106" t="s">
+        <v>970</v>
+      </c>
+      <c r="D2106">
+        <v>302</v>
+      </c>
+      <c r="E2106">
+        <v>50</v>
+      </c>
+      <c r="F2106">
+        <v>73.17</v>
+      </c>
+      <c r="G2106">
+        <v>51.72</v>
+      </c>
+      <c r="H2106">
+        <v>64</v>
+      </c>
+      <c r="I2106">
+        <v>67.27</v>
+      </c>
+      <c r="J2106" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2106" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2106">
+        <v>4</v>
+      </c>
+      <c r="M2106">
+        <v>2</v>
+      </c>
+      <c r="N2106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:14" ht="15" customHeight="1">
+      <c r="A2107" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2107" t="s">
+        <v>779</v>
+      </c>
+      <c r="C2107" t="s">
+        <v>972</v>
+      </c>
+      <c r="D2107">
+        <v>260</v>
+      </c>
+      <c r="E2107">
+        <v>38</v>
+      </c>
+      <c r="F2107">
+        <v>60.98</v>
+      </c>
+      <c r="G2107">
+        <v>37.93</v>
+      </c>
+      <c r="H2107">
+        <v>72</v>
+      </c>
+      <c r="I2107">
+        <v>47.27</v>
+      </c>
+      <c r="J2107" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2107" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2107">
+        <v>3</v>
+      </c>
+      <c r="M2107">
+        <v>2</v>
+      </c>
+      <c r="N2107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:14" ht="15" customHeight="1">
+      <c r="A2108" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2108" t="s">
+        <v>787</v>
+      </c>
+      <c r="C2108" t="s">
+        <v>788</v>
+      </c>
+      <c r="D2108">
+        <v>81</v>
+      </c>
+      <c r="E2108">
+        <v>16</v>
+      </c>
+      <c r="F2108">
+        <v>0</v>
+      </c>
+      <c r="G2108">
+        <v>13.79</v>
+      </c>
+      <c r="H2108">
+        <v>28</v>
+      </c>
+      <c r="I2108">
+        <v>36.36</v>
+      </c>
+      <c r="J2108" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2108" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2108">
+        <v>1</v>
+      </c>
+      <c r="M2108">
+        <v>1</v>
+      </c>
+      <c r="N2108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:14" ht="15" customHeight="1">
+      <c r="A2109" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>760</v>
+      </c>
+      <c r="C2109" t="s">
+        <v>761</v>
+      </c>
+      <c r="D2109">
+        <v>182</v>
+      </c>
+      <c r="E2109">
+        <v>36</v>
+      </c>
+      <c r="F2109">
+        <v>0</v>
+      </c>
+      <c r="G2109">
+        <v>43.1</v>
+      </c>
+      <c r="H2109">
+        <v>46</v>
+      </c>
+      <c r="I2109">
+        <v>96.36</v>
+      </c>
+      <c r="J2109" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2109" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2109">
+        <v>1</v>
+      </c>
+      <c r="M2109">
+        <v>2</v>
+      </c>
+      <c r="N2109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:14" ht="15" customHeight="1">
+      <c r="A2110" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>795</v>
+      </c>
+      <c r="C2110" t="s">
+        <v>973</v>
+      </c>
+      <c r="D2110">
+        <v>257</v>
+      </c>
+      <c r="E2110">
+        <v>28</v>
+      </c>
+      <c r="F2110">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2110">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H2110">
+        <v>60</v>
+      </c>
+      <c r="I2110">
+        <v>41.82</v>
+      </c>
+      <c r="J2110" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2110" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2110">
+        <v>4</v>
+      </c>
+      <c r="M2110">
+        <v>1</v>
+      </c>
+      <c r="N2110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:14" ht="15" customHeight="1">
+      <c r="A2111" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>823</v>
+      </c>
+      <c r="C2111" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D2111">
+        <v>203</v>
+      </c>
+      <c r="E2111">
+        <v>36</v>
+      </c>
+      <c r="F2111">
+        <v>48.78</v>
+      </c>
+      <c r="G2111">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H2111">
+        <v>42</v>
+      </c>
+      <c r="I2111">
+        <v>43.64</v>
+      </c>
+      <c r="J2111" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2111" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2111">
+        <v>2</v>
+      </c>
+      <c r="M2111">
+        <v>2</v>
+      </c>
+      <c r="N2111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:14" ht="15" customHeight="1">
+      <c r="A2112" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>603</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>604</v>
+      </c>
+      <c r="D2112">
+        <v>84</v>
+      </c>
+      <c r="E2112">
+        <v>20</v>
+      </c>
+      <c r="F2112">
+        <v>0</v>
+      </c>
+      <c r="G2112">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="H2112">
+        <v>32</v>
+      </c>
+      <c r="I2112">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2112" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2112" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2112">
+        <v>1</v>
+      </c>
+      <c r="M2112">
+        <v>1</v>
+      </c>
+      <c r="N2112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:14" ht="15" customHeight="1">
+      <c r="A2113" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>782</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>974</v>
+      </c>
+      <c r="D2113">
+        <v>232</v>
+      </c>
+      <c r="E2113">
+        <v>32</v>
+      </c>
+      <c r="F2113">
+        <v>75.61</v>
+      </c>
+      <c r="G2113">
+        <v>29.31</v>
+      </c>
+      <c r="H2113">
+        <v>50</v>
+      </c>
+      <c r="I2113">
+        <v>41.82</v>
+      </c>
+      <c r="J2113" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2113" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2113">
+        <v>4</v>
+      </c>
+      <c r="M2113">
+        <v>1</v>
+      </c>
+      <c r="N2113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:14" ht="15" customHeight="1">
+      <c r="A2114" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>975</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>976</v>
+      </c>
+      <c r="D2114">
+        <v>271</v>
+      </c>
+      <c r="E2114">
+        <v>44</v>
+      </c>
+      <c r="F2114">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2114">
+        <v>46.55</v>
+      </c>
+      <c r="H2114">
+        <v>68</v>
+      </c>
+      <c r="I2114">
+        <v>30.91</v>
+      </c>
+      <c r="J2114" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2114" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2114">
+        <v>3</v>
+      </c>
+      <c r="M2114">
+        <v>2</v>
+      </c>
+      <c r="N2114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:14" ht="15" customHeight="1">
+      <c r="A2115" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D2115">
+        <v>99</v>
+      </c>
+      <c r="E2115">
+        <v>16</v>
+      </c>
+      <c r="F2115">
+        <v>0</v>
+      </c>
+      <c r="G2115">
+        <v>22.41</v>
+      </c>
+      <c r="H2115">
+        <v>36</v>
+      </c>
+      <c r="I2115">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2115" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2115" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2115">
+        <v>1</v>
+      </c>
+      <c r="M2115">
+        <v>1</v>
+      </c>
+      <c r="N2115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:14" ht="15" customHeight="1">
+      <c r="A2116" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>796</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>797</v>
+      </c>
+      <c r="D2116">
+        <v>267</v>
+      </c>
+      <c r="E2116">
+        <v>38</v>
+      </c>
+      <c r="F2116">
+        <v>75.61</v>
+      </c>
+      <c r="G2116">
+        <v>37.93</v>
+      </c>
+      <c r="H2116">
+        <v>64</v>
+      </c>
+      <c r="I2116">
+        <v>45.45</v>
+      </c>
+      <c r="J2116" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2116" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2116">
+        <v>4</v>
+      </c>
+      <c r="M2116">
+        <v>2</v>
+      </c>
+      <c r="N2116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:14" ht="15" customHeight="1">
+      <c r="A2117" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>977</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>978</v>
+      </c>
+      <c r="D2117">
+        <v>167</v>
+      </c>
+      <c r="E2117">
+        <v>18</v>
+      </c>
+      <c r="F2117">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2117">
+        <v>12.07</v>
+      </c>
+      <c r="H2117">
+        <v>46</v>
+      </c>
+      <c r="I2117">
+        <v>0</v>
+      </c>
+      <c r="J2117" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2117" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2117">
+        <v>4</v>
+      </c>
+      <c r="M2117">
+        <v>1</v>
+      </c>
+      <c r="N2117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:14" ht="15" customHeight="1">
+      <c r="A2118" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>772</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>979</v>
+      </c>
+      <c r="D2118">
+        <v>269</v>
+      </c>
+      <c r="E2118">
+        <v>32</v>
+      </c>
+      <c r="F2118">
+        <v>70.73</v>
+      </c>
+      <c r="G2118">
+        <v>46.55</v>
+      </c>
+      <c r="H2118">
+        <v>74</v>
+      </c>
+      <c r="I2118">
+        <v>27.27</v>
+      </c>
+      <c r="J2118" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2118" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2118">
+        <v>4</v>
+      </c>
+      <c r="M2118">
+        <v>1</v>
+      </c>
+      <c r="N2118">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:14" ht="15" customHeight="1">
+      <c r="A2119" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>756</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>981</v>
+      </c>
+      <c r="D2119">
+        <v>347</v>
+      </c>
+      <c r="E2119">
+        <v>52</v>
+      </c>
+      <c r="F2119">
+        <v>85.37</v>
+      </c>
+      <c r="G2119">
+        <v>63.79</v>
+      </c>
+      <c r="H2119">
+        <v>78</v>
+      </c>
+      <c r="I2119">
+        <v>63.64</v>
+      </c>
+      <c r="J2119" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2119" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2119">
+        <v>4</v>
+      </c>
+      <c r="M2119">
+        <v>3</v>
+      </c>
+      <c r="N2119">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:14" ht="15" customHeight="1">
+      <c r="A2120" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>770</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>982</v>
+      </c>
+      <c r="D2120">
+        <v>359</v>
+      </c>
+      <c r="E2120">
+        <v>66</v>
+      </c>
+      <c r="F2120">
+        <v>85.37</v>
+      </c>
+      <c r="G2120">
+        <v>58.62</v>
+      </c>
+      <c r="H2120">
+        <v>78</v>
+      </c>
+      <c r="I2120">
+        <v>67.27</v>
+      </c>
+      <c r="J2120" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2120" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2120">
+        <v>4</v>
+      </c>
+      <c r="M2120">
+        <v>3</v>
+      </c>
+      <c r="N2120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:14" ht="15" customHeight="1">
+      <c r="A2121" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>771</v>
+      </c>
+      <c r="C2121" t="s">
+        <v>983</v>
+      </c>
+      <c r="D2121">
+        <v>296</v>
+      </c>
+      <c r="E2121">
+        <v>58</v>
+      </c>
+      <c r="F2121">
+        <v>87.8</v>
+      </c>
+      <c r="G2121">
+        <v>27.59</v>
+      </c>
+      <c r="H2121">
+        <v>68</v>
+      </c>
+      <c r="I2121">
+        <v>43.64</v>
+      </c>
+      <c r="J2121" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2121" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2121">
+        <v>4</v>
+      </c>
+      <c r="M2121">
+        <v>3</v>
+      </c>
+      <c r="N2121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:14" ht="15" customHeight="1">
+      <c r="A2122" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>754</v>
+      </c>
+      <c r="C2122" t="s">
+        <v>755</v>
+      </c>
+      <c r="D2122">
+        <v>372</v>
+      </c>
+      <c r="E2122">
+        <v>66</v>
+      </c>
+      <c r="F2122">
+        <v>95.12</v>
+      </c>
+      <c r="G2122">
+        <v>60.34</v>
+      </c>
+      <c r="H2122">
+        <v>88</v>
+      </c>
+      <c r="I2122">
+        <v>36.36</v>
+      </c>
+      <c r="J2122" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2122" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2122">
+        <v>4</v>
+      </c>
+      <c r="M2122">
+        <v>3</v>
+      </c>
+      <c r="N2122">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:14" ht="15" customHeight="1">
+      <c r="A2123" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C2123" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D2123">
+        <v>49</v>
+      </c>
+      <c r="E2123">
+        <v>10</v>
+      </c>
+      <c r="F2123">
+        <v>0</v>
+      </c>
+      <c r="G2123">
+        <v>13.79</v>
+      </c>
+      <c r="H2123">
+        <v>10</v>
+      </c>
+      <c r="I2123">
+        <v>23.64</v>
+      </c>
+      <c r="J2123" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2123" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2123">
+        <v>1</v>
+      </c>
+      <c r="M2123">
+        <v>1</v>
+      </c>
+      <c r="N2123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:14" ht="15" customHeight="1">
+      <c r="A2124" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>781</v>
+      </c>
+      <c r="C2124" t="s">
+        <v>984</v>
+      </c>
+      <c r="D2124">
+        <v>309</v>
+      </c>
+      <c r="E2124">
+        <v>48</v>
+      </c>
+      <c r="F2124">
+        <v>82.93</v>
+      </c>
+      <c r="G2124">
+        <v>51.72</v>
+      </c>
+      <c r="H2124">
+        <v>68</v>
+      </c>
+      <c r="I2124">
+        <v>49.09</v>
+      </c>
+      <c r="J2124" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2124" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2124">
+        <v>4</v>
+      </c>
+      <c r="M2124">
+        <v>2</v>
+      </c>
+      <c r="N2124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:14" ht="15" customHeight="1">
+      <c r="A2125" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>817</v>
+      </c>
+      <c r="C2125" t="s">
+        <v>987</v>
+      </c>
+      <c r="D2125">
+        <v>298</v>
+      </c>
+      <c r="E2125">
+        <v>36</v>
+      </c>
+      <c r="F2125">
+        <v>82.93</v>
+      </c>
+      <c r="G2125">
+        <v>43.1</v>
+      </c>
+      <c r="H2125">
+        <v>78</v>
+      </c>
+      <c r="I2125">
+        <v>52.73</v>
+      </c>
+      <c r="J2125" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2125" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2125">
+        <v>4</v>
+      </c>
+      <c r="M2125">
+        <v>2</v>
+      </c>
+      <c r="N2125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:14" ht="15" customHeight="1">
+      <c r="A2126" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>804</v>
+      </c>
+      <c r="C2126" t="s">
+        <v>805</v>
+      </c>
+      <c r="D2126">
+        <v>297</v>
+      </c>
+      <c r="E2126">
+        <v>34</v>
+      </c>
+      <c r="F2126">
+        <v>70.73</v>
+      </c>
+      <c r="G2126">
+        <v>70.69</v>
+      </c>
+      <c r="H2126">
+        <v>66</v>
+      </c>
+      <c r="I2126">
+        <v>45.45</v>
+      </c>
+      <c r="J2126" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2126" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2126">
+        <v>4</v>
+      </c>
+      <c r="M2126">
+        <v>1</v>
+      </c>
+      <c r="N2126">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:14" ht="15" customHeight="1">
+      <c r="A2127" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2127" t="s">
+        <v>812</v>
+      </c>
+      <c r="C2127" t="s">
+        <v>989</v>
+      </c>
+      <c r="D2127">
+        <v>385</v>
+      </c>
+      <c r="E2127">
+        <v>60</v>
+      </c>
+      <c r="F2127">
+        <v>85.37</v>
+      </c>
+      <c r="G2127">
+        <v>68.97</v>
+      </c>
+      <c r="H2127">
+        <v>86</v>
+      </c>
+      <c r="I2127">
+        <v>98.18</v>
+      </c>
+      <c r="J2127" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2127" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2127">
+        <v>4</v>
+      </c>
+      <c r="M2127">
+        <v>3</v>
+      </c>
+      <c r="N2127">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:14" ht="15" customHeight="1">
+      <c r="A2128" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2128" t="s">
+        <v>824</v>
+      </c>
+      <c r="C2128" t="s">
+        <v>990</v>
+      </c>
+      <c r="D2128">
+        <v>307</v>
+      </c>
+      <c r="E2128">
+        <v>58</v>
+      </c>
+      <c r="F2128">
+        <v>78.05</v>
+      </c>
+      <c r="G2128">
+        <v>58.62</v>
+      </c>
+      <c r="H2128">
+        <v>60</v>
+      </c>
+      <c r="I2128">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2128" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2128" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2128">
+        <v>4</v>
+      </c>
+      <c r="M2128">
+        <v>3</v>
+      </c>
+      <c r="N2128">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:14" ht="15" customHeight="1">
+      <c r="A2129" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2129" t="s">
+        <v>832</v>
+      </c>
+      <c r="C2129" t="s">
+        <v>833</v>
+      </c>
+      <c r="D2129">
+        <v>391</v>
+      </c>
+      <c r="E2129">
+        <v>64</v>
+      </c>
+      <c r="F2129">
+        <v>87.8</v>
+      </c>
+      <c r="G2129">
+        <v>75.86</v>
+      </c>
+      <c r="H2129">
+        <v>82</v>
+      </c>
+      <c r="I2129">
+        <v>87.27</v>
+      </c>
+      <c r="J2129" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2129" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2129">
+        <v>4</v>
+      </c>
+      <c r="M2129">
+        <v>3</v>
+      </c>
+      <c r="N2129">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:14" ht="15" customHeight="1">
+      <c r="A2130" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2130" t="s">
+        <v>843</v>
+      </c>
+      <c r="C2130" t="s">
+        <v>991</v>
+      </c>
+      <c r="D2130">
+        <v>157</v>
+      </c>
+      <c r="E2130">
+        <v>34</v>
+      </c>
+      <c r="F2130">
+        <v>0</v>
+      </c>
+      <c r="G2130">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H2130">
+        <v>38</v>
+      </c>
+      <c r="I2130">
+        <v>87.27</v>
+      </c>
+      <c r="J2130" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2130" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2130">
+        <v>1</v>
+      </c>
+      <c r="M2130">
+        <v>1</v>
+      </c>
+      <c r="N2130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:14" ht="15" customHeight="1">
+      <c r="A2131" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2131" t="s">
+        <v>806</v>
+      </c>
+      <c r="C2131" t="s">
+        <v>807</v>
+      </c>
+      <c r="D2131">
+        <v>391</v>
+      </c>
+      <c r="E2131">
+        <v>58</v>
+      </c>
+      <c r="F2131">
+        <v>87.8</v>
+      </c>
+      <c r="G2131">
+        <v>74.14</v>
+      </c>
+      <c r="H2131">
+        <v>92</v>
+      </c>
+      <c r="I2131">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2131" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2131" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2131">
+        <v>4</v>
+      </c>
+      <c r="M2131">
+        <v>3</v>
+      </c>
+      <c r="N2131">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:14" ht="15" customHeight="1">
+      <c r="A2132" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2132" t="s">
+        <v>838</v>
+      </c>
+      <c r="C2132" t="s">
+        <v>992</v>
+      </c>
+      <c r="D2132">
+        <v>203</v>
+      </c>
+      <c r="E2132">
+        <v>32</v>
+      </c>
+      <c r="F2132">
+        <v>78.05</v>
+      </c>
+      <c r="G2132">
+        <v>29.31</v>
+      </c>
+      <c r="H2132">
+        <v>36</v>
+      </c>
+      <c r="I2132">
+        <v>0</v>
+      </c>
+      <c r="J2132" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2132" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2132">
+        <v>4</v>
+      </c>
+      <c r="M2132">
+        <v>1</v>
+      </c>
+      <c r="N2132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:14" ht="15" customHeight="1">
+      <c r="A2133" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2133" t="s">
+        <v>803</v>
+      </c>
+      <c r="C2133" t="s">
+        <v>993</v>
+      </c>
+      <c r="D2133">
+        <v>380</v>
+      </c>
+      <c r="E2133">
+        <v>64</v>
+      </c>
+      <c r="F2133">
+        <v>87.8</v>
+      </c>
+      <c r="G2133">
+        <v>67.239999999999995</v>
+      </c>
+      <c r="H2133">
+        <v>80</v>
+      </c>
+      <c r="I2133">
+        <v>89.09</v>
+      </c>
+      <c r="J2133" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2133" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2133">
+        <v>4</v>
+      </c>
+      <c r="M2133">
+        <v>3</v>
+      </c>
+      <c r="N2133">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:14" ht="15" customHeight="1">
+      <c r="A2134" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2134" t="s">
+        <v>995</v>
+      </c>
+      <c r="C2134" t="s">
+        <v>996</v>
+      </c>
+      <c r="D2134">
+        <v>245</v>
+      </c>
+      <c r="E2134">
+        <v>28</v>
+      </c>
+      <c r="F2134">
+        <v>73.17</v>
+      </c>
+      <c r="G2134">
+        <v>31.03</v>
+      </c>
+      <c r="H2134">
+        <v>60</v>
+      </c>
+      <c r="I2134">
+        <v>58.18</v>
+      </c>
+      <c r="J2134" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2134" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2134">
+        <v>4</v>
+      </c>
+      <c r="M2134">
+        <v>1</v>
+      </c>
+      <c r="N2134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:14" ht="15" customHeight="1">
+      <c r="A2135" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2135" t="s">
+        <v>826</v>
+      </c>
+      <c r="C2135" t="s">
+        <v>997</v>
+      </c>
+      <c r="D2135">
+        <v>315</v>
+      </c>
+      <c r="E2135">
+        <v>54</v>
+      </c>
+      <c r="F2135">
+        <v>78.05</v>
+      </c>
+      <c r="G2135">
+        <v>43.1</v>
+      </c>
+      <c r="H2135">
+        <v>74</v>
+      </c>
+      <c r="I2135">
+        <v>69.09</v>
+      </c>
+      <c r="J2135" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2135" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2135">
+        <v>4</v>
+      </c>
+      <c r="M2135">
+        <v>3</v>
+      </c>
+      <c r="N2135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:14" ht="15" customHeight="1">
+      <c r="A2136" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2136" t="s">
+        <v>813</v>
+      </c>
+      <c r="C2136" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D2136">
+        <v>414</v>
+      </c>
+      <c r="E2136">
+        <v>72</v>
+      </c>
+      <c r="F2136">
+        <v>85.37</v>
+      </c>
+      <c r="G2136">
+        <v>84.48</v>
+      </c>
+      <c r="H2136">
+        <v>86</v>
+      </c>
+      <c r="I2136">
+        <v>90.91</v>
+      </c>
+      <c r="J2136" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2136" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2136">
+        <v>4</v>
+      </c>
+      <c r="M2136">
+        <v>4</v>
+      </c>
+      <c r="N2136">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:14" ht="15" customHeight="1">
+      <c r="A2137" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2137" t="s">
+        <v>872</v>
+      </c>
+      <c r="C2137" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D2137">
+        <v>197</v>
+      </c>
+      <c r="E2137">
+        <v>36</v>
+      </c>
+      <c r="F2137">
+        <v>46.34</v>
+      </c>
+      <c r="G2137">
+        <v>36.21</v>
+      </c>
+      <c r="H2137">
+        <v>38</v>
+      </c>
+      <c r="I2137">
+        <v>41.82</v>
+      </c>
+      <c r="J2137" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2137" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2137">
+        <v>2</v>
+      </c>
+      <c r="M2137">
+        <v>2</v>
+      </c>
+      <c r="N2137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:14" ht="15" customHeight="1">
+      <c r="A2138" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2138" t="s">
+        <v>808</v>
+      </c>
+      <c r="C2138" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D2138">
+        <v>337</v>
+      </c>
+      <c r="E2138">
+        <v>40</v>
+      </c>
+      <c r="F2138">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2138">
+        <v>74.14</v>
+      </c>
+      <c r="H2138">
+        <v>78</v>
+      </c>
+      <c r="I2138">
+        <v>58.18</v>
+      </c>
+      <c r="J2138" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2138" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2138">
+        <v>4</v>
+      </c>
+      <c r="M2138">
+        <v>2</v>
+      </c>
+      <c r="N2138">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:14" ht="15" customHeight="1">
+      <c r="A2139" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2139" t="s">
+        <v>818</v>
+      </c>
+      <c r="C2139" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D2139">
+        <v>353</v>
+      </c>
+      <c r="E2139">
+        <v>40</v>
+      </c>
+      <c r="F2139">
+        <v>82.93</v>
+      </c>
+      <c r="G2139">
+        <v>70.69</v>
+      </c>
+      <c r="H2139">
+        <v>82</v>
+      </c>
+      <c r="I2139">
+        <v>89.09</v>
+      </c>
+      <c r="J2139" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2139" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2139">
+        <v>4</v>
+      </c>
+      <c r="M2139">
+        <v>2</v>
+      </c>
+      <c r="N2139">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:14" ht="15" customHeight="1">
+      <c r="A2140" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2140" t="s">
+        <v>809</v>
+      </c>
+      <c r="C2140" t="s">
+        <v>810</v>
+      </c>
+      <c r="D2140">
+        <v>378</v>
+      </c>
+      <c r="E2140">
+        <v>66</v>
+      </c>
+      <c r="F2140">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2140">
+        <v>70.69</v>
+      </c>
+      <c r="H2140">
+        <v>80</v>
+      </c>
+      <c r="I2140">
+        <v>89.09</v>
+      </c>
+      <c r="J2140" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2140" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2140">
+        <v>4</v>
+      </c>
+      <c r="M2140">
+        <v>3</v>
+      </c>
+      <c r="N2140">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:14" ht="15" customHeight="1">
+      <c r="A2141" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2141" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C2141" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D2141">
+        <v>386</v>
+      </c>
+      <c r="E2141">
+        <v>70</v>
+      </c>
+      <c r="F2141">
+        <v>82.93</v>
+      </c>
+      <c r="G2141">
+        <v>72.41</v>
+      </c>
+      <c r="H2141">
+        <v>80</v>
+      </c>
+      <c r="I2141">
+        <v>87.27</v>
+      </c>
+      <c r="J2141" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2141" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2141">
+        <v>4</v>
+      </c>
+      <c r="M2141">
+        <v>3</v>
+      </c>
+      <c r="N2141">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:14" ht="15" customHeight="1">
+      <c r="A2142" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2142" t="s">
+        <v>834</v>
+      </c>
+      <c r="C2142" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D2142">
+        <v>410</v>
+      </c>
+      <c r="E2142">
+        <v>72</v>
+      </c>
+      <c r="F2142">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2142">
+        <v>84.48</v>
+      </c>
+      <c r="H2142">
+        <v>88</v>
+      </c>
+      <c r="I2142">
+        <v>89.09</v>
+      </c>
+      <c r="J2142" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2142" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2142">
+        <v>4</v>
+      </c>
+      <c r="M2142">
+        <v>4</v>
+      </c>
+      <c r="N2142">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:14" ht="15" customHeight="1">
+      <c r="A2143" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2143" t="s">
+        <v>837</v>
+      </c>
+      <c r="C2143" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D2143">
+        <v>265</v>
+      </c>
+      <c r="E2143">
+        <v>30</v>
+      </c>
+      <c r="F2143">
+        <v>73.17</v>
+      </c>
+      <c r="G2143">
+        <v>36.21</v>
+      </c>
+      <c r="H2143">
+        <v>68</v>
+      </c>
+      <c r="I2143">
+        <v>65.45</v>
+      </c>
+      <c r="J2143" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2143" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2143">
+        <v>4</v>
+      </c>
+      <c r="M2143">
+        <v>1</v>
+      </c>
+      <c r="N2143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:14" ht="15" customHeight="1">
+      <c r="A2144" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2144" t="s">
+        <v>815</v>
+      </c>
+      <c r="C2144" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D2144">
+        <v>365</v>
+      </c>
+      <c r="E2144">
+        <v>54</v>
+      </c>
+      <c r="F2144">
+        <v>87.8</v>
+      </c>
+      <c r="G2144">
+        <v>65.52</v>
+      </c>
+      <c r="H2144">
+        <v>80</v>
+      </c>
+      <c r="I2144">
+        <v>85.45</v>
+      </c>
+      <c r="J2144" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2144" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2144">
+        <v>4</v>
+      </c>
+      <c r="M2144">
+        <v>3</v>
+      </c>
+      <c r="N2144">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:14" ht="15" customHeight="1">
+      <c r="A2145" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2145" t="s">
+        <v>828</v>
+      </c>
+      <c r="C2145" t="s">
+        <v>829</v>
+      </c>
+      <c r="D2145">
+        <v>263</v>
+      </c>
+      <c r="E2145">
+        <v>62</v>
+      </c>
+      <c r="F2145">
+        <v>41.46</v>
+      </c>
+      <c r="G2145">
+        <v>44.83</v>
+      </c>
+      <c r="H2145">
+        <v>50</v>
+      </c>
+      <c r="I2145">
+        <v>87.27</v>
+      </c>
+      <c r="J2145" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2145" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2145">
+        <v>2</v>
+      </c>
+      <c r="M2145">
+        <v>3</v>
+      </c>
+      <c r="N2145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:14" ht="15" customHeight="1">
+      <c r="A2146" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2146" t="s">
+        <v>811</v>
+      </c>
+      <c r="C2146" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D2146">
+        <v>368</v>
+      </c>
+      <c r="E2146">
+        <v>46</v>
+      </c>
+      <c r="F2146">
+        <v>82.93</v>
+      </c>
+      <c r="G2146">
+        <v>75.86</v>
+      </c>
+      <c r="H2146">
+        <v>84</v>
+      </c>
+      <c r="I2146">
+        <v>89.09</v>
+      </c>
+      <c r="J2146" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2146" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2146">
+        <v>4</v>
+      </c>
+      <c r="M2146">
+        <v>2</v>
+      </c>
+      <c r="N2146">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:14" ht="15" customHeight="1">
+      <c r="A2147" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2147" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2147" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D2147">
+        <v>334</v>
+      </c>
+      <c r="E2147">
+        <v>52</v>
+      </c>
+      <c r="F2147">
+        <v>73.17</v>
+      </c>
+      <c r="G2147">
+        <v>60.34</v>
+      </c>
+      <c r="H2147">
+        <v>74</v>
+      </c>
+      <c r="I2147">
+        <v>89.09</v>
+      </c>
+      <c r="J2147" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2147" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2147">
+        <v>4</v>
+      </c>
+      <c r="M2147">
+        <v>3</v>
+      </c>
+      <c r="N2147">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:14" ht="15" customHeight="1">
+      <c r="A2148" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2148" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C2148" t="s">
+        <v>840</v>
+      </c>
+      <c r="D2148">
+        <v>252</v>
+      </c>
+      <c r="E2148">
+        <v>40</v>
+      </c>
+      <c r="F2148">
+        <v>78.05</v>
+      </c>
+      <c r="G2148">
+        <v>48.28</v>
+      </c>
+      <c r="H2148">
+        <v>22</v>
+      </c>
+      <c r="I2148">
+        <v>89.09</v>
+      </c>
+      <c r="J2148" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2148" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2148">
+        <v>4</v>
+      </c>
+      <c r="M2148">
+        <v>2</v>
+      </c>
+      <c r="N2148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:14" ht="15" customHeight="1">
+      <c r="A2149" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2149" t="s">
+        <v>821</v>
+      </c>
+      <c r="C2149" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D2149">
+        <v>388</v>
+      </c>
+      <c r="E2149">
+        <v>86</v>
+      </c>
+      <c r="F2149">
+        <v>85.37</v>
+      </c>
+      <c r="G2149">
+        <v>58.62</v>
+      </c>
+      <c r="H2149">
+        <v>78</v>
+      </c>
+      <c r="I2149">
+        <v>83.64</v>
+      </c>
+      <c r="J2149" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2149" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2149">
+        <v>4</v>
+      </c>
+      <c r="M2149">
+        <v>4</v>
+      </c>
+      <c r="N2149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:14" ht="15" customHeight="1">
+      <c r="A2150" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2150" t="s">
+        <v>879</v>
+      </c>
+      <c r="C2150" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D2150">
+        <v>239</v>
+      </c>
+      <c r="E2150">
+        <v>34</v>
+      </c>
+      <c r="F2150">
+        <v>73.17</v>
+      </c>
+      <c r="G2150">
+        <v>43.1</v>
+      </c>
+      <c r="H2150">
+        <v>50</v>
+      </c>
+      <c r="I2150">
+        <v>18.18</v>
+      </c>
+      <c r="J2150" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2150" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2150">
+        <v>4</v>
+      </c>
+      <c r="M2150">
+        <v>1</v>
+      </c>
+      <c r="N2150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:14" ht="15" customHeight="1">
+      <c r="A2151" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2151" t="s">
+        <v>877</v>
+      </c>
+      <c r="C2151" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D2151">
+        <v>333</v>
+      </c>
+      <c r="E2151">
+        <v>86</v>
+      </c>
+      <c r="F2151">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2151">
+        <v>51.72</v>
+      </c>
+      <c r="H2151">
+        <v>56</v>
+      </c>
+      <c r="I2151">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2151" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2151" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2151">
+        <v>4</v>
+      </c>
+      <c r="M2151">
+        <v>4</v>
+      </c>
+      <c r="N2151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:14" ht="15" customHeight="1">
+      <c r="A2152" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2152" t="s">
+        <v>878</v>
+      </c>
+      <c r="C2152" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D2152">
+        <v>352</v>
+      </c>
+      <c r="E2152">
+        <v>56</v>
+      </c>
+      <c r="F2152">
+        <v>87.8</v>
+      </c>
+      <c r="G2152">
+        <v>60.34</v>
+      </c>
+      <c r="H2152">
+        <v>76</v>
+      </c>
+      <c r="I2152">
+        <v>72.73</v>
+      </c>
+      <c r="J2152" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2152" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2152">
+        <v>4</v>
+      </c>
+      <c r="M2152">
+        <v>3</v>
+      </c>
+      <c r="N2152">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:14" ht="15" customHeight="1">
+      <c r="A2153" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2153" t="s">
+        <v>860</v>
+      </c>
+      <c r="C2153" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D2153">
+        <v>195</v>
+      </c>
+      <c r="E2153">
+        <v>34</v>
+      </c>
+      <c r="F2153">
+        <v>82.93</v>
+      </c>
+      <c r="G2153">
+        <v>13.79</v>
+      </c>
+      <c r="H2153">
+        <v>38</v>
+      </c>
+      <c r="I2153">
+        <v>0</v>
+      </c>
+      <c r="J2153" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2153" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2153">
+        <v>4</v>
+      </c>
+      <c r="M2153">
+        <v>1</v>
+      </c>
+      <c r="N2153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:14" ht="15" customHeight="1">
+      <c r="A2154" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2154" t="s">
+        <v>849</v>
+      </c>
+      <c r="C2154" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D2154">
+        <v>334</v>
+      </c>
+      <c r="E2154">
+        <v>52</v>
+      </c>
+      <c r="F2154">
+        <v>87.8</v>
+      </c>
+      <c r="G2154">
+        <v>60.34</v>
+      </c>
+      <c r="H2154">
+        <v>74</v>
+      </c>
+      <c r="I2154">
+        <v>45.45</v>
+      </c>
+      <c r="J2154" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2154" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2154">
+        <v>4</v>
+      </c>
+      <c r="M2154">
+        <v>3</v>
+      </c>
+      <c r="N2154">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:14" ht="15" customHeight="1">
+      <c r="A2155" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2155" t="s">
+        <v>853</v>
+      </c>
+      <c r="C2155" t="s">
+        <v>854</v>
+      </c>
+      <c r="D2155">
+        <v>329</v>
+      </c>
+      <c r="E2155">
+        <v>56</v>
+      </c>
+      <c r="F2155">
+        <v>73.17</v>
+      </c>
+      <c r="G2155">
+        <v>77.59</v>
+      </c>
+      <c r="H2155">
+        <v>64</v>
+      </c>
+      <c r="I2155">
+        <v>41.82</v>
+      </c>
+      <c r="J2155" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2155" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2155">
+        <v>4</v>
+      </c>
+      <c r="M2155">
+        <v>3</v>
+      </c>
+      <c r="N2155">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:14" ht="15" customHeight="1">
+      <c r="A2156" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2156" t="s">
+        <v>850</v>
+      </c>
+      <c r="C2156" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D2156">
+        <v>307</v>
+      </c>
+      <c r="E2156">
+        <v>42</v>
+      </c>
+      <c r="F2156">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2156">
+        <v>44.83</v>
+      </c>
+      <c r="H2156">
+        <v>72</v>
+      </c>
+      <c r="I2156">
+        <v>80</v>
+      </c>
+      <c r="J2156" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2156" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2156">
+        <v>4</v>
+      </c>
+      <c r="M2156">
+        <v>2</v>
+      </c>
+      <c r="N2156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:14" ht="15" customHeight="1">
+      <c r="A2157" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2157" t="s">
+        <v>856</v>
+      </c>
+      <c r="C2157" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D2157">
+        <v>327</v>
+      </c>
+      <c r="E2157">
+        <v>38</v>
+      </c>
+      <c r="F2157">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2157">
+        <v>53.45</v>
+      </c>
+      <c r="H2157">
+        <v>82</v>
+      </c>
+      <c r="I2157">
+        <v>87.27</v>
+      </c>
+      <c r="J2157" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2157" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2157">
+        <v>4</v>
+      </c>
+      <c r="M2157">
+        <v>2</v>
+      </c>
+      <c r="N2157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:14" ht="15" customHeight="1">
+      <c r="A2158" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2158" t="s">
+        <v>857</v>
+      </c>
+      <c r="C2158" t="s">
+        <v>858</v>
+      </c>
+      <c r="D2158">
+        <v>265</v>
+      </c>
+      <c r="E2158">
+        <v>34</v>
+      </c>
+      <c r="F2158">
+        <v>75.61</v>
+      </c>
+      <c r="G2158">
+        <v>31.03</v>
+      </c>
+      <c r="H2158">
+        <v>70</v>
+      </c>
+      <c r="I2158">
+        <v>54.55</v>
+      </c>
+      <c r="J2158" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2158" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2158">
+        <v>4</v>
+      </c>
+      <c r="M2158">
+        <v>1</v>
+      </c>
+      <c r="N2158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:14" ht="15" customHeight="1">
+      <c r="A2159" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2159" t="s">
+        <v>873</v>
+      </c>
+      <c r="C2159" t="s">
+        <v>874</v>
+      </c>
+      <c r="D2159">
+        <v>244</v>
+      </c>
+      <c r="E2159">
+        <v>38</v>
+      </c>
+      <c r="F2159">
+        <v>82.93</v>
+      </c>
+      <c r="G2159">
+        <v>22.41</v>
+      </c>
+      <c r="H2159">
+        <v>54</v>
+      </c>
+      <c r="I2159">
+        <v>41.82</v>
+      </c>
+      <c r="J2159" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2159" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2159">
+        <v>4</v>
+      </c>
+      <c r="M2159">
+        <v>2</v>
+      </c>
+      <c r="N2159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:14" ht="15" customHeight="1">
+      <c r="A2160" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2160" t="s">
+        <v>855</v>
+      </c>
+      <c r="C2160" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D2160">
+        <v>445</v>
+      </c>
+      <c r="E2160">
+        <v>86</v>
+      </c>
+      <c r="F2160">
+        <v>95.12</v>
+      </c>
+      <c r="G2160">
+        <v>87.93</v>
+      </c>
+      <c r="H2160">
+        <v>84</v>
+      </c>
+      <c r="I2160">
+        <v>96.36</v>
+      </c>
+      <c r="J2160" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2160" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2160">
+        <v>4</v>
+      </c>
+      <c r="M2160">
+        <v>4</v>
+      </c>
+      <c r="N2160">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:14" ht="15" customHeight="1">
+      <c r="A2161" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2161" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C2161" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D2161">
+        <v>217</v>
+      </c>
+      <c r="E2161">
+        <v>38</v>
+      </c>
+      <c r="F2161">
+        <v>58.54</v>
+      </c>
+      <c r="G2161">
+        <v>27.59</v>
+      </c>
+      <c r="H2161">
+        <v>56</v>
+      </c>
+      <c r="I2161">
+        <v>21.82</v>
+      </c>
+      <c r="J2161" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2161" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2161">
+        <v>3</v>
+      </c>
+      <c r="M2161">
+        <v>2</v>
+      </c>
+      <c r="N2161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:14" ht="15" customHeight="1">
+      <c r="A2162" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2162" t="s">
+        <v>882</v>
+      </c>
+      <c r="C2162" t="s">
+        <v>883</v>
+      </c>
+      <c r="D2162">
+        <v>279</v>
+      </c>
+      <c r="E2162">
+        <v>50</v>
+      </c>
+      <c r="F2162">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2162">
+        <v>41.38</v>
+      </c>
+      <c r="H2162">
+        <v>74</v>
+      </c>
+      <c r="I2162">
+        <v>30.91</v>
+      </c>
+      <c r="J2162" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2162" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2162">
+        <v>3</v>
+      </c>
+      <c r="M2162">
+        <v>2</v>
+      </c>
+      <c r="N2162">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:14" ht="15" customHeight="1">
+      <c r="A2163" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2163" t="s">
+        <v>880</v>
+      </c>
+      <c r="C2163" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D2163">
+        <v>329</v>
+      </c>
+      <c r="E2163">
+        <v>60</v>
+      </c>
+      <c r="F2163">
+        <v>90.24</v>
+      </c>
+      <c r="G2163">
+        <v>50</v>
+      </c>
+      <c r="H2163">
+        <v>64</v>
+      </c>
+      <c r="I2163">
+        <v>61.82</v>
+      </c>
+      <c r="J2163" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2163" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2163">
+        <v>4</v>
+      </c>
+      <c r="M2163">
+        <v>3</v>
+      </c>
+      <c r="N2163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:14" ht="15" customHeight="1">
+      <c r="A2164" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2164" t="s">
+        <v>851</v>
+      </c>
+      <c r="C2164" t="s">
+        <v>852</v>
+      </c>
+      <c r="D2164">
+        <v>310</v>
+      </c>
+      <c r="E2164">
+        <v>34</v>
+      </c>
+      <c r="F2164">
+        <v>78.05</v>
+      </c>
+      <c r="G2164">
+        <v>55.17</v>
+      </c>
+      <c r="H2164">
+        <v>74</v>
+      </c>
+      <c r="I2164">
+        <v>80</v>
+      </c>
+      <c r="J2164" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2164" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2164">
+        <v>4</v>
+      </c>
+      <c r="M2164">
+        <v>1</v>
+      </c>
+      <c r="N2164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:14" ht="15" customHeight="1">
+      <c r="A2165" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2165" t="s">
+        <v>875</v>
+      </c>
+      <c r="C2165" t="s">
+        <v>876</v>
+      </c>
+      <c r="D2165">
+        <v>225</v>
+      </c>
+      <c r="E2165">
+        <v>46</v>
+      </c>
+      <c r="F2165">
+        <v>43.9</v>
+      </c>
+      <c r="G2165">
+        <v>32.76</v>
+      </c>
+      <c r="H2165">
+        <v>56</v>
+      </c>
+      <c r="I2165">
+        <v>47.27</v>
+      </c>
+      <c r="J2165" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2165" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2165">
+        <v>2</v>
+      </c>
+      <c r="M2165">
+        <v>2</v>
+      </c>
+      <c r="N2165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:14" ht="15" customHeight="1">
+      <c r="A2166" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2166" t="s">
+        <v>846</v>
+      </c>
+      <c r="C2166" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D2166">
+        <v>372</v>
+      </c>
+      <c r="E2166">
+        <v>58</v>
+      </c>
+      <c r="F2166">
+        <v>92.68</v>
+      </c>
+      <c r="G2166">
+        <v>65.52</v>
+      </c>
+      <c r="H2166">
+        <v>80</v>
+      </c>
+      <c r="I2166">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2166" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2166" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2166">
+        <v>4</v>
+      </c>
+      <c r="M2166">
+        <v>3</v>
+      </c>
+      <c r="N2166">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:14" ht="15" customHeight="1">
+      <c r="A2167" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2167" t="s">
+        <v>871</v>
+      </c>
+      <c r="C2167" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D2167">
+        <v>289</v>
+      </c>
+      <c r="E2167">
+        <v>38</v>
+      </c>
+      <c r="F2167">
+        <v>73.17</v>
+      </c>
+      <c r="G2167">
+        <v>41.38</v>
+      </c>
+      <c r="H2167">
+        <v>76</v>
+      </c>
+      <c r="I2167">
+        <v>63.64</v>
+      </c>
+      <c r="J2167" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2167" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2167">
+        <v>4</v>
+      </c>
+      <c r="M2167">
+        <v>2</v>
+      </c>
+      <c r="N2167">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:14" ht="15" customHeight="1">
+      <c r="A2168" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2168" t="s">
+        <v>859</v>
+      </c>
+      <c r="C2168" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D2168">
+        <v>399</v>
+      </c>
+      <c r="E2168">
+        <v>86</v>
+      </c>
+      <c r="F2168">
+        <v>92.68</v>
+      </c>
+      <c r="G2168">
+        <v>55.17</v>
+      </c>
+      <c r="H2168">
+        <v>80</v>
+      </c>
+      <c r="I2168">
+        <v>94.55</v>
+      </c>
+      <c r="J2168" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2168" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2168">
+        <v>4</v>
+      </c>
+      <c r="M2168">
+        <v>4</v>
+      </c>
+      <c r="N2168">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:14" ht="15" customHeight="1">
+      <c r="A2169" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2169" t="s">
+        <v>886</v>
+      </c>
+      <c r="C2169" t="s">
+        <v>887</v>
+      </c>
+      <c r="D2169">
+        <v>78</v>
+      </c>
+      <c r="E2169">
+        <v>18</v>
+      </c>
+      <c r="F2169">
+        <v>0</v>
+      </c>
+      <c r="G2169">
+        <v>13.79</v>
+      </c>
+      <c r="H2169">
+        <v>24</v>
+      </c>
+      <c r="I2169">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2169" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2169" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2169">
+        <v>1</v>
+      </c>
+      <c r="M2169">
+        <v>1</v>
+      </c>
+      <c r="N2169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:14" ht="15" customHeight="1">
+      <c r="A2170" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2170" t="s">
+        <v>847</v>
+      </c>
+      <c r="C2170" t="s">
+        <v>848</v>
+      </c>
+      <c r="D2170">
+        <v>338</v>
+      </c>
+      <c r="E2170">
+        <v>56</v>
+      </c>
+      <c r="F2170">
+        <v>85.37</v>
+      </c>
+      <c r="G2170">
+        <v>56.9</v>
+      </c>
+      <c r="H2170">
+        <v>74</v>
+      </c>
+      <c r="I2170">
+        <v>61.82</v>
+      </c>
+      <c r="J2170" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2170" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2170">
+        <v>4</v>
+      </c>
+      <c r="M2170">
+        <v>3</v>
+      </c>
+      <c r="N2170">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:14" ht="15" customHeight="1">
+      <c r="A2171" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2171" t="s">
+        <v>869</v>
+      </c>
+      <c r="C2171" t="s">
+        <v>870</v>
+      </c>
+      <c r="D2171">
+        <v>310</v>
+      </c>
+      <c r="E2171">
+        <v>44</v>
+      </c>
+      <c r="F2171">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2171">
+        <v>48.28</v>
+      </c>
+      <c r="H2171">
+        <v>80</v>
+      </c>
+      <c r="I2171">
+        <v>47.27</v>
+      </c>
+      <c r="J2171" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2171" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2171">
+        <v>4</v>
+      </c>
+      <c r="M2171">
+        <v>2</v>
+      </c>
+      <c r="N2171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:14" ht="15" customHeight="1">
+      <c r="A2172" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2172" t="s">
+        <v>844</v>
+      </c>
+      <c r="C2172" t="s">
+        <v>845</v>
+      </c>
+      <c r="D2172">
+        <v>372</v>
+      </c>
+      <c r="E2172">
+        <v>60</v>
+      </c>
+      <c r="F2172">
+        <v>85.37</v>
+      </c>
+      <c r="G2172">
+        <v>70.69</v>
+      </c>
+      <c r="H2172">
+        <v>84</v>
+      </c>
+      <c r="I2172">
+        <v>65.45</v>
+      </c>
+      <c r="J2172" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2172" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2172">
+        <v>4</v>
+      </c>
+      <c r="M2172">
+        <v>3</v>
+      </c>
+      <c r="N2172">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:14" ht="15" customHeight="1">
+      <c r="A2173" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2173" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C2173" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D2173">
+        <v>277</v>
+      </c>
+      <c r="E2173">
+        <v>56</v>
+      </c>
+      <c r="F2173">
+        <v>73.17</v>
+      </c>
+      <c r="G2173">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H2173">
+        <v>56</v>
+      </c>
+      <c r="I2173">
+        <v>45.45</v>
+      </c>
+      <c r="J2173" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2173" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2173">
+        <v>4</v>
+      </c>
+      <c r="M2173">
+        <v>3</v>
+      </c>
+      <c r="N2173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:14" ht="15" customHeight="1">
+      <c r="A2174" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2174" t="s">
+        <v>866</v>
+      </c>
+      <c r="C2174" t="s">
+        <v>867</v>
+      </c>
+      <c r="D2174">
+        <v>330</v>
+      </c>
+      <c r="E2174">
+        <v>64</v>
+      </c>
+      <c r="F2174">
+        <v>78.05</v>
+      </c>
+      <c r="G2174">
+        <v>55.17</v>
+      </c>
+      <c r="H2174">
+        <v>72</v>
+      </c>
+      <c r="I2174">
+        <v>49.09</v>
+      </c>
+      <c r="J2174" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2174" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2174">
+        <v>4</v>
+      </c>
+      <c r="M2174">
+        <v>3</v>
+      </c>
+      <c r="N2174">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:14" ht="15" customHeight="1">
+      <c r="A2175" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2175" t="s">
+        <v>839</v>
+      </c>
+      <c r="C2175" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D2175">
+        <v>341</v>
+      </c>
+      <c r="E2175">
+        <v>70</v>
+      </c>
+      <c r="F2175">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2175">
+        <v>51.72</v>
+      </c>
+      <c r="H2175">
+        <v>80</v>
+      </c>
+      <c r="I2175">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="J2175" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2175" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2175">
+        <v>3</v>
+      </c>
+      <c r="M2175">
+        <v>3</v>
+      </c>
+      <c r="N2175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:14" ht="15" customHeight="1">
+      <c r="A2176" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2176" t="s">
+        <v>884</v>
+      </c>
+      <c r="C2176" t="s">
+        <v>885</v>
+      </c>
+      <c r="D2176">
+        <v>255</v>
+      </c>
+      <c r="E2176">
+        <v>54</v>
+      </c>
+      <c r="F2176">
+        <v>75.61</v>
+      </c>
+      <c r="G2176">
+        <v>31.03</v>
+      </c>
+      <c r="H2176">
+        <v>50</v>
+      </c>
+      <c r="I2176">
+        <v>30.91</v>
+      </c>
+      <c r="J2176" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2176" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2176">
+        <v>4</v>
+      </c>
+      <c r="M2176">
+        <v>3</v>
+      </c>
+      <c r="N2176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:14" ht="15" customHeight="1">
+      <c r="A2177" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2177" t="s">
+        <v>861</v>
+      </c>
+      <c r="C2177" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D2177">
+        <v>336</v>
+      </c>
+      <c r="E2177">
+        <v>48</v>
+      </c>
+      <c r="F2177">
+        <v>78.05</v>
+      </c>
+      <c r="G2177">
+        <v>67.239999999999995</v>
+      </c>
+      <c r="H2177">
+        <v>82</v>
+      </c>
+      <c r="I2177">
+        <v>45.45</v>
+      </c>
+      <c r="J2177" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2177" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2177">
+        <v>4</v>
+      </c>
+      <c r="M2177">
+        <v>2</v>
+      </c>
+      <c r="N2177">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:14" ht="15" customHeight="1">
+      <c r="A2178" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2178" t="s">
+        <v>925</v>
+      </c>
+      <c r="C2178" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D2178">
+        <v>290</v>
+      </c>
+      <c r="E2178">
+        <v>50</v>
+      </c>
+      <c r="F2178">
+        <v>73.17</v>
+      </c>
+      <c r="G2178">
+        <v>44.83</v>
+      </c>
+      <c r="H2178">
+        <v>70</v>
+      </c>
+      <c r="I2178">
+        <v>38.18</v>
+      </c>
+      <c r="J2178" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2178" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2178">
+        <v>4</v>
+      </c>
+      <c r="M2178">
+        <v>2</v>
+      </c>
+      <c r="N2178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:14" ht="15" customHeight="1">
+      <c r="A2179" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2179" t="s">
+        <v>901</v>
+      </c>
+      <c r="C2179" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D2179">
+        <v>365</v>
+      </c>
+      <c r="E2179">
+        <v>60</v>
+      </c>
+      <c r="F2179">
+        <v>87.8</v>
+      </c>
+      <c r="G2179">
+        <v>62.07</v>
+      </c>
+      <c r="H2179">
+        <v>82</v>
+      </c>
+      <c r="I2179">
+        <v>72.73</v>
+      </c>
+      <c r="J2179" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2179" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2179">
+        <v>4</v>
+      </c>
+      <c r="M2179">
+        <v>3</v>
+      </c>
+      <c r="N2179">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:14" ht="15" customHeight="1">
+      <c r="A2180" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2180" t="s">
+        <v>918</v>
+      </c>
+      <c r="C2180" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D2180">
+        <v>351</v>
+      </c>
+      <c r="E2180">
+        <v>68</v>
+      </c>
+      <c r="F2180">
+        <v>82.93</v>
+      </c>
+      <c r="G2180">
+        <v>53.45</v>
+      </c>
+      <c r="H2180">
+        <v>76</v>
+      </c>
+      <c r="I2180">
+        <v>70.91</v>
+      </c>
+      <c r="J2180" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2180" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2180">
+        <v>4</v>
+      </c>
+      <c r="M2180">
+        <v>3</v>
+      </c>
+      <c r="N2180">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:14" ht="15" customHeight="1">
+      <c r="A2181" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2181" t="s">
+        <v>898</v>
+      </c>
+      <c r="C2181" t="s">
+        <v>899</v>
+      </c>
+      <c r="D2181">
+        <v>278</v>
+      </c>
+      <c r="E2181">
+        <v>50</v>
+      </c>
+      <c r="F2181">
+        <v>78.05</v>
+      </c>
+      <c r="G2181">
+        <v>37.93</v>
+      </c>
+      <c r="H2181">
+        <v>58</v>
+      </c>
+      <c r="I2181">
+        <v>49.09</v>
+      </c>
+      <c r="J2181" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2181" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2181">
+        <v>4</v>
+      </c>
+      <c r="M2181">
+        <v>2</v>
+      </c>
+      <c r="N2181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:14" ht="15" customHeight="1">
+      <c r="A2182" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2182" t="s">
+        <v>888</v>
+      </c>
+      <c r="C2182" t="s">
+        <v>889</v>
+      </c>
+      <c r="D2182">
+        <v>412</v>
+      </c>
+      <c r="E2182">
+        <v>70</v>
+      </c>
+      <c r="F2182">
+        <v>87.8</v>
+      </c>
+      <c r="G2182">
+        <v>79.31</v>
+      </c>
+      <c r="H2182">
+        <v>86</v>
+      </c>
+      <c r="I2182">
+        <v>100</v>
+      </c>
+      <c r="J2182" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2182" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2182">
+        <v>4</v>
+      </c>
+      <c r="M2182">
+        <v>3</v>
+      </c>
+      <c r="N2182">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:14" ht="15" customHeight="1">
+      <c r="A2183" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2183" t="s">
+        <v>892</v>
+      </c>
+      <c r="C2183" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D2183">
+        <v>233</v>
+      </c>
+      <c r="E2183">
+        <v>44</v>
+      </c>
+      <c r="F2183">
+        <v>48.78</v>
+      </c>
+      <c r="G2183">
+        <v>41.38</v>
+      </c>
+      <c r="H2183">
+        <v>58</v>
+      </c>
+      <c r="I2183">
+        <v>29.09</v>
+      </c>
+      <c r="J2183" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2183" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2183">
+        <v>2</v>
+      </c>
+      <c r="M2183">
+        <v>2</v>
+      </c>
+      <c r="N2183">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:14" ht="15" customHeight="1">
+      <c r="A2184" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2184" t="s">
+        <v>926</v>
+      </c>
+      <c r="C2184" t="s">
+        <v>927</v>
+      </c>
+      <c r="D2184">
+        <v>273</v>
+      </c>
+      <c r="E2184">
+        <v>58</v>
+      </c>
+      <c r="F2184">
+        <v>73.17</v>
+      </c>
+      <c r="G2184">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H2184">
+        <v>60</v>
+      </c>
+      <c r="I2184">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2184" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2184" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2184">
+        <v>4</v>
+      </c>
+      <c r="M2184">
+        <v>3</v>
+      </c>
+      <c r="N2184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:14" ht="15" customHeight="1">
+      <c r="A2185" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2185" t="s">
+        <v>896</v>
+      </c>
+      <c r="C2185" t="s">
+        <v>897</v>
+      </c>
+      <c r="D2185">
+        <v>285</v>
+      </c>
+      <c r="E2185">
+        <v>48</v>
+      </c>
+      <c r="F2185">
+        <v>90.24</v>
+      </c>
+      <c r="G2185">
+        <v>32.76</v>
+      </c>
+      <c r="H2185">
+        <v>58</v>
+      </c>
+      <c r="I2185">
+        <v>52.73</v>
+      </c>
+      <c r="J2185" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2185" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2185">
+        <v>4</v>
+      </c>
+      <c r="M2185">
+        <v>2</v>
+      </c>
+      <c r="N2185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:14" ht="15" customHeight="1">
+      <c r="A2186" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2186" t="s">
+        <v>911</v>
+      </c>
+      <c r="C2186" t="s">
+        <v>912</v>
+      </c>
+      <c r="D2186">
+        <v>329</v>
+      </c>
+      <c r="E2186">
+        <v>58</v>
+      </c>
+      <c r="F2186">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2186">
+        <v>55.17</v>
+      </c>
+      <c r="H2186">
+        <v>78</v>
+      </c>
+      <c r="I2186">
+        <v>40</v>
+      </c>
+      <c r="J2186" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2186" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2186">
+        <v>4</v>
+      </c>
+      <c r="M2186">
+        <v>3</v>
+      </c>
+      <c r="N2186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:14" ht="15" customHeight="1">
+      <c r="A2187" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2187" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C2187" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D2187">
+        <v>326</v>
+      </c>
+      <c r="E2187">
+        <v>62</v>
+      </c>
+      <c r="F2187">
+        <v>78.05</v>
+      </c>
+      <c r="G2187">
+        <v>55.17</v>
+      </c>
+      <c r="H2187">
+        <v>64</v>
+      </c>
+      <c r="I2187">
+        <v>69.09</v>
+      </c>
+      <c r="J2187" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2187" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2187">
+        <v>4</v>
+      </c>
+      <c r="M2187">
+        <v>3</v>
+      </c>
+      <c r="N2187">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:14" ht="15" customHeight="1">
+      <c r="A2188" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2188" t="s">
+        <v>923</v>
+      </c>
+      <c r="C2188" t="s">
+        <v>924</v>
+      </c>
+      <c r="D2188">
+        <v>296</v>
+      </c>
+      <c r="E2188">
+        <v>42</v>
+      </c>
+      <c r="F2188">
+        <v>87.8</v>
+      </c>
+      <c r="G2188">
+        <v>46.55</v>
+      </c>
+      <c r="H2188">
+        <v>66</v>
+      </c>
+      <c r="I2188">
+        <v>40</v>
+      </c>
+      <c r="J2188" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2188" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2188">
+        <v>4</v>
+      </c>
+      <c r="M2188">
+        <v>2</v>
+      </c>
+      <c r="N2188">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:14" ht="15" customHeight="1">
+      <c r="A2189" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2189" t="s">
+        <v>902</v>
+      </c>
+      <c r="C2189" t="s">
+        <v>903</v>
+      </c>
+      <c r="D2189">
+        <v>308</v>
+      </c>
+      <c r="E2189">
+        <v>52</v>
+      </c>
+      <c r="F2189">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2189">
+        <v>27.59</v>
+      </c>
+      <c r="H2189">
+        <v>82</v>
+      </c>
+      <c r="I2189">
+        <v>74.55</v>
+      </c>
+      <c r="J2189" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2189" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2189">
+        <v>4</v>
+      </c>
+      <c r="M2189">
+        <v>3</v>
+      </c>
+      <c r="N2189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:14" ht="15" customHeight="1">
+      <c r="A2190" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2190" t="s">
+        <v>909</v>
+      </c>
+      <c r="C2190" t="s">
+        <v>910</v>
+      </c>
+      <c r="D2190">
+        <v>203</v>
+      </c>
+      <c r="E2190">
+        <v>40</v>
+      </c>
+      <c r="F2190">
+        <v>46.34</v>
+      </c>
+      <c r="G2190">
+        <v>32.76</v>
+      </c>
+      <c r="H2190">
+        <v>44</v>
+      </c>
+      <c r="I2190">
+        <v>38.18</v>
+      </c>
+      <c r="J2190" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2190" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2190">
+        <v>2</v>
+      </c>
+      <c r="M2190">
+        <v>2</v>
+      </c>
+      <c r="N2190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:14" ht="15" customHeight="1">
+      <c r="A2191" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2191" t="s">
+        <v>922</v>
+      </c>
+      <c r="C2191" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D2191">
+        <v>190</v>
+      </c>
+      <c r="E2191">
+        <v>30</v>
+      </c>
+      <c r="F2191">
+        <v>41.46</v>
+      </c>
+      <c r="G2191">
+        <v>41.38</v>
+      </c>
+      <c r="H2191">
+        <v>42</v>
+      </c>
+      <c r="I2191">
+        <v>29.09</v>
+      </c>
+      <c r="J2191" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2191" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2191">
+        <v>2</v>
+      </c>
+      <c r="M2191">
+        <v>1</v>
+      </c>
+      <c r="N2191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:14" ht="15" customHeight="1">
+      <c r="A2192" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2192" t="s">
+        <v>900</v>
+      </c>
+      <c r="C2192" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D2192">
+        <v>88</v>
+      </c>
+      <c r="E2192">
+        <v>16</v>
+      </c>
+      <c r="F2192">
+        <v>0</v>
+      </c>
+      <c r="G2192">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="H2192">
+        <v>26</v>
+      </c>
+      <c r="I2192">
+        <v>49.09</v>
+      </c>
+      <c r="J2192" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2192" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2192">
+        <v>1</v>
+      </c>
+      <c r="M2192">
+        <v>1</v>
+      </c>
+      <c r="N2192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:14" ht="15" customHeight="1">
+      <c r="A2193" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2193" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C2193" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D2193">
+        <v>251</v>
+      </c>
+      <c r="E2193">
+        <v>48</v>
+      </c>
+      <c r="F2193">
+        <v>56.1</v>
+      </c>
+      <c r="G2193">
+        <v>46.55</v>
+      </c>
+      <c r="H2193">
+        <v>54</v>
+      </c>
+      <c r="I2193">
+        <v>38.18</v>
+      </c>
+      <c r="J2193" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2193" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2193">
+        <v>3</v>
+      </c>
+      <c r="M2193">
+        <v>2</v>
+      </c>
+      <c r="N2193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:14" ht="15" customHeight="1">
+      <c r="A2194" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2194" t="s">
+        <v>919</v>
+      </c>
+      <c r="C2194" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D2194">
+        <v>277</v>
+      </c>
+      <c r="E2194">
+        <v>44</v>
+      </c>
+      <c r="F2194">
+        <v>87.8</v>
+      </c>
+      <c r="G2194">
+        <v>41.38</v>
+      </c>
+      <c r="H2194">
+        <v>50</v>
+      </c>
+      <c r="I2194">
+        <v>49.09</v>
+      </c>
+      <c r="J2194" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2194" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2194">
+        <v>4</v>
+      </c>
+      <c r="M2194">
+        <v>2</v>
+      </c>
+      <c r="N2194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:14" ht="15" customHeight="1">
+      <c r="A2195" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2195" t="s">
+        <v>534</v>
+      </c>
+      <c r="C2195" t="s">
+        <v>535</v>
+      </c>
+      <c r="D2195">
+        <v>310</v>
+      </c>
+      <c r="E2195">
+        <v>56</v>
+      </c>
+      <c r="F2195">
+        <v>73.17</v>
+      </c>
+      <c r="G2195">
+        <v>53.45</v>
+      </c>
+      <c r="H2195">
+        <v>72</v>
+      </c>
+      <c r="I2195">
+        <v>41.82</v>
+      </c>
+      <c r="J2195" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2195" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2195">
+        <v>4</v>
+      </c>
+      <c r="M2195">
+        <v>3</v>
+      </c>
+      <c r="N2195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:14" ht="15" customHeight="1">
+      <c r="A2196" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2196" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C2196" t="s">
+        <v>890</v>
+      </c>
+      <c r="D2196">
+        <v>253</v>
+      </c>
+      <c r="E2196">
+        <v>38</v>
+      </c>
+      <c r="F2196">
+        <v>78.05</v>
+      </c>
+      <c r="G2196">
+        <v>31.03</v>
+      </c>
+      <c r="H2196">
+        <v>56</v>
+      </c>
+      <c r="I2196">
+        <v>47.27</v>
+      </c>
+      <c r="J2196" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2196" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2196">
+        <v>4</v>
+      </c>
+      <c r="M2196">
+        <v>2</v>
+      </c>
+      <c r="N2196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:14" ht="15" customHeight="1">
+      <c r="A2197" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2197" t="s">
+        <v>773</v>
+      </c>
+      <c r="C2197" t="s">
+        <v>774</v>
+      </c>
+      <c r="D2197">
+        <v>374</v>
+      </c>
+      <c r="E2197">
+        <v>64</v>
+      </c>
+      <c r="F2197">
+        <v>85.37</v>
+      </c>
+      <c r="G2197">
+        <v>70.69</v>
+      </c>
+      <c r="H2197">
+        <v>82</v>
+      </c>
+      <c r="I2197">
+        <v>63.64</v>
+      </c>
+      <c r="J2197" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2197" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2197">
+        <v>4</v>
+      </c>
+      <c r="M2197">
+        <v>3</v>
+      </c>
+      <c r="N2197">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:14" ht="15" customHeight="1">
+      <c r="A2198" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2198" t="s">
+        <v>904</v>
+      </c>
+      <c r="C2198" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D2198">
+        <v>192</v>
+      </c>
+      <c r="E2198">
+        <v>30</v>
+      </c>
+      <c r="F2198">
+        <v>48.78</v>
+      </c>
+      <c r="G2198">
+        <v>43.1</v>
+      </c>
+      <c r="H2198">
+        <v>34</v>
+      </c>
+      <c r="I2198">
+        <v>30.91</v>
+      </c>
+      <c r="J2198" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2198" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2198">
+        <v>2</v>
+      </c>
+      <c r="M2198">
+        <v>1</v>
+      </c>
+      <c r="N2198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:14" ht="15" customHeight="1">
+      <c r="A2199" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2199" t="s">
+        <v>913</v>
+      </c>
+      <c r="C2199" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D2199">
+        <v>303</v>
+      </c>
+      <c r="E2199">
+        <v>34</v>
+      </c>
+      <c r="F2199">
+        <v>82.93</v>
+      </c>
+      <c r="G2199">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H2199">
+        <v>84</v>
+      </c>
+      <c r="I2199">
+        <v>63.64</v>
+      </c>
+      <c r="J2199" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2199" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2199">
+        <v>4</v>
+      </c>
+      <c r="M2199">
+        <v>1</v>
+      </c>
+      <c r="N2199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:14" ht="15" customHeight="1">
+      <c r="A2200" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2200" t="s">
+        <v>914</v>
+      </c>
+      <c r="C2200" t="s">
+        <v>915</v>
+      </c>
+      <c r="D2200">
+        <v>171</v>
+      </c>
+      <c r="E2200">
+        <v>28</v>
+      </c>
+      <c r="F2200">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2200">
+        <v>15.52</v>
+      </c>
+      <c r="H2200">
+        <v>36</v>
+      </c>
+      <c r="I2200">
+        <v>0</v>
+      </c>
+      <c r="J2200" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2200" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2200">
+        <v>4</v>
+      </c>
+      <c r="M2200">
+        <v>1</v>
+      </c>
+      <c r="N2200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:14" ht="15" customHeight="1">
+      <c r="A2201" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2201" t="s">
+        <v>894</v>
+      </c>
+      <c r="C2201" t="s">
+        <v>895</v>
+      </c>
+      <c r="D2201">
+        <v>212</v>
+      </c>
+      <c r="E2201">
+        <v>34</v>
+      </c>
+      <c r="F2201">
+        <v>51.22</v>
+      </c>
+      <c r="G2201">
+        <v>20.69</v>
+      </c>
+      <c r="H2201">
+        <v>60</v>
+      </c>
+      <c r="I2201">
+        <v>52.73</v>
+      </c>
+      <c r="J2201" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2201" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2201">
+        <v>3</v>
+      </c>
+      <c r="M2201">
+        <v>1</v>
+      </c>
+      <c r="N2201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:14" ht="15" customHeight="1">
+      <c r="A2202" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2202" t="s">
+        <v>916</v>
+      </c>
+      <c r="C2202" t="s">
+        <v>917</v>
+      </c>
+      <c r="D2202">
+        <v>329</v>
+      </c>
+      <c r="E2202">
+        <v>54</v>
+      </c>
+      <c r="F2202">
+        <v>73.17</v>
+      </c>
+      <c r="G2202">
+        <v>55.17</v>
+      </c>
+      <c r="H2202">
+        <v>80</v>
+      </c>
+      <c r="I2202">
+        <v>67.27</v>
+      </c>
+      <c r="J2202" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2202" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2202">
+        <v>4</v>
+      </c>
+      <c r="M2202">
+        <v>3</v>
+      </c>
+      <c r="N2202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:14" ht="15" customHeight="1">
+      <c r="A2203" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2203" t="s">
+        <v>793</v>
+      </c>
+      <c r="C2203" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D2203">
+        <v>285</v>
+      </c>
+      <c r="E2203">
+        <v>42</v>
+      </c>
+      <c r="F2203">
+        <v>75.61</v>
+      </c>
+      <c r="G2203">
+        <v>44.83</v>
+      </c>
+      <c r="H2203">
+        <v>68</v>
+      </c>
+      <c r="I2203">
+        <v>47.27</v>
+      </c>
+      <c r="J2203" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2203" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2203">
+        <v>4</v>
+      </c>
+      <c r="M2203">
+        <v>2</v>
+      </c>
+      <c r="N2203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:14" ht="15" customHeight="1">
+      <c r="A2204" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2204" t="s">
+        <v>905</v>
+      </c>
+      <c r="C2204" t="s">
+        <v>906</v>
+      </c>
+      <c r="D2204">
+        <v>312</v>
+      </c>
+      <c r="E2204">
+        <v>42</v>
+      </c>
+      <c r="F2204">
+        <v>75.61</v>
+      </c>
+      <c r="G2204">
+        <v>53.45</v>
+      </c>
+      <c r="H2204">
+        <v>72</v>
+      </c>
+      <c r="I2204">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="J2204" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2204" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2204">
+        <v>4</v>
+      </c>
+      <c r="M2204">
+        <v>2</v>
+      </c>
+      <c r="N2204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:14" ht="15" customHeight="1">
+      <c r="A2205" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2205" t="s">
+        <v>893</v>
+      </c>
+      <c r="C2205" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D2205">
+        <v>392</v>
+      </c>
+      <c r="E2205">
+        <v>64</v>
+      </c>
+      <c r="F2205">
+        <v>97.56</v>
+      </c>
+      <c r="G2205">
+        <v>77.59</v>
+      </c>
+      <c r="H2205">
+        <v>74</v>
+      </c>
+      <c r="I2205">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2205" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2205" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2205">
+        <v>4</v>
+      </c>
+      <c r="M2205">
+        <v>3</v>
+      </c>
+      <c r="N2205">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:14" ht="15" customHeight="1">
+      <c r="A2206" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2206" t="s">
+        <v>907</v>
+      </c>
+      <c r="C2206" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D2206">
+        <v>335</v>
+      </c>
+      <c r="E2206">
+        <v>46</v>
+      </c>
+      <c r="F2206">
+        <v>90.24</v>
+      </c>
+      <c r="G2206">
+        <v>60.34</v>
+      </c>
+      <c r="H2206">
+        <v>72</v>
+      </c>
+      <c r="I2206">
+        <v>63.64</v>
+      </c>
+      <c r="J2206" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2206" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2206">
+        <v>4</v>
+      </c>
+      <c r="M2206">
+        <v>2</v>
+      </c>
+      <c r="N2206">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:14" ht="15" customHeight="1">
+      <c r="A2207" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2207" t="s">
+        <v>891</v>
+      </c>
+      <c r="C2207" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2207">
+        <v>356</v>
+      </c>
+      <c r="E2207">
+        <v>64</v>
+      </c>
+      <c r="F2207">
+        <v>85.37</v>
+      </c>
+      <c r="G2207">
+        <v>51.72</v>
+      </c>
+      <c r="H2207">
+        <v>82</v>
+      </c>
+      <c r="I2207">
+        <v>74.55</v>
+      </c>
+      <c r="J2207" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2207" t="s">
+        <v>393</v>
+      </c>
+      <c r="L2207">
+        <v>4</v>
+      </c>
+      <c r="M2207">
+        <v>3</v>
+      </c>
+      <c r="N2207">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1825" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/data/Resultados_Simulacro_ICFES.xlsx
+++ b/data/Resultados_Simulacro_ICFES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorios\R_IEOS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961CEBA7-9C0B-436C-B546-74B0E2577E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE750588-5877-47EC-86DC-DD739D45485C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8427" uniqueCount="1470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9062" uniqueCount="1470">
   <si>
     <t>Grupo</t>
   </si>
@@ -4815,7 +4815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2207"/>
+  <dimension ref="A1:N2334"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -101932,6 +101932,5594 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2208" spans="1:14" ht="15" customHeight="1">
+      <c r="A2208" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2208" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C2208" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D2208">
+        <v>292</v>
+      </c>
+      <c r="E2208">
+        <v>44</v>
+      </c>
+      <c r="F2208">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2208">
+        <v>53.45</v>
+      </c>
+      <c r="H2208">
+        <v>72</v>
+      </c>
+      <c r="I2208">
+        <v>50.91</v>
+      </c>
+      <c r="J2208" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2208" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2208">
+        <v>3</v>
+      </c>
+      <c r="M2208">
+        <v>2</v>
+      </c>
+      <c r="N2208">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:14" ht="15" customHeight="1">
+      <c r="A2209" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2209" t="s">
+        <v>789</v>
+      </c>
+      <c r="C2209" t="s">
+        <v>953</v>
+      </c>
+      <c r="D2209">
+        <v>291</v>
+      </c>
+      <c r="E2209">
+        <v>48</v>
+      </c>
+      <c r="F2209">
+        <v>56.1</v>
+      </c>
+      <c r="G2209">
+        <v>53.45</v>
+      </c>
+      <c r="H2209">
+        <v>68</v>
+      </c>
+      <c r="I2209">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2209" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2209" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2209">
+        <v>3</v>
+      </c>
+      <c r="M2209">
+        <v>2</v>
+      </c>
+      <c r="N2209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:14" ht="15" customHeight="1">
+      <c r="A2210" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2210" t="s">
+        <v>954</v>
+      </c>
+      <c r="C2210" t="s">
+        <v>955</v>
+      </c>
+      <c r="D2210">
+        <v>99</v>
+      </c>
+      <c r="E2210">
+        <v>28</v>
+      </c>
+      <c r="F2210">
+        <v>29.27</v>
+      </c>
+      <c r="G2210">
+        <v>1.72</v>
+      </c>
+      <c r="H2210">
+        <v>26</v>
+      </c>
+      <c r="I2210">
+        <v>0</v>
+      </c>
+      <c r="J2210" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2210" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2210">
+        <v>1</v>
+      </c>
+      <c r="M2210">
+        <v>1</v>
+      </c>
+      <c r="N2210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:14" ht="15" customHeight="1">
+      <c r="A2211" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2211" t="s">
+        <v>792</v>
+      </c>
+      <c r="C2211" t="s">
+        <v>956</v>
+      </c>
+      <c r="D2211">
+        <v>252</v>
+      </c>
+      <c r="E2211">
+        <v>34</v>
+      </c>
+      <c r="F2211">
+        <v>48.78</v>
+      </c>
+      <c r="G2211">
+        <v>51.72</v>
+      </c>
+      <c r="H2211">
+        <v>56</v>
+      </c>
+      <c r="I2211">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="J2211" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2211" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2211">
+        <v>2</v>
+      </c>
+      <c r="M2211">
+        <v>1</v>
+      </c>
+      <c r="N2211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:14" ht="15" customHeight="1">
+      <c r="A2212" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2212" t="s">
+        <v>864</v>
+      </c>
+      <c r="C2212" t="s">
+        <v>865</v>
+      </c>
+      <c r="D2212">
+        <v>251</v>
+      </c>
+      <c r="E2212">
+        <v>44</v>
+      </c>
+      <c r="F2212">
+        <v>41.46</v>
+      </c>
+      <c r="G2212">
+        <v>58.62</v>
+      </c>
+      <c r="H2212">
+        <v>46</v>
+      </c>
+      <c r="I2212">
+        <v>80</v>
+      </c>
+      <c r="J2212" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2212" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2212">
+        <v>2</v>
+      </c>
+      <c r="M2212">
+        <v>2</v>
+      </c>
+      <c r="N2212">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:14" ht="15" customHeight="1">
+      <c r="A2213" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2213" t="s">
+        <v>766</v>
+      </c>
+      <c r="C2213" t="s">
+        <v>767</v>
+      </c>
+      <c r="D2213">
+        <v>346</v>
+      </c>
+      <c r="E2213">
+        <v>54</v>
+      </c>
+      <c r="F2213">
+        <v>75.61</v>
+      </c>
+      <c r="G2213">
+        <v>63.79</v>
+      </c>
+      <c r="H2213">
+        <v>82</v>
+      </c>
+      <c r="I2213">
+        <v>72.73</v>
+      </c>
+      <c r="J2213" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2213" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2213">
+        <v>4</v>
+      </c>
+      <c r="M2213">
+        <v>3</v>
+      </c>
+      <c r="N2213">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:14" ht="15" customHeight="1">
+      <c r="A2214" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2214" t="s">
+        <v>636</v>
+      </c>
+      <c r="C2214" t="s">
+        <v>637</v>
+      </c>
+      <c r="D2214">
+        <v>355</v>
+      </c>
+      <c r="E2214">
+        <v>56</v>
+      </c>
+      <c r="F2214">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2214">
+        <v>70.69</v>
+      </c>
+      <c r="H2214">
+        <v>80</v>
+      </c>
+      <c r="I2214">
+        <v>60</v>
+      </c>
+      <c r="J2214" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2214" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2214">
+        <v>4</v>
+      </c>
+      <c r="M2214">
+        <v>3</v>
+      </c>
+      <c r="N2214">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:14" ht="15" customHeight="1">
+      <c r="A2215" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2215" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C2215" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D2215">
+        <v>286</v>
+      </c>
+      <c r="E2215">
+        <v>56</v>
+      </c>
+      <c r="F2215">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2215">
+        <v>31.03</v>
+      </c>
+      <c r="H2215">
+        <v>70</v>
+      </c>
+      <c r="I2215">
+        <v>74.55</v>
+      </c>
+      <c r="J2215" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2215" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2215">
+        <v>3</v>
+      </c>
+      <c r="M2215">
+        <v>3</v>
+      </c>
+      <c r="N2215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:14" ht="15" customHeight="1">
+      <c r="A2216" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2216" t="s">
+        <v>784</v>
+      </c>
+      <c r="C2216" t="s">
+        <v>959</v>
+      </c>
+      <c r="D2216">
+        <v>245</v>
+      </c>
+      <c r="E2216">
+        <v>26</v>
+      </c>
+      <c r="F2216">
+        <v>51.22</v>
+      </c>
+      <c r="G2216">
+        <v>44.83</v>
+      </c>
+      <c r="H2216">
+        <v>68</v>
+      </c>
+      <c r="I2216">
+        <v>65.45</v>
+      </c>
+      <c r="J2216" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2216" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2216">
+        <v>3</v>
+      </c>
+      <c r="M2216">
+        <v>1</v>
+      </c>
+      <c r="N2216">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:14" ht="15" customHeight="1">
+      <c r="A2217" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2217" t="s">
+        <v>763</v>
+      </c>
+      <c r="C2217" t="s">
+        <v>960</v>
+      </c>
+      <c r="D2217">
+        <v>221</v>
+      </c>
+      <c r="E2217">
+        <v>38</v>
+      </c>
+      <c r="F2217">
+        <v>46.34</v>
+      </c>
+      <c r="G2217">
+        <v>31.03</v>
+      </c>
+      <c r="H2217">
+        <v>44</v>
+      </c>
+      <c r="I2217">
+        <v>94.55</v>
+      </c>
+      <c r="J2217" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2217" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2217">
+        <v>2</v>
+      </c>
+      <c r="M2217">
+        <v>2</v>
+      </c>
+      <c r="N2217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:14" ht="15" customHeight="1">
+      <c r="A2218" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2218" t="s">
+        <v>769</v>
+      </c>
+      <c r="C2218" t="s">
+        <v>961</v>
+      </c>
+      <c r="D2218">
+        <v>318</v>
+      </c>
+      <c r="E2218">
+        <v>58</v>
+      </c>
+      <c r="F2218">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2218">
+        <v>55.17</v>
+      </c>
+      <c r="H2218">
+        <v>68</v>
+      </c>
+      <c r="I2218">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2218" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2218" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2218">
+        <v>4</v>
+      </c>
+      <c r="M2218">
+        <v>3</v>
+      </c>
+      <c r="N2218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:14" ht="15" customHeight="1">
+      <c r="A2219" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2219" t="s">
+        <v>764</v>
+      </c>
+      <c r="C2219" t="s">
+        <v>765</v>
+      </c>
+      <c r="D2219">
+        <v>287</v>
+      </c>
+      <c r="E2219">
+        <v>52</v>
+      </c>
+      <c r="F2219">
+        <v>53.66</v>
+      </c>
+      <c r="G2219">
+        <v>43.1</v>
+      </c>
+      <c r="H2219">
+        <v>80</v>
+      </c>
+      <c r="I2219">
+        <v>58.18</v>
+      </c>
+      <c r="J2219" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2219" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2219">
+        <v>3</v>
+      </c>
+      <c r="M2219">
+        <v>3</v>
+      </c>
+      <c r="N2219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:14" ht="15" customHeight="1">
+      <c r="A2220" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2220" t="s">
+        <v>777</v>
+      </c>
+      <c r="C2220" t="s">
+        <v>778</v>
+      </c>
+      <c r="D2220">
+        <v>242</v>
+      </c>
+      <c r="E2220">
+        <v>42</v>
+      </c>
+      <c r="F2220">
+        <v>56.1</v>
+      </c>
+      <c r="G2220">
+        <v>36.21</v>
+      </c>
+      <c r="H2220">
+        <v>54</v>
+      </c>
+      <c r="I2220">
+        <v>61.82</v>
+      </c>
+      <c r="J2220" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2220" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2220">
+        <v>3</v>
+      </c>
+      <c r="M2220">
+        <v>2</v>
+      </c>
+      <c r="N2220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:14" ht="15" customHeight="1">
+      <c r="A2221" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2221" t="s">
+        <v>762</v>
+      </c>
+      <c r="C2221" t="s">
+        <v>962</v>
+      </c>
+      <c r="D2221">
+        <v>331</v>
+      </c>
+      <c r="E2221">
+        <v>46</v>
+      </c>
+      <c r="F2221">
+        <v>70.73</v>
+      </c>
+      <c r="G2221">
+        <v>65.52</v>
+      </c>
+      <c r="H2221">
+        <v>82</v>
+      </c>
+      <c r="I2221">
+        <v>67.27</v>
+      </c>
+      <c r="J2221" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2221" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2221">
+        <v>4</v>
+      </c>
+      <c r="M2221">
+        <v>2</v>
+      </c>
+      <c r="N2221">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:14" ht="15" customHeight="1">
+      <c r="A2222" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2222" t="s">
+        <v>785</v>
+      </c>
+      <c r="C2222" t="s">
+        <v>786</v>
+      </c>
+      <c r="D2222">
+        <v>335</v>
+      </c>
+      <c r="E2222">
+        <v>48</v>
+      </c>
+      <c r="F2222">
+        <v>75.61</v>
+      </c>
+      <c r="G2222">
+        <v>68.97</v>
+      </c>
+      <c r="H2222">
+        <v>74</v>
+      </c>
+      <c r="I2222">
+        <v>70.91</v>
+      </c>
+      <c r="J2222" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2222" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2222">
+        <v>4</v>
+      </c>
+      <c r="M2222">
+        <v>2</v>
+      </c>
+      <c r="N2222">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:14" ht="15" customHeight="1">
+      <c r="A2223" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2223" t="s">
+        <v>652</v>
+      </c>
+      <c r="C2223" t="s">
+        <v>653</v>
+      </c>
+      <c r="D2223">
+        <v>216</v>
+      </c>
+      <c r="E2223">
+        <v>44</v>
+      </c>
+      <c r="F2223">
+        <v>46.34</v>
+      </c>
+      <c r="G2223">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H2223">
+        <v>42</v>
+      </c>
+      <c r="I2223">
+        <v>60</v>
+      </c>
+      <c r="J2223" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2223" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2223">
+        <v>2</v>
+      </c>
+      <c r="M2223">
+        <v>2</v>
+      </c>
+      <c r="N2223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:14" ht="15" customHeight="1">
+      <c r="A2224" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2224" t="s">
+        <v>798</v>
+      </c>
+      <c r="C2224" t="s">
+        <v>799</v>
+      </c>
+      <c r="D2224">
+        <v>273</v>
+      </c>
+      <c r="E2224">
+        <v>44</v>
+      </c>
+      <c r="F2224">
+        <v>48.78</v>
+      </c>
+      <c r="G2224">
+        <v>55.17</v>
+      </c>
+      <c r="H2224">
+        <v>62</v>
+      </c>
+      <c r="I2224">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2224" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2224" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2224">
+        <v>2</v>
+      </c>
+      <c r="M2224">
+        <v>2</v>
+      </c>
+      <c r="N2224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:14" ht="15" customHeight="1">
+      <c r="A2225" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2225" t="s">
+        <v>776</v>
+      </c>
+      <c r="C2225" t="s">
+        <v>965</v>
+      </c>
+      <c r="D2225">
+        <v>272</v>
+      </c>
+      <c r="E2225">
+        <v>40</v>
+      </c>
+      <c r="F2225">
+        <v>58.54</v>
+      </c>
+      <c r="G2225">
+        <v>41.38</v>
+      </c>
+      <c r="H2225">
+        <v>72</v>
+      </c>
+      <c r="I2225">
+        <v>69.09</v>
+      </c>
+      <c r="J2225" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2225" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2225">
+        <v>3</v>
+      </c>
+      <c r="M2225">
+        <v>2</v>
+      </c>
+      <c r="N2225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:14" ht="15" customHeight="1">
+      <c r="A2226" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2226" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C2226" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D2226">
+        <v>281</v>
+      </c>
+      <c r="E2226">
+        <v>36</v>
+      </c>
+      <c r="F2226">
+        <v>51.22</v>
+      </c>
+      <c r="G2226">
+        <v>56.9</v>
+      </c>
+      <c r="H2226">
+        <v>72</v>
+      </c>
+      <c r="I2226">
+        <v>80</v>
+      </c>
+      <c r="J2226" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2226" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2226">
+        <v>3</v>
+      </c>
+      <c r="M2226">
+        <v>2</v>
+      </c>
+      <c r="N2226">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:14" ht="15" customHeight="1">
+      <c r="A2227" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2227" t="s">
+        <v>757</v>
+      </c>
+      <c r="C2227" t="s">
+        <v>966</v>
+      </c>
+      <c r="D2227">
+        <v>265</v>
+      </c>
+      <c r="E2227">
+        <v>44</v>
+      </c>
+      <c r="F2227">
+        <v>51.22</v>
+      </c>
+      <c r="G2227">
+        <v>56.9</v>
+      </c>
+      <c r="H2227">
+        <v>54</v>
+      </c>
+      <c r="I2227">
+        <v>69.09</v>
+      </c>
+      <c r="J2227" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2227" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2227">
+        <v>3</v>
+      </c>
+      <c r="M2227">
+        <v>2</v>
+      </c>
+      <c r="N2227">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:14" ht="15" customHeight="1">
+      <c r="A2228" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2228" t="s">
+        <v>783</v>
+      </c>
+      <c r="C2228" t="s">
+        <v>967</v>
+      </c>
+      <c r="D2228">
+        <v>263</v>
+      </c>
+      <c r="E2228">
+        <v>38</v>
+      </c>
+      <c r="F2228">
+        <v>63.41</v>
+      </c>
+      <c r="G2228">
+        <v>46.55</v>
+      </c>
+      <c r="H2228">
+        <v>54</v>
+      </c>
+      <c r="I2228">
+        <v>76.36</v>
+      </c>
+      <c r="J2228" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2228" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2228">
+        <v>3</v>
+      </c>
+      <c r="M2228">
+        <v>2</v>
+      </c>
+      <c r="N2228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:14" ht="15" customHeight="1">
+      <c r="A2229" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2229" t="s">
+        <v>968</v>
+      </c>
+      <c r="C2229" t="s">
+        <v>969</v>
+      </c>
+      <c r="D2229">
+        <v>360</v>
+      </c>
+      <c r="E2229">
+        <v>48</v>
+      </c>
+      <c r="F2229">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2229">
+        <v>72.41</v>
+      </c>
+      <c r="H2229">
+        <v>92</v>
+      </c>
+      <c r="I2229">
+        <v>92.73</v>
+      </c>
+      <c r="J2229" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2229" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2229">
+        <v>4</v>
+      </c>
+      <c r="M2229">
+        <v>2</v>
+      </c>
+      <c r="N2229">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:14" ht="15" customHeight="1">
+      <c r="A2230" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2230" t="s">
+        <v>768</v>
+      </c>
+      <c r="C2230" t="s">
+        <v>970</v>
+      </c>
+      <c r="D2230">
+        <v>268</v>
+      </c>
+      <c r="E2230">
+        <v>44</v>
+      </c>
+      <c r="F2230">
+        <v>56.1</v>
+      </c>
+      <c r="G2230">
+        <v>48.28</v>
+      </c>
+      <c r="H2230">
+        <v>64</v>
+      </c>
+      <c r="I2230">
+        <v>58.18</v>
+      </c>
+      <c r="J2230" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2230" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2230">
+        <v>3</v>
+      </c>
+      <c r="M2230">
+        <v>2</v>
+      </c>
+      <c r="N2230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:14" ht="15" customHeight="1">
+      <c r="A2231" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2231" t="s">
+        <v>640</v>
+      </c>
+      <c r="C2231" t="s">
+        <v>641</v>
+      </c>
+      <c r="D2231">
+        <v>274</v>
+      </c>
+      <c r="E2231">
+        <v>48</v>
+      </c>
+      <c r="F2231">
+        <v>70.73</v>
+      </c>
+      <c r="G2231">
+        <v>25.86</v>
+      </c>
+      <c r="H2231">
+        <v>66</v>
+      </c>
+      <c r="I2231">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2231" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2231" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2231">
+        <v>4</v>
+      </c>
+      <c r="M2231">
+        <v>2</v>
+      </c>
+      <c r="N2231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:14" ht="15" customHeight="1">
+      <c r="A2232" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>775</v>
+      </c>
+      <c r="C2232" t="s">
+        <v>971</v>
+      </c>
+      <c r="D2232">
+        <v>311</v>
+      </c>
+      <c r="E2232">
+        <v>58</v>
+      </c>
+      <c r="F2232">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2232">
+        <v>48.28</v>
+      </c>
+      <c r="H2232">
+        <v>70</v>
+      </c>
+      <c r="I2232">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="J2232" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2232" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2232">
+        <v>3</v>
+      </c>
+      <c r="M2232">
+        <v>3</v>
+      </c>
+      <c r="N2232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:14" ht="15" customHeight="1">
+      <c r="A2233" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2233" t="s">
+        <v>779</v>
+      </c>
+      <c r="C2233" t="s">
+        <v>972</v>
+      </c>
+      <c r="D2233">
+        <v>244</v>
+      </c>
+      <c r="E2233">
+        <v>28</v>
+      </c>
+      <c r="F2233">
+        <v>53.66</v>
+      </c>
+      <c r="G2233">
+        <v>56.9</v>
+      </c>
+      <c r="H2233">
+        <v>56</v>
+      </c>
+      <c r="I2233">
+        <v>49.09</v>
+      </c>
+      <c r="J2233" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2233" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2233">
+        <v>3</v>
+      </c>
+      <c r="M2233">
+        <v>1</v>
+      </c>
+      <c r="N2233">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:14" ht="15" customHeight="1">
+      <c r="A2234" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>787</v>
+      </c>
+      <c r="C2234" t="s">
+        <v>788</v>
+      </c>
+      <c r="D2234">
+        <v>240</v>
+      </c>
+      <c r="E2234">
+        <v>62</v>
+      </c>
+      <c r="F2234">
+        <v>34.15</v>
+      </c>
+      <c r="G2234">
+        <v>43.1</v>
+      </c>
+      <c r="H2234">
+        <v>48</v>
+      </c>
+      <c r="I2234">
+        <v>61.82</v>
+      </c>
+      <c r="J2234" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2234" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2234">
+        <v>1</v>
+      </c>
+      <c r="M2234">
+        <v>3</v>
+      </c>
+      <c r="N2234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:14" ht="15" customHeight="1">
+      <c r="A2235" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2235" t="s">
+        <v>760</v>
+      </c>
+      <c r="C2235" t="s">
+        <v>761</v>
+      </c>
+      <c r="D2235">
+        <v>382</v>
+      </c>
+      <c r="E2235">
+        <v>56</v>
+      </c>
+      <c r="F2235">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="G2235">
+        <v>74.14</v>
+      </c>
+      <c r="H2235">
+        <v>88</v>
+      </c>
+      <c r="I2235">
+        <v>96.36</v>
+      </c>
+      <c r="J2235" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2235" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2235">
+        <v>4</v>
+      </c>
+      <c r="M2235">
+        <v>3</v>
+      </c>
+      <c r="N2235">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:14" ht="15" customHeight="1">
+      <c r="A2236" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>795</v>
+      </c>
+      <c r="C2236" t="s">
+        <v>973</v>
+      </c>
+      <c r="D2236">
+        <v>243</v>
+      </c>
+      <c r="E2236">
+        <v>42</v>
+      </c>
+      <c r="F2236">
+        <v>43.9</v>
+      </c>
+      <c r="G2236">
+        <v>43.1</v>
+      </c>
+      <c r="H2236">
+        <v>60</v>
+      </c>
+      <c r="I2236">
+        <v>63.64</v>
+      </c>
+      <c r="J2236" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2236" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2236">
+        <v>2</v>
+      </c>
+      <c r="M2236">
+        <v>2</v>
+      </c>
+      <c r="N2236">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:14" ht="15" customHeight="1">
+      <c r="A2237" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2237" t="s">
+        <v>823</v>
+      </c>
+      <c r="C2237" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D2237">
+        <v>237</v>
+      </c>
+      <c r="E2237">
+        <v>46</v>
+      </c>
+      <c r="F2237">
+        <v>29.27</v>
+      </c>
+      <c r="G2237">
+        <v>50</v>
+      </c>
+      <c r="H2237">
+        <v>60</v>
+      </c>
+      <c r="I2237">
+        <v>60</v>
+      </c>
+      <c r="J2237" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2237" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2237">
+        <v>1</v>
+      </c>
+      <c r="M2237">
+        <v>2</v>
+      </c>
+      <c r="N2237">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:14" ht="15" customHeight="1">
+      <c r="A2238" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>603</v>
+      </c>
+      <c r="C2238" t="s">
+        <v>604</v>
+      </c>
+      <c r="D2238">
+        <v>221</v>
+      </c>
+      <c r="E2238">
+        <v>36</v>
+      </c>
+      <c r="F2238">
+        <v>48.78</v>
+      </c>
+      <c r="G2238">
+        <v>41.38</v>
+      </c>
+      <c r="H2238">
+        <v>56</v>
+      </c>
+      <c r="I2238">
+        <v>27.27</v>
+      </c>
+      <c r="J2238" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2238" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2238">
+        <v>2</v>
+      </c>
+      <c r="M2238">
+        <v>2</v>
+      </c>
+      <c r="N2238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:14" ht="15" customHeight="1">
+      <c r="A2239" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2239" t="s">
+        <v>782</v>
+      </c>
+      <c r="C2239" t="s">
+        <v>974</v>
+      </c>
+      <c r="D2239">
+        <v>219</v>
+      </c>
+      <c r="E2239">
+        <v>52</v>
+      </c>
+      <c r="F2239">
+        <v>43.9</v>
+      </c>
+      <c r="G2239">
+        <v>29.31</v>
+      </c>
+      <c r="H2239">
+        <v>50</v>
+      </c>
+      <c r="I2239">
+        <v>43.64</v>
+      </c>
+      <c r="J2239" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2239" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2239">
+        <v>2</v>
+      </c>
+      <c r="M2239">
+        <v>3</v>
+      </c>
+      <c r="N2239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:14" ht="15" customHeight="1">
+      <c r="A2240" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>975</v>
+      </c>
+      <c r="C2240" t="s">
+        <v>976</v>
+      </c>
+      <c r="D2240">
+        <v>254</v>
+      </c>
+      <c r="E2240">
+        <v>40</v>
+      </c>
+      <c r="F2240">
+        <v>41.46</v>
+      </c>
+      <c r="G2240">
+        <v>55.17</v>
+      </c>
+      <c r="H2240">
+        <v>64</v>
+      </c>
+      <c r="I2240">
+        <v>56.36</v>
+      </c>
+      <c r="J2240" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2240" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2240">
+        <v>2</v>
+      </c>
+      <c r="M2240">
+        <v>2</v>
+      </c>
+      <c r="N2240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:14" ht="15" customHeight="1">
+      <c r="A2241" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2241" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C2241" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D2241">
+        <v>258</v>
+      </c>
+      <c r="E2241">
+        <v>52</v>
+      </c>
+      <c r="F2241">
+        <v>41.46</v>
+      </c>
+      <c r="G2241">
+        <v>50</v>
+      </c>
+      <c r="H2241">
+        <v>64</v>
+      </c>
+      <c r="I2241">
+        <v>47.27</v>
+      </c>
+      <c r="J2241" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2241" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2241">
+        <v>2</v>
+      </c>
+      <c r="M2241">
+        <v>3</v>
+      </c>
+      <c r="N2241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:14" ht="15" customHeight="1">
+      <c r="A2242" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>796</v>
+      </c>
+      <c r="C2242" t="s">
+        <v>797</v>
+      </c>
+      <c r="D2242">
+        <v>273</v>
+      </c>
+      <c r="E2242">
+        <v>24</v>
+      </c>
+      <c r="F2242">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2242">
+        <v>50</v>
+      </c>
+      <c r="H2242">
+        <v>76</v>
+      </c>
+      <c r="I2242">
+        <v>52.73</v>
+      </c>
+      <c r="J2242" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2242" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2242">
+        <v>4</v>
+      </c>
+      <c r="M2242">
+        <v>1</v>
+      </c>
+      <c r="N2242">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:14" ht="15" customHeight="1">
+      <c r="A2243" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2243" t="s">
+        <v>977</v>
+      </c>
+      <c r="C2243" t="s">
+        <v>978</v>
+      </c>
+      <c r="D2243">
+        <v>269</v>
+      </c>
+      <c r="E2243">
+        <v>42</v>
+      </c>
+      <c r="F2243">
+        <v>60.98</v>
+      </c>
+      <c r="G2243">
+        <v>36.21</v>
+      </c>
+      <c r="H2243">
+        <v>70</v>
+      </c>
+      <c r="I2243">
+        <v>70.91</v>
+      </c>
+      <c r="J2243" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2243" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2243">
+        <v>3</v>
+      </c>
+      <c r="M2243">
+        <v>2</v>
+      </c>
+      <c r="N2243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:14" ht="15" customHeight="1">
+      <c r="A2244" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>772</v>
+      </c>
+      <c r="C2244" t="s">
+        <v>979</v>
+      </c>
+      <c r="D2244">
+        <v>282</v>
+      </c>
+      <c r="E2244">
+        <v>48</v>
+      </c>
+      <c r="F2244">
+        <v>46.34</v>
+      </c>
+      <c r="G2244">
+        <v>58.62</v>
+      </c>
+      <c r="H2244">
+        <v>72</v>
+      </c>
+      <c r="I2244">
+        <v>56.36</v>
+      </c>
+      <c r="J2244" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2244" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2244">
+        <v>2</v>
+      </c>
+      <c r="M2244">
+        <v>2</v>
+      </c>
+      <c r="N2244">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:14" ht="15" customHeight="1">
+      <c r="A2245" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2245" t="s">
+        <v>756</v>
+      </c>
+      <c r="C2245" t="s">
+        <v>981</v>
+      </c>
+      <c r="D2245">
+        <v>293</v>
+      </c>
+      <c r="E2245">
+        <v>48</v>
+      </c>
+      <c r="F2245">
+        <v>63.41</v>
+      </c>
+      <c r="G2245">
+        <v>63.79</v>
+      </c>
+      <c r="H2245">
+        <v>62</v>
+      </c>
+      <c r="I2245">
+        <v>49.09</v>
+      </c>
+      <c r="J2245" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2245" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2245">
+        <v>3</v>
+      </c>
+      <c r="M2245">
+        <v>2</v>
+      </c>
+      <c r="N2245">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:14" ht="15" customHeight="1">
+      <c r="A2246" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>770</v>
+      </c>
+      <c r="C2246" t="s">
+        <v>982</v>
+      </c>
+      <c r="D2246">
+        <v>340</v>
+      </c>
+      <c r="E2246">
+        <v>64</v>
+      </c>
+      <c r="F2246">
+        <v>73.17</v>
+      </c>
+      <c r="G2246">
+        <v>67.239999999999995</v>
+      </c>
+      <c r="H2246">
+        <v>68</v>
+      </c>
+      <c r="I2246">
+        <v>65.45</v>
+      </c>
+      <c r="J2246" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2246" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2246">
+        <v>4</v>
+      </c>
+      <c r="M2246">
+        <v>3</v>
+      </c>
+      <c r="N2246">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:14" ht="15" customHeight="1">
+      <c r="A2247" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2247" t="s">
+        <v>771</v>
+      </c>
+      <c r="C2247" t="s">
+        <v>983</v>
+      </c>
+      <c r="D2247">
+        <v>290</v>
+      </c>
+      <c r="E2247">
+        <v>68</v>
+      </c>
+      <c r="F2247">
+        <v>46.34</v>
+      </c>
+      <c r="G2247">
+        <v>58.62</v>
+      </c>
+      <c r="H2247">
+        <v>62</v>
+      </c>
+      <c r="I2247">
+        <v>49.09</v>
+      </c>
+      <c r="J2247" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2247" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2247">
+        <v>2</v>
+      </c>
+      <c r="M2247">
+        <v>3</v>
+      </c>
+      <c r="N2247">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:14" ht="15" customHeight="1">
+      <c r="A2248" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>754</v>
+      </c>
+      <c r="C2248" t="s">
+        <v>755</v>
+      </c>
+      <c r="D2248">
+        <v>351</v>
+      </c>
+      <c r="E2248">
+        <v>62</v>
+      </c>
+      <c r="F2248">
+        <v>75.61</v>
+      </c>
+      <c r="G2248">
+        <v>67.239999999999995</v>
+      </c>
+      <c r="H2248">
+        <v>82</v>
+      </c>
+      <c r="I2248">
+        <v>50.91</v>
+      </c>
+      <c r="J2248" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2248" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2248">
+        <v>4</v>
+      </c>
+      <c r="M2248">
+        <v>3</v>
+      </c>
+      <c r="N2248">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:14" ht="15" customHeight="1">
+      <c r="A2249" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2249" t="s">
+        <v>781</v>
+      </c>
+      <c r="C2249" t="s">
+        <v>984</v>
+      </c>
+      <c r="D2249">
+        <v>276</v>
+      </c>
+      <c r="E2249">
+        <v>52</v>
+      </c>
+      <c r="F2249">
+        <v>56.1</v>
+      </c>
+      <c r="G2249">
+        <v>43.1</v>
+      </c>
+      <c r="H2249">
+        <v>64</v>
+      </c>
+      <c r="I2249">
+        <v>70.91</v>
+      </c>
+      <c r="J2249" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2249" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2249">
+        <v>3</v>
+      </c>
+      <c r="M2249">
+        <v>3</v>
+      </c>
+      <c r="N2249">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:14" ht="15" customHeight="1">
+      <c r="A2250" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>817</v>
+      </c>
+      <c r="C2250" t="s">
+        <v>987</v>
+      </c>
+      <c r="D2250">
+        <v>260</v>
+      </c>
+      <c r="E2250">
+        <v>46</v>
+      </c>
+      <c r="F2250">
+        <v>41.46</v>
+      </c>
+      <c r="G2250">
+        <v>50</v>
+      </c>
+      <c r="H2250">
+        <v>66</v>
+      </c>
+      <c r="I2250">
+        <v>63.64</v>
+      </c>
+      <c r="J2250" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2250" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2250">
+        <v>2</v>
+      </c>
+      <c r="M2250">
+        <v>2</v>
+      </c>
+      <c r="N2250">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:14" ht="15" customHeight="1">
+      <c r="A2251" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2251" t="s">
+        <v>804</v>
+      </c>
+      <c r="C2251" t="s">
+        <v>805</v>
+      </c>
+      <c r="D2251">
+        <v>274</v>
+      </c>
+      <c r="E2251">
+        <v>48</v>
+      </c>
+      <c r="F2251">
+        <v>58.54</v>
+      </c>
+      <c r="G2251">
+        <v>46.55</v>
+      </c>
+      <c r="H2251">
+        <v>54</v>
+      </c>
+      <c r="I2251">
+        <v>89.09</v>
+      </c>
+      <c r="J2251" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2251" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2251">
+        <v>3</v>
+      </c>
+      <c r="M2251">
+        <v>2</v>
+      </c>
+      <c r="N2251">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:14" ht="15" customHeight="1">
+      <c r="A2252" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2252" t="s">
+        <v>812</v>
+      </c>
+      <c r="C2252" t="s">
+        <v>989</v>
+      </c>
+      <c r="D2252">
+        <v>341</v>
+      </c>
+      <c r="E2252">
+        <v>56</v>
+      </c>
+      <c r="F2252">
+        <v>73.17</v>
+      </c>
+      <c r="G2252">
+        <v>46.55</v>
+      </c>
+      <c r="H2252">
+        <v>88</v>
+      </c>
+      <c r="I2252">
+        <v>94.55</v>
+      </c>
+      <c r="J2252" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2252" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2252">
+        <v>4</v>
+      </c>
+      <c r="M2252">
+        <v>3</v>
+      </c>
+      <c r="N2252">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:14" ht="15" customHeight="1">
+      <c r="A2253" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2253" t="s">
+        <v>824</v>
+      </c>
+      <c r="C2253" t="s">
+        <v>990</v>
+      </c>
+      <c r="D2253">
+        <v>222</v>
+      </c>
+      <c r="E2253">
+        <v>46</v>
+      </c>
+      <c r="F2253">
+        <v>58.54</v>
+      </c>
+      <c r="G2253">
+        <v>29.31</v>
+      </c>
+      <c r="H2253">
+        <v>42</v>
+      </c>
+      <c r="I2253">
+        <v>49.09</v>
+      </c>
+      <c r="J2253" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2253" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2253">
+        <v>3</v>
+      </c>
+      <c r="M2253">
+        <v>2</v>
+      </c>
+      <c r="N2253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:14" ht="15" customHeight="1">
+      <c r="A2254" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>832</v>
+      </c>
+      <c r="C2254" t="s">
+        <v>833</v>
+      </c>
+      <c r="D2254">
+        <v>276</v>
+      </c>
+      <c r="E2254">
+        <v>56</v>
+      </c>
+      <c r="F2254">
+        <v>43.9</v>
+      </c>
+      <c r="G2254">
+        <v>44.83</v>
+      </c>
+      <c r="H2254">
+        <v>66</v>
+      </c>
+      <c r="I2254">
+        <v>83.64</v>
+      </c>
+      <c r="J2254" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2254" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2254">
+        <v>2</v>
+      </c>
+      <c r="M2254">
+        <v>3</v>
+      </c>
+      <c r="N2254">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:14" ht="15" customHeight="1">
+      <c r="A2255" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2255" t="s">
+        <v>843</v>
+      </c>
+      <c r="C2255" t="s">
+        <v>991</v>
+      </c>
+      <c r="D2255">
+        <v>228</v>
+      </c>
+      <c r="E2255">
+        <v>46</v>
+      </c>
+      <c r="F2255">
+        <v>26.83</v>
+      </c>
+      <c r="G2255">
+        <v>32.76</v>
+      </c>
+      <c r="H2255">
+        <v>70</v>
+      </c>
+      <c r="I2255">
+        <v>63.64</v>
+      </c>
+      <c r="J2255" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2255" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2255">
+        <v>1</v>
+      </c>
+      <c r="M2255">
+        <v>2</v>
+      </c>
+      <c r="N2255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:14" ht="15" customHeight="1">
+      <c r="A2256" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2256" t="s">
+        <v>806</v>
+      </c>
+      <c r="C2256" t="s">
+        <v>807</v>
+      </c>
+      <c r="D2256">
+        <v>381</v>
+      </c>
+      <c r="E2256">
+        <v>54</v>
+      </c>
+      <c r="F2256">
+        <v>87.8</v>
+      </c>
+      <c r="G2256">
+        <v>77.59</v>
+      </c>
+      <c r="H2256">
+        <v>80</v>
+      </c>
+      <c r="I2256">
+        <v>90.91</v>
+      </c>
+      <c r="J2256" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2256" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2256">
+        <v>4</v>
+      </c>
+      <c r="M2256">
+        <v>3</v>
+      </c>
+      <c r="N2256">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:14" ht="15" customHeight="1">
+      <c r="A2257" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2257" t="s">
+        <v>838</v>
+      </c>
+      <c r="C2257" t="s">
+        <v>992</v>
+      </c>
+      <c r="D2257">
+        <v>250</v>
+      </c>
+      <c r="E2257">
+        <v>32</v>
+      </c>
+      <c r="F2257">
+        <v>58.54</v>
+      </c>
+      <c r="G2257">
+        <v>50</v>
+      </c>
+      <c r="H2257">
+        <v>58</v>
+      </c>
+      <c r="I2257">
+        <v>52.73</v>
+      </c>
+      <c r="J2257" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2257" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2257">
+        <v>3</v>
+      </c>
+      <c r="M2257">
+        <v>1</v>
+      </c>
+      <c r="N2257">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:14" ht="15" customHeight="1">
+      <c r="A2258" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2258" t="s">
+        <v>803</v>
+      </c>
+      <c r="C2258" t="s">
+        <v>993</v>
+      </c>
+      <c r="D2258">
+        <v>323</v>
+      </c>
+      <c r="E2258">
+        <v>50</v>
+      </c>
+      <c r="F2258">
+        <v>73.17</v>
+      </c>
+      <c r="G2258">
+        <v>48.28</v>
+      </c>
+      <c r="H2258">
+        <v>78</v>
+      </c>
+      <c r="I2258">
+        <v>90.91</v>
+      </c>
+      <c r="J2258" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2258" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2258">
+        <v>4</v>
+      </c>
+      <c r="M2258">
+        <v>2</v>
+      </c>
+      <c r="N2258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:14" ht="15" customHeight="1">
+      <c r="A2259" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2259" t="s">
+        <v>995</v>
+      </c>
+      <c r="C2259" t="s">
+        <v>996</v>
+      </c>
+      <c r="D2259">
+        <v>243</v>
+      </c>
+      <c r="E2259">
+        <v>38</v>
+      </c>
+      <c r="F2259">
+        <v>51.22</v>
+      </c>
+      <c r="G2259">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H2259">
+        <v>64</v>
+      </c>
+      <c r="I2259">
+        <v>52.73</v>
+      </c>
+      <c r="J2259" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2259" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2259">
+        <v>3</v>
+      </c>
+      <c r="M2259">
+        <v>2</v>
+      </c>
+      <c r="N2259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:14" ht="15" customHeight="1">
+      <c r="A2260" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2260" t="s">
+        <v>826</v>
+      </c>
+      <c r="C2260" t="s">
+        <v>997</v>
+      </c>
+      <c r="D2260">
+        <v>279</v>
+      </c>
+      <c r="E2260">
+        <v>54</v>
+      </c>
+      <c r="F2260">
+        <v>53.66</v>
+      </c>
+      <c r="G2260">
+        <v>43.1</v>
+      </c>
+      <c r="H2260">
+        <v>66</v>
+      </c>
+      <c r="I2260">
+        <v>72.73</v>
+      </c>
+      <c r="J2260" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2260" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2260">
+        <v>3</v>
+      </c>
+      <c r="M2260">
+        <v>3</v>
+      </c>
+      <c r="N2260">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:14" ht="15" customHeight="1">
+      <c r="A2261" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2261" t="s">
+        <v>813</v>
+      </c>
+      <c r="C2261" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D2261">
+        <v>270</v>
+      </c>
+      <c r="E2261">
+        <v>56</v>
+      </c>
+      <c r="F2261">
+        <v>48.78</v>
+      </c>
+      <c r="G2261">
+        <v>41.38</v>
+      </c>
+      <c r="H2261">
+        <v>62</v>
+      </c>
+      <c r="I2261">
+        <v>76.36</v>
+      </c>
+      <c r="J2261" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2261" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2261">
+        <v>2</v>
+      </c>
+      <c r="M2261">
+        <v>3</v>
+      </c>
+      <c r="N2261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:14" ht="15" customHeight="1">
+      <c r="A2262" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>872</v>
+      </c>
+      <c r="C2262" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D2262">
+        <v>196</v>
+      </c>
+      <c r="E2262">
+        <v>34</v>
+      </c>
+      <c r="F2262">
+        <v>34.15</v>
+      </c>
+      <c r="G2262">
+        <v>46.55</v>
+      </c>
+      <c r="H2262">
+        <v>34</v>
+      </c>
+      <c r="I2262">
+        <v>61.82</v>
+      </c>
+      <c r="J2262" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2262" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2262">
+        <v>1</v>
+      </c>
+      <c r="M2262">
+        <v>1</v>
+      </c>
+      <c r="N2262">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:14" ht="15" customHeight="1">
+      <c r="A2263" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2263" t="s">
+        <v>808</v>
+      </c>
+      <c r="C2263" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D2263">
+        <v>298</v>
+      </c>
+      <c r="E2263">
+        <v>40</v>
+      </c>
+      <c r="F2263">
+        <v>75.61</v>
+      </c>
+      <c r="G2263">
+        <v>48.28</v>
+      </c>
+      <c r="H2263">
+        <v>76</v>
+      </c>
+      <c r="I2263">
+        <v>52.73</v>
+      </c>
+      <c r="J2263" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2263" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2263">
+        <v>4</v>
+      </c>
+      <c r="M2263">
+        <v>2</v>
+      </c>
+      <c r="N2263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:14" ht="15" customHeight="1">
+      <c r="A2264" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2264" t="s">
+        <v>818</v>
+      </c>
+      <c r="C2264" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D2264">
+        <v>340</v>
+      </c>
+      <c r="E2264">
+        <v>46</v>
+      </c>
+      <c r="F2264">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2264">
+        <v>55.17</v>
+      </c>
+      <c r="H2264">
+        <v>94</v>
+      </c>
+      <c r="I2264">
+        <v>92.73</v>
+      </c>
+      <c r="J2264" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2264" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2264">
+        <v>4</v>
+      </c>
+      <c r="M2264">
+        <v>2</v>
+      </c>
+      <c r="N2264">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:14" ht="15" customHeight="1">
+      <c r="A2265" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2265" t="s">
+        <v>809</v>
+      </c>
+      <c r="C2265" t="s">
+        <v>810</v>
+      </c>
+      <c r="D2265">
+        <v>285</v>
+      </c>
+      <c r="E2265">
+        <v>50</v>
+      </c>
+      <c r="F2265">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2265">
+        <v>41.38</v>
+      </c>
+      <c r="H2265">
+        <v>68</v>
+      </c>
+      <c r="I2265">
+        <v>63.64</v>
+      </c>
+      <c r="J2265" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2265" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2265">
+        <v>3</v>
+      </c>
+      <c r="M2265">
+        <v>2</v>
+      </c>
+      <c r="N2265">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:14" ht="15" customHeight="1">
+      <c r="A2266" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2266" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C2266" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D2266">
+        <v>282</v>
+      </c>
+      <c r="E2266">
+        <v>58</v>
+      </c>
+      <c r="F2266">
+        <v>51.22</v>
+      </c>
+      <c r="G2266">
+        <v>44.83</v>
+      </c>
+      <c r="H2266">
+        <v>68</v>
+      </c>
+      <c r="I2266">
+        <v>65.45</v>
+      </c>
+      <c r="J2266" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2266" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2266">
+        <v>3</v>
+      </c>
+      <c r="M2266">
+        <v>3</v>
+      </c>
+      <c r="N2266">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:14" ht="15" customHeight="1">
+      <c r="A2267" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2267" t="s">
+        <v>834</v>
+      </c>
+      <c r="C2267" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D2267">
+        <v>278</v>
+      </c>
+      <c r="E2267">
+        <v>50</v>
+      </c>
+      <c r="F2267">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2267">
+        <v>41.38</v>
+      </c>
+      <c r="H2267">
+        <v>64</v>
+      </c>
+      <c r="I2267">
+        <v>58.18</v>
+      </c>
+      <c r="J2267" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2267" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2267">
+        <v>3</v>
+      </c>
+      <c r="M2267">
+        <v>2</v>
+      </c>
+      <c r="N2267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:14" ht="15" customHeight="1">
+      <c r="A2268" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2268" t="s">
+        <v>837</v>
+      </c>
+      <c r="C2268" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D2268">
+        <v>187</v>
+      </c>
+      <c r="E2268">
+        <v>46</v>
+      </c>
+      <c r="F2268">
+        <v>34.15</v>
+      </c>
+      <c r="G2268">
+        <v>25.86</v>
+      </c>
+      <c r="H2268">
+        <v>42</v>
+      </c>
+      <c r="I2268">
+        <v>41.82</v>
+      </c>
+      <c r="J2268" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2268" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2268">
+        <v>1</v>
+      </c>
+      <c r="M2268">
+        <v>2</v>
+      </c>
+      <c r="N2268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:14" ht="15" customHeight="1">
+      <c r="A2269" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2269" t="s">
+        <v>815</v>
+      </c>
+      <c r="C2269" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D2269">
+        <v>332</v>
+      </c>
+      <c r="E2269">
+        <v>56</v>
+      </c>
+      <c r="F2269">
+        <v>73.17</v>
+      </c>
+      <c r="G2269">
+        <v>56.9</v>
+      </c>
+      <c r="H2269">
+        <v>82</v>
+      </c>
+      <c r="I2269">
+        <v>58.18</v>
+      </c>
+      <c r="J2269" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2269" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2269">
+        <v>4</v>
+      </c>
+      <c r="M2269">
+        <v>3</v>
+      </c>
+      <c r="N2269">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:14" ht="15" customHeight="1">
+      <c r="A2270" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2270" t="s">
+        <v>828</v>
+      </c>
+      <c r="C2270" t="s">
+        <v>829</v>
+      </c>
+      <c r="D2270">
+        <v>266</v>
+      </c>
+      <c r="E2270">
+        <v>48</v>
+      </c>
+      <c r="F2270">
+        <v>46.34</v>
+      </c>
+      <c r="G2270">
+        <v>56.9</v>
+      </c>
+      <c r="H2270">
+        <v>62</v>
+      </c>
+      <c r="I2270">
+        <v>50.91</v>
+      </c>
+      <c r="J2270" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2270" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2270">
+        <v>2</v>
+      </c>
+      <c r="M2270">
+        <v>2</v>
+      </c>
+      <c r="N2270">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:14" ht="15" customHeight="1">
+      <c r="A2271" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2271" t="s">
+        <v>811</v>
+      </c>
+      <c r="C2271" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D2271">
+        <v>283</v>
+      </c>
+      <c r="E2271">
+        <v>48</v>
+      </c>
+      <c r="F2271">
+        <v>43.9</v>
+      </c>
+      <c r="G2271">
+        <v>46.55</v>
+      </c>
+      <c r="H2271">
+        <v>80</v>
+      </c>
+      <c r="I2271">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2271" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2271" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2271">
+        <v>2</v>
+      </c>
+      <c r="M2271">
+        <v>2</v>
+      </c>
+      <c r="N2271">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:14" ht="15" customHeight="1">
+      <c r="A2272" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2272" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2272" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D2272">
+        <v>258</v>
+      </c>
+      <c r="E2272">
+        <v>44</v>
+      </c>
+      <c r="F2272">
+        <v>56.1</v>
+      </c>
+      <c r="G2272">
+        <v>36.21</v>
+      </c>
+      <c r="H2272">
+        <v>64</v>
+      </c>
+      <c r="I2272">
+        <v>69.09</v>
+      </c>
+      <c r="J2272" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2272" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2272">
+        <v>3</v>
+      </c>
+      <c r="M2272">
+        <v>2</v>
+      </c>
+      <c r="N2272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:14" ht="15" customHeight="1">
+      <c r="A2273" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2273" t="s">
+        <v>822</v>
+      </c>
+      <c r="C2273" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D2273">
+        <v>264</v>
+      </c>
+      <c r="E2273">
+        <v>56</v>
+      </c>
+      <c r="F2273">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G2273">
+        <v>46.55</v>
+      </c>
+      <c r="H2273">
+        <v>64</v>
+      </c>
+      <c r="I2273">
+        <v>69.09</v>
+      </c>
+      <c r="J2273" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2273" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2273">
+        <v>2</v>
+      </c>
+      <c r="M2273">
+        <v>3</v>
+      </c>
+      <c r="N2273">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:14" ht="15" customHeight="1">
+      <c r="A2274" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2274" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C2274" t="s">
+        <v>840</v>
+      </c>
+      <c r="D2274">
+        <v>212</v>
+      </c>
+      <c r="E2274">
+        <v>30</v>
+      </c>
+      <c r="F2274">
+        <v>46.34</v>
+      </c>
+      <c r="G2274">
+        <v>37.93</v>
+      </c>
+      <c r="H2274">
+        <v>44</v>
+      </c>
+      <c r="I2274">
+        <v>74.55</v>
+      </c>
+      <c r="J2274" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2274" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2274">
+        <v>2</v>
+      </c>
+      <c r="M2274">
+        <v>1</v>
+      </c>
+      <c r="N2274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:14" ht="15" customHeight="1">
+      <c r="A2275" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2275" t="s">
+        <v>821</v>
+      </c>
+      <c r="C2275" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D2275">
+        <v>336</v>
+      </c>
+      <c r="E2275">
+        <v>50</v>
+      </c>
+      <c r="F2275">
+        <v>78.05</v>
+      </c>
+      <c r="G2275">
+        <v>65.52</v>
+      </c>
+      <c r="H2275">
+        <v>78</v>
+      </c>
+      <c r="I2275">
+        <v>58.18</v>
+      </c>
+      <c r="J2275" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2275" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2275">
+        <v>4</v>
+      </c>
+      <c r="M2275">
+        <v>2</v>
+      </c>
+      <c r="N2275">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:14" ht="15" customHeight="1">
+      <c r="A2276" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2276" t="s">
+        <v>879</v>
+      </c>
+      <c r="C2276" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D2276">
+        <v>230</v>
+      </c>
+      <c r="E2276">
+        <v>18</v>
+      </c>
+      <c r="F2276">
+        <v>56.1</v>
+      </c>
+      <c r="G2276">
+        <v>37.93</v>
+      </c>
+      <c r="H2276">
+        <v>60</v>
+      </c>
+      <c r="I2276">
+        <v>80</v>
+      </c>
+      <c r="J2276" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2276" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2276">
+        <v>3</v>
+      </c>
+      <c r="M2276">
+        <v>1</v>
+      </c>
+      <c r="N2276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:14" ht="15" customHeight="1">
+      <c r="A2277" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2277" t="s">
+        <v>877</v>
+      </c>
+      <c r="C2277" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D2277">
+        <v>276</v>
+      </c>
+      <c r="E2277">
+        <v>64</v>
+      </c>
+      <c r="F2277">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="G2277">
+        <v>46.55</v>
+      </c>
+      <c r="H2277">
+        <v>64</v>
+      </c>
+      <c r="I2277">
+        <v>74.55</v>
+      </c>
+      <c r="J2277" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2277" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2277">
+        <v>2</v>
+      </c>
+      <c r="M2277">
+        <v>3</v>
+      </c>
+      <c r="N2277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:14" ht="15" customHeight="1">
+      <c r="A2278" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2278" t="s">
+        <v>878</v>
+      </c>
+      <c r="C2278" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D2278">
+        <v>317</v>
+      </c>
+      <c r="E2278">
+        <v>52</v>
+      </c>
+      <c r="F2278">
+        <v>73.17</v>
+      </c>
+      <c r="G2278">
+        <v>51.72</v>
+      </c>
+      <c r="H2278">
+        <v>76</v>
+      </c>
+      <c r="I2278">
+        <v>65.45</v>
+      </c>
+      <c r="J2278" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2278" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2278">
+        <v>4</v>
+      </c>
+      <c r="M2278">
+        <v>3</v>
+      </c>
+      <c r="N2278">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:14" ht="15" customHeight="1">
+      <c r="A2279" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2279" t="s">
+        <v>860</v>
+      </c>
+      <c r="C2279" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D2279">
+        <v>329</v>
+      </c>
+      <c r="E2279">
+        <v>46</v>
+      </c>
+      <c r="F2279">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2279">
+        <v>56.9</v>
+      </c>
+      <c r="H2279">
+        <v>86</v>
+      </c>
+      <c r="I2279">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="J2279" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2279" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2279">
+        <v>4</v>
+      </c>
+      <c r="M2279">
+        <v>2</v>
+      </c>
+      <c r="N2279">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:14" ht="15" customHeight="1">
+      <c r="A2280" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2280" t="s">
+        <v>849</v>
+      </c>
+      <c r="C2280" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D2280">
+        <v>302</v>
+      </c>
+      <c r="E2280">
+        <v>34</v>
+      </c>
+      <c r="F2280">
+        <v>63.41</v>
+      </c>
+      <c r="G2280">
+        <v>56.9</v>
+      </c>
+      <c r="H2280">
+        <v>80</v>
+      </c>
+      <c r="I2280">
+        <v>80</v>
+      </c>
+      <c r="J2280" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2280" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2280">
+        <v>3</v>
+      </c>
+      <c r="M2280">
+        <v>1</v>
+      </c>
+      <c r="N2280">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:14" ht="15" customHeight="1">
+      <c r="A2281" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2281" t="s">
+        <v>853</v>
+      </c>
+      <c r="C2281" t="s">
+        <v>854</v>
+      </c>
+      <c r="D2281">
+        <v>277</v>
+      </c>
+      <c r="E2281">
+        <v>34</v>
+      </c>
+      <c r="F2281">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2281">
+        <v>46.55</v>
+      </c>
+      <c r="H2281">
+        <v>66</v>
+      </c>
+      <c r="I2281">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="J2281" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2281" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2281">
+        <v>3</v>
+      </c>
+      <c r="M2281">
+        <v>1</v>
+      </c>
+      <c r="N2281">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:14" ht="15" customHeight="1">
+      <c r="A2282" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2282" t="s">
+        <v>850</v>
+      </c>
+      <c r="C2282" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D2282">
+        <v>272</v>
+      </c>
+      <c r="E2282">
+        <v>34</v>
+      </c>
+      <c r="F2282">
+        <v>63.41</v>
+      </c>
+      <c r="G2282">
+        <v>37.93</v>
+      </c>
+      <c r="H2282">
+        <v>76</v>
+      </c>
+      <c r="I2282">
+        <v>72.73</v>
+      </c>
+      <c r="J2282" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2282" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2282">
+        <v>3</v>
+      </c>
+      <c r="M2282">
+        <v>1</v>
+      </c>
+      <c r="N2282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:14" ht="15" customHeight="1">
+      <c r="A2283" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2283" t="s">
+        <v>856</v>
+      </c>
+      <c r="C2283" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D2283">
+        <v>302</v>
+      </c>
+      <c r="E2283">
+        <v>40</v>
+      </c>
+      <c r="F2283">
+        <v>70.73</v>
+      </c>
+      <c r="G2283">
+        <v>50</v>
+      </c>
+      <c r="H2283">
+        <v>70</v>
+      </c>
+      <c r="I2283">
+        <v>92.73</v>
+      </c>
+      <c r="J2283" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2283" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2283">
+        <v>4</v>
+      </c>
+      <c r="M2283">
+        <v>2</v>
+      </c>
+      <c r="N2283">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:14" ht="15" customHeight="1">
+      <c r="A2284" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2284" t="s">
+        <v>857</v>
+      </c>
+      <c r="C2284" t="s">
+        <v>858</v>
+      </c>
+      <c r="D2284">
+        <v>243</v>
+      </c>
+      <c r="E2284">
+        <v>36</v>
+      </c>
+      <c r="F2284">
+        <v>58.54</v>
+      </c>
+      <c r="G2284">
+        <v>44.83</v>
+      </c>
+      <c r="H2284">
+        <v>52</v>
+      </c>
+      <c r="I2284">
+        <v>56.36</v>
+      </c>
+      <c r="J2284" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2284" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2284">
+        <v>3</v>
+      </c>
+      <c r="M2284">
+        <v>2</v>
+      </c>
+      <c r="N2284">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:14" ht="15" customHeight="1">
+      <c r="A2285" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2285" t="s">
+        <v>873</v>
+      </c>
+      <c r="C2285" t="s">
+        <v>874</v>
+      </c>
+      <c r="D2285">
+        <v>321</v>
+      </c>
+      <c r="E2285">
+        <v>72</v>
+      </c>
+      <c r="F2285">
+        <v>60.98</v>
+      </c>
+      <c r="G2285">
+        <v>58.62</v>
+      </c>
+      <c r="H2285">
+        <v>58</v>
+      </c>
+      <c r="I2285">
+        <v>83.64</v>
+      </c>
+      <c r="J2285" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2285" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2285">
+        <v>3</v>
+      </c>
+      <c r="M2285">
+        <v>4</v>
+      </c>
+      <c r="N2285">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:14" ht="15" customHeight="1">
+      <c r="A2286" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2286" t="s">
+        <v>855</v>
+      </c>
+      <c r="C2286" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D2286">
+        <v>418</v>
+      </c>
+      <c r="E2286">
+        <v>76</v>
+      </c>
+      <c r="F2286">
+        <v>87.8</v>
+      </c>
+      <c r="G2286">
+        <v>81.03</v>
+      </c>
+      <c r="H2286">
+        <v>84</v>
+      </c>
+      <c r="I2286">
+        <v>98.18</v>
+      </c>
+      <c r="J2286" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2286" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2286">
+        <v>4</v>
+      </c>
+      <c r="M2286">
+        <v>4</v>
+      </c>
+      <c r="N2286">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:14" ht="15" customHeight="1">
+      <c r="A2287" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2287" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C2287" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D2287">
+        <v>149</v>
+      </c>
+      <c r="E2287">
+        <v>30</v>
+      </c>
+      <c r="F2287">
+        <v>29.27</v>
+      </c>
+      <c r="G2287">
+        <v>32.76</v>
+      </c>
+      <c r="H2287">
+        <v>28</v>
+      </c>
+      <c r="I2287">
+        <v>27.27</v>
+      </c>
+      <c r="J2287" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2287" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2287">
+        <v>1</v>
+      </c>
+      <c r="M2287">
+        <v>1</v>
+      </c>
+      <c r="N2287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:14" ht="15" customHeight="1">
+      <c r="A2288" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2288" t="s">
+        <v>882</v>
+      </c>
+      <c r="C2288" t="s">
+        <v>883</v>
+      </c>
+      <c r="D2288">
+        <v>272</v>
+      </c>
+      <c r="E2288">
+        <v>38</v>
+      </c>
+      <c r="F2288">
+        <v>63.41</v>
+      </c>
+      <c r="G2288">
+        <v>44.83</v>
+      </c>
+      <c r="H2288">
+        <v>64</v>
+      </c>
+      <c r="I2288">
+        <v>76.36</v>
+      </c>
+      <c r="J2288" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2288" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2288">
+        <v>3</v>
+      </c>
+      <c r="M2288">
+        <v>2</v>
+      </c>
+      <c r="N2288">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:14" ht="15" customHeight="1">
+      <c r="A2289" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2289" t="s">
+        <v>880</v>
+      </c>
+      <c r="C2289" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D2289">
+        <v>347</v>
+      </c>
+      <c r="E2289">
+        <v>52</v>
+      </c>
+      <c r="F2289">
+        <v>70.73</v>
+      </c>
+      <c r="G2289">
+        <v>70.69</v>
+      </c>
+      <c r="H2289">
+        <v>78</v>
+      </c>
+      <c r="I2289">
+        <v>85.45</v>
+      </c>
+      <c r="J2289" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2289" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2289">
+        <v>4</v>
+      </c>
+      <c r="M2289">
+        <v>3</v>
+      </c>
+      <c r="N2289">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:14" ht="15" customHeight="1">
+      <c r="A2290" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2290" t="s">
+        <v>851</v>
+      </c>
+      <c r="C2290" t="s">
+        <v>852</v>
+      </c>
+      <c r="D2290">
+        <v>283</v>
+      </c>
+      <c r="E2290">
+        <v>48</v>
+      </c>
+      <c r="F2290">
+        <v>51.22</v>
+      </c>
+      <c r="G2290">
+        <v>58.62</v>
+      </c>
+      <c r="H2290">
+        <v>66</v>
+      </c>
+      <c r="I2290">
+        <v>61.82</v>
+      </c>
+      <c r="J2290" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2290" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2290">
+        <v>3</v>
+      </c>
+      <c r="M2290">
+        <v>2</v>
+      </c>
+      <c r="N2290">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:14" ht="15" customHeight="1">
+      <c r="A2291" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2291" t="s">
+        <v>875</v>
+      </c>
+      <c r="C2291" t="s">
+        <v>876</v>
+      </c>
+      <c r="D2291">
+        <v>268</v>
+      </c>
+      <c r="E2291">
+        <v>52</v>
+      </c>
+      <c r="F2291">
+        <v>60.98</v>
+      </c>
+      <c r="G2291">
+        <v>53.45</v>
+      </c>
+      <c r="H2291">
+        <v>48</v>
+      </c>
+      <c r="I2291">
+        <v>52.73</v>
+      </c>
+      <c r="J2291" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2291" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2291">
+        <v>3</v>
+      </c>
+      <c r="M2291">
+        <v>3</v>
+      </c>
+      <c r="N2291">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:14" ht="15" customHeight="1">
+      <c r="A2292" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2292" t="s">
+        <v>846</v>
+      </c>
+      <c r="C2292" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D2292">
+        <v>310</v>
+      </c>
+      <c r="E2292">
+        <v>32</v>
+      </c>
+      <c r="F2292">
+        <v>70.73</v>
+      </c>
+      <c r="G2292">
+        <v>58.62</v>
+      </c>
+      <c r="H2292">
+        <v>76</v>
+      </c>
+      <c r="I2292">
+        <v>92.73</v>
+      </c>
+      <c r="J2292" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2292" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2292">
+        <v>4</v>
+      </c>
+      <c r="M2292">
+        <v>1</v>
+      </c>
+      <c r="N2292">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:14" ht="15" customHeight="1">
+      <c r="A2293" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2293" t="s">
+        <v>871</v>
+      </c>
+      <c r="C2293" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D2293">
+        <v>258</v>
+      </c>
+      <c r="E2293">
+        <v>38</v>
+      </c>
+      <c r="F2293">
+        <v>56.1</v>
+      </c>
+      <c r="G2293">
+        <v>51.72</v>
+      </c>
+      <c r="H2293">
+        <v>54</v>
+      </c>
+      <c r="I2293">
+        <v>69.09</v>
+      </c>
+      <c r="J2293" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2293" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2293">
+        <v>3</v>
+      </c>
+      <c r="M2293">
+        <v>2</v>
+      </c>
+      <c r="N2293">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:14" ht="15" customHeight="1">
+      <c r="A2294" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2294" t="s">
+        <v>998</v>
+      </c>
+      <c r="C2294" t="s">
+        <v>999</v>
+      </c>
+      <c r="D2294">
+        <v>390</v>
+      </c>
+      <c r="E2294">
+        <v>76</v>
+      </c>
+      <c r="F2294">
+        <v>87.8</v>
+      </c>
+      <c r="G2294">
+        <v>74.14</v>
+      </c>
+      <c r="H2294">
+        <v>84</v>
+      </c>
+      <c r="I2294">
+        <v>47.27</v>
+      </c>
+      <c r="J2294" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2294" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2294">
+        <v>4</v>
+      </c>
+      <c r="M2294">
+        <v>4</v>
+      </c>
+      <c r="N2294">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:14" ht="15" customHeight="1">
+      <c r="A2295" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2295" t="s">
+        <v>859</v>
+      </c>
+      <c r="C2295" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D2295">
+        <v>354</v>
+      </c>
+      <c r="E2295">
+        <v>70</v>
+      </c>
+      <c r="F2295">
+        <v>70.73</v>
+      </c>
+      <c r="G2295">
+        <v>65.52</v>
+      </c>
+      <c r="H2295">
+        <v>74</v>
+      </c>
+      <c r="I2295">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2295" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2295" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2295">
+        <v>4</v>
+      </c>
+      <c r="M2295">
+        <v>3</v>
+      </c>
+      <c r="N2295">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:14" ht="15" customHeight="1">
+      <c r="A2296" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2296" t="s">
+        <v>886</v>
+      </c>
+      <c r="C2296" t="s">
+        <v>887</v>
+      </c>
+      <c r="D2296">
+        <v>283</v>
+      </c>
+      <c r="E2296">
+        <v>60</v>
+      </c>
+      <c r="F2296">
+        <v>53.66</v>
+      </c>
+      <c r="G2296">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H2296">
+        <v>78</v>
+      </c>
+      <c r="I2296">
+        <v>41.82</v>
+      </c>
+      <c r="J2296" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2296" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2296">
+        <v>3</v>
+      </c>
+      <c r="M2296">
+        <v>3</v>
+      </c>
+      <c r="N2296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:14" ht="15" customHeight="1">
+      <c r="A2297" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2297" t="s">
+        <v>847</v>
+      </c>
+      <c r="C2297" t="s">
+        <v>848</v>
+      </c>
+      <c r="D2297">
+        <v>283</v>
+      </c>
+      <c r="E2297">
+        <v>52</v>
+      </c>
+      <c r="F2297">
+        <v>63.41</v>
+      </c>
+      <c r="G2297">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="H2297">
+        <v>72</v>
+      </c>
+      <c r="I2297">
+        <v>54.55</v>
+      </c>
+      <c r="J2297" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2297" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2297">
+        <v>3</v>
+      </c>
+      <c r="M2297">
+        <v>3</v>
+      </c>
+      <c r="N2297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:14" ht="15" customHeight="1">
+      <c r="A2298" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2298" t="s">
+        <v>869</v>
+      </c>
+      <c r="C2298" t="s">
+        <v>870</v>
+      </c>
+      <c r="D2298">
+        <v>226</v>
+      </c>
+      <c r="E2298">
+        <v>30</v>
+      </c>
+      <c r="F2298">
+        <v>53.66</v>
+      </c>
+      <c r="G2298">
+        <v>37.93</v>
+      </c>
+      <c r="H2298">
+        <v>54</v>
+      </c>
+      <c r="I2298">
+        <v>60</v>
+      </c>
+      <c r="J2298" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2298" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2298">
+        <v>3</v>
+      </c>
+      <c r="M2298">
+        <v>1</v>
+      </c>
+      <c r="N2298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:14" ht="15" customHeight="1">
+      <c r="A2299" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2299" t="s">
+        <v>844</v>
+      </c>
+      <c r="C2299" t="s">
+        <v>845</v>
+      </c>
+      <c r="D2299">
+        <v>305</v>
+      </c>
+      <c r="E2299">
+        <v>52</v>
+      </c>
+      <c r="F2299">
+        <v>63.41</v>
+      </c>
+      <c r="G2299">
+        <v>55.17</v>
+      </c>
+      <c r="H2299">
+        <v>72</v>
+      </c>
+      <c r="I2299">
+        <v>63.64</v>
+      </c>
+      <c r="J2299" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2299" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2299">
+        <v>3</v>
+      </c>
+      <c r="M2299">
+        <v>3</v>
+      </c>
+      <c r="N2299">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:14" ht="15" customHeight="1">
+      <c r="A2300" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2300" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C2300" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D2300">
+        <v>234</v>
+      </c>
+      <c r="E2300">
+        <v>34</v>
+      </c>
+      <c r="F2300">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2300">
+        <v>43.1</v>
+      </c>
+      <c r="H2300">
+        <v>44</v>
+      </c>
+      <c r="I2300">
+        <v>47.27</v>
+      </c>
+      <c r="J2300" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2300" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2300">
+        <v>3</v>
+      </c>
+      <c r="M2300">
+        <v>1</v>
+      </c>
+      <c r="N2300">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:14" ht="15" customHeight="1">
+      <c r="A2301" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2301" t="s">
+        <v>866</v>
+      </c>
+      <c r="C2301" t="s">
+        <v>867</v>
+      </c>
+      <c r="D2301">
+        <v>285</v>
+      </c>
+      <c r="E2301">
+        <v>40</v>
+      </c>
+      <c r="F2301">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="G2301">
+        <v>43.1</v>
+      </c>
+      <c r="H2301">
+        <v>80</v>
+      </c>
+      <c r="I2301">
+        <v>45.45</v>
+      </c>
+      <c r="J2301" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2301" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2301">
+        <v>4</v>
+      </c>
+      <c r="M2301">
+        <v>2</v>
+      </c>
+      <c r="N2301">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:14" ht="15" customHeight="1">
+      <c r="A2302" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2302" t="s">
+        <v>839</v>
+      </c>
+      <c r="C2302" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D2302">
+        <v>178</v>
+      </c>
+      <c r="E2302">
+        <v>26</v>
+      </c>
+      <c r="F2302">
+        <v>60.98</v>
+      </c>
+      <c r="G2302">
+        <v>20.69</v>
+      </c>
+      <c r="H2302">
+        <v>46</v>
+      </c>
+      <c r="I2302">
+        <v>0</v>
+      </c>
+      <c r="J2302" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2302" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2302">
+        <v>3</v>
+      </c>
+      <c r="M2302">
+        <v>1</v>
+      </c>
+      <c r="N2302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:14" ht="15" customHeight="1">
+      <c r="A2303" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2303" t="s">
+        <v>884</v>
+      </c>
+      <c r="C2303" t="s">
+        <v>885</v>
+      </c>
+      <c r="D2303">
+        <v>204</v>
+      </c>
+      <c r="E2303">
+        <v>20</v>
+      </c>
+      <c r="F2303">
+        <v>48.78</v>
+      </c>
+      <c r="G2303">
+        <v>43.1</v>
+      </c>
+      <c r="H2303">
+        <v>56</v>
+      </c>
+      <c r="I2303">
+        <v>25.45</v>
+      </c>
+      <c r="J2303" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2303" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2303">
+        <v>2</v>
+      </c>
+      <c r="M2303">
+        <v>1</v>
+      </c>
+      <c r="N2303">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:14" ht="15" customHeight="1">
+      <c r="A2304" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2304" t="s">
+        <v>861</v>
+      </c>
+      <c r="C2304" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D2304">
+        <v>283</v>
+      </c>
+      <c r="E2304">
+        <v>38</v>
+      </c>
+      <c r="F2304">
+        <v>58.54</v>
+      </c>
+      <c r="G2304">
+        <v>55.17</v>
+      </c>
+      <c r="H2304">
+        <v>74</v>
+      </c>
+      <c r="I2304">
+        <v>58.18</v>
+      </c>
+      <c r="J2304" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2304" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2304">
+        <v>3</v>
+      </c>
+      <c r="M2304">
+        <v>2</v>
+      </c>
+      <c r="N2304">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:14" ht="15" customHeight="1">
+      <c r="A2305" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2305" t="s">
+        <v>925</v>
+      </c>
+      <c r="C2305" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D2305">
+        <v>250</v>
+      </c>
+      <c r="E2305">
+        <v>40</v>
+      </c>
+      <c r="F2305">
+        <v>58.54</v>
+      </c>
+      <c r="G2305">
+        <v>48.28</v>
+      </c>
+      <c r="H2305">
+        <v>64</v>
+      </c>
+      <c r="I2305">
+        <v>16.36</v>
+      </c>
+      <c r="J2305" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2305" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2305">
+        <v>3</v>
+      </c>
+      <c r="M2305">
+        <v>2</v>
+      </c>
+      <c r="N2305">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:14" ht="15" customHeight="1">
+      <c r="A2306" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2306" t="s">
+        <v>901</v>
+      </c>
+      <c r="C2306" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D2306">
+        <v>286</v>
+      </c>
+      <c r="E2306">
+        <v>44</v>
+      </c>
+      <c r="F2306">
+        <v>58.54</v>
+      </c>
+      <c r="G2306">
+        <v>58.62</v>
+      </c>
+      <c r="H2306">
+        <v>58</v>
+      </c>
+      <c r="I2306">
+        <v>85.45</v>
+      </c>
+      <c r="J2306" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2306" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2306">
+        <v>3</v>
+      </c>
+      <c r="M2306">
+        <v>2</v>
+      </c>
+      <c r="N2306">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:14" ht="15" customHeight="1">
+      <c r="A2307" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2307" t="s">
+        <v>918</v>
+      </c>
+      <c r="C2307" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D2307">
+        <v>304</v>
+      </c>
+      <c r="E2307">
+        <v>50</v>
+      </c>
+      <c r="F2307">
+        <v>73.17</v>
+      </c>
+      <c r="G2307">
+        <v>65.52</v>
+      </c>
+      <c r="H2307">
+        <v>48</v>
+      </c>
+      <c r="I2307">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2307" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2307" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2307">
+        <v>4</v>
+      </c>
+      <c r="M2307">
+        <v>2</v>
+      </c>
+      <c r="N2307">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:14" ht="15" customHeight="1">
+      <c r="A2308" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2308" t="s">
+        <v>898</v>
+      </c>
+      <c r="C2308" t="s">
+        <v>899</v>
+      </c>
+      <c r="D2308">
+        <v>254</v>
+      </c>
+      <c r="E2308">
+        <v>58</v>
+      </c>
+      <c r="F2308">
+        <v>60.98</v>
+      </c>
+      <c r="G2308">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="H2308">
+        <v>52</v>
+      </c>
+      <c r="I2308">
+        <v>43.64</v>
+      </c>
+      <c r="J2308" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2308" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2308">
+        <v>3</v>
+      </c>
+      <c r="M2308">
+        <v>3</v>
+      </c>
+      <c r="N2308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:14" ht="15" customHeight="1">
+      <c r="A2309" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2309" t="s">
+        <v>888</v>
+      </c>
+      <c r="C2309" t="s">
+        <v>889</v>
+      </c>
+      <c r="D2309">
+        <v>419</v>
+      </c>
+      <c r="E2309">
+        <v>70</v>
+      </c>
+      <c r="F2309">
+        <v>90.24</v>
+      </c>
+      <c r="G2309">
+        <v>79.31</v>
+      </c>
+      <c r="H2309">
+        <v>90</v>
+      </c>
+      <c r="I2309">
+        <v>98.18</v>
+      </c>
+      <c r="J2309" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2309" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2309">
+        <v>4</v>
+      </c>
+      <c r="M2309">
+        <v>3</v>
+      </c>
+      <c r="N2309">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:14" ht="15" customHeight="1">
+      <c r="A2310" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2310" t="s">
+        <v>892</v>
+      </c>
+      <c r="C2310" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D2310">
+        <v>187</v>
+      </c>
+      <c r="E2310">
+        <v>38</v>
+      </c>
+      <c r="F2310">
+        <v>34.15</v>
+      </c>
+      <c r="G2310">
+        <v>32.76</v>
+      </c>
+      <c r="H2310">
+        <v>46</v>
+      </c>
+      <c r="I2310">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J2310" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2310" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2310">
+        <v>1</v>
+      </c>
+      <c r="M2310">
+        <v>2</v>
+      </c>
+      <c r="N2310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:14" ht="15" customHeight="1">
+      <c r="A2311" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2311" t="s">
+        <v>926</v>
+      </c>
+      <c r="C2311" t="s">
+        <v>927</v>
+      </c>
+      <c r="D2311">
+        <v>208</v>
+      </c>
+      <c r="E2311">
+        <v>22</v>
+      </c>
+      <c r="F2311">
+        <v>46.34</v>
+      </c>
+      <c r="G2311">
+        <v>46.55</v>
+      </c>
+      <c r="H2311">
+        <v>58</v>
+      </c>
+      <c r="I2311">
+        <v>21.82</v>
+      </c>
+      <c r="J2311" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2311" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2311">
+        <v>2</v>
+      </c>
+      <c r="M2311">
+        <v>1</v>
+      </c>
+      <c r="N2311">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:14" ht="15" customHeight="1">
+      <c r="A2312" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2312" t="s">
+        <v>896</v>
+      </c>
+      <c r="C2312" t="s">
+        <v>897</v>
+      </c>
+      <c r="D2312">
+        <v>250</v>
+      </c>
+      <c r="E2312">
+        <v>40</v>
+      </c>
+      <c r="F2312">
+        <v>51.22</v>
+      </c>
+      <c r="G2312">
+        <v>41.38</v>
+      </c>
+      <c r="H2312">
+        <v>62</v>
+      </c>
+      <c r="I2312">
+        <v>63.64</v>
+      </c>
+      <c r="J2312" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2312" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2312">
+        <v>3</v>
+      </c>
+      <c r="M2312">
+        <v>2</v>
+      </c>
+      <c r="N2312">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:14" ht="15" customHeight="1">
+      <c r="A2313" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2313" t="s">
+        <v>911</v>
+      </c>
+      <c r="C2313" t="s">
+        <v>912</v>
+      </c>
+      <c r="D2313">
+        <v>209</v>
+      </c>
+      <c r="E2313">
+        <v>36</v>
+      </c>
+      <c r="F2313">
+        <v>63.41</v>
+      </c>
+      <c r="G2313">
+        <v>22.41</v>
+      </c>
+      <c r="H2313">
+        <v>50</v>
+      </c>
+      <c r="I2313">
+        <v>25.45</v>
+      </c>
+      <c r="J2313" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2313" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2313">
+        <v>3</v>
+      </c>
+      <c r="M2313">
+        <v>2</v>
+      </c>
+      <c r="N2313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:14" ht="15" customHeight="1">
+      <c r="A2314" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2314" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C2314" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D2314">
+        <v>309</v>
+      </c>
+      <c r="E2314">
+        <v>58</v>
+      </c>
+      <c r="F2314">
+        <v>70.73</v>
+      </c>
+      <c r="G2314">
+        <v>55.17</v>
+      </c>
+      <c r="H2314">
+        <v>60</v>
+      </c>
+      <c r="I2314">
+        <v>70.91</v>
+      </c>
+      <c r="J2314" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2314" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2314">
+        <v>4</v>
+      </c>
+      <c r="M2314">
+        <v>3</v>
+      </c>
+      <c r="N2314">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:14" ht="15" customHeight="1">
+      <c r="A2315" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2315" t="s">
+        <v>923</v>
+      </c>
+      <c r="C2315" t="s">
+        <v>924</v>
+      </c>
+      <c r="D2315">
+        <v>239</v>
+      </c>
+      <c r="E2315">
+        <v>42</v>
+      </c>
+      <c r="F2315">
+        <v>51.22</v>
+      </c>
+      <c r="G2315">
+        <v>37.93</v>
+      </c>
+      <c r="H2315">
+        <v>62</v>
+      </c>
+      <c r="I2315">
+        <v>40</v>
+      </c>
+      <c r="J2315" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2315" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2315">
+        <v>3</v>
+      </c>
+      <c r="M2315">
+        <v>2</v>
+      </c>
+      <c r="N2315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:14" ht="15" customHeight="1">
+      <c r="A2316" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2316" t="s">
+        <v>902</v>
+      </c>
+      <c r="C2316" t="s">
+        <v>903</v>
+      </c>
+      <c r="D2316">
+        <v>297</v>
+      </c>
+      <c r="E2316">
+        <v>42</v>
+      </c>
+      <c r="F2316">
+        <v>60.98</v>
+      </c>
+      <c r="G2316">
+        <v>50</v>
+      </c>
+      <c r="H2316">
+        <v>74</v>
+      </c>
+      <c r="I2316">
+        <v>90.91</v>
+      </c>
+      <c r="J2316" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2316" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2316">
+        <v>3</v>
+      </c>
+      <c r="M2316">
+        <v>2</v>
+      </c>
+      <c r="N2316">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:14" ht="15" customHeight="1">
+      <c r="A2317" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2317" t="s">
+        <v>909</v>
+      </c>
+      <c r="C2317" t="s">
+        <v>910</v>
+      </c>
+      <c r="D2317">
+        <v>185</v>
+      </c>
+      <c r="E2317">
+        <v>34</v>
+      </c>
+      <c r="F2317">
+        <v>31.71</v>
+      </c>
+      <c r="G2317">
+        <v>31.03</v>
+      </c>
+      <c r="H2317">
+        <v>50</v>
+      </c>
+      <c r="I2317">
+        <v>38.18</v>
+      </c>
+      <c r="J2317" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2317" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2317">
+        <v>1</v>
+      </c>
+      <c r="M2317">
+        <v>1</v>
+      </c>
+      <c r="N2317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:14" ht="15" customHeight="1">
+      <c r="A2318" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2318" t="s">
+        <v>922</v>
+      </c>
+      <c r="C2318" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D2318">
+        <v>171</v>
+      </c>
+      <c r="E2318">
+        <v>28</v>
+      </c>
+      <c r="F2318">
+        <v>29.27</v>
+      </c>
+      <c r="G2318">
+        <v>31.03</v>
+      </c>
+      <c r="H2318">
+        <v>48</v>
+      </c>
+      <c r="I2318">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="J2318" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2318" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2318">
+        <v>1</v>
+      </c>
+      <c r="M2318">
+        <v>1</v>
+      </c>
+      <c r="N2318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:14" ht="15" customHeight="1">
+      <c r="A2319" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2319" t="s">
+        <v>900</v>
+      </c>
+      <c r="C2319" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D2319">
+        <v>201</v>
+      </c>
+      <c r="E2319">
+        <v>32</v>
+      </c>
+      <c r="F2319">
+        <v>41.46</v>
+      </c>
+      <c r="G2319">
+        <v>31.03</v>
+      </c>
+      <c r="H2319">
+        <v>52</v>
+      </c>
+      <c r="I2319">
+        <v>52.73</v>
+      </c>
+      <c r="J2319" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2319" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2319">
+        <v>2</v>
+      </c>
+      <c r="M2319">
+        <v>1</v>
+      </c>
+      <c r="N2319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:14" ht="15" customHeight="1">
+      <c r="A2320" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2320" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C2320" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D2320">
+        <v>206</v>
+      </c>
+      <c r="E2320">
+        <v>36</v>
+      </c>
+      <c r="F2320">
+        <v>41.46</v>
+      </c>
+      <c r="G2320">
+        <v>37.93</v>
+      </c>
+      <c r="H2320">
+        <v>46</v>
+      </c>
+      <c r="I2320">
+        <v>49.09</v>
+      </c>
+      <c r="J2320" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2320" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2320">
+        <v>2</v>
+      </c>
+      <c r="M2320">
+        <v>2</v>
+      </c>
+      <c r="N2320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:14" ht="15" customHeight="1">
+      <c r="A2321" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2321" t="s">
+        <v>919</v>
+      </c>
+      <c r="C2321" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D2321">
+        <v>296</v>
+      </c>
+      <c r="E2321">
+        <v>52</v>
+      </c>
+      <c r="F2321">
+        <v>63.41</v>
+      </c>
+      <c r="G2321">
+        <v>43.1</v>
+      </c>
+      <c r="H2321">
+        <v>74</v>
+      </c>
+      <c r="I2321">
+        <v>70.91</v>
+      </c>
+      <c r="J2321" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2321" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2321">
+        <v>3</v>
+      </c>
+      <c r="M2321">
+        <v>3</v>
+      </c>
+      <c r="N2321">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:14" ht="15" customHeight="1">
+      <c r="A2322" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2322" t="s">
+        <v>534</v>
+      </c>
+      <c r="C2322" t="s">
+        <v>535</v>
+      </c>
+      <c r="D2322">
+        <v>287</v>
+      </c>
+      <c r="E2322">
+        <v>54</v>
+      </c>
+      <c r="F2322">
+        <v>58.54</v>
+      </c>
+      <c r="G2322">
+        <v>46.55</v>
+      </c>
+      <c r="H2322">
+        <v>70</v>
+      </c>
+      <c r="I2322">
+        <v>58.18</v>
+      </c>
+      <c r="J2322" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2322" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2322">
+        <v>3</v>
+      </c>
+      <c r="M2322">
+        <v>3</v>
+      </c>
+      <c r="N2322">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:14" ht="15" customHeight="1">
+      <c r="A2323" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2323" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C2323" t="s">
+        <v>890</v>
+      </c>
+      <c r="D2323">
+        <v>296</v>
+      </c>
+      <c r="E2323">
+        <v>48</v>
+      </c>
+      <c r="F2323">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2323">
+        <v>48.28</v>
+      </c>
+      <c r="H2323">
+        <v>74</v>
+      </c>
+      <c r="I2323">
+        <v>60</v>
+      </c>
+      <c r="J2323" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2323" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2323">
+        <v>3</v>
+      </c>
+      <c r="M2323">
+        <v>2</v>
+      </c>
+      <c r="N2323">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:14" ht="15" customHeight="1">
+      <c r="A2324" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2324" t="s">
+        <v>773</v>
+      </c>
+      <c r="C2324" t="s">
+        <v>774</v>
+      </c>
+      <c r="D2324">
+        <v>366</v>
+      </c>
+      <c r="E2324">
+        <v>64</v>
+      </c>
+      <c r="F2324">
+        <v>78.05</v>
+      </c>
+      <c r="G2324">
+        <v>70.69</v>
+      </c>
+      <c r="H2324">
+        <v>80</v>
+      </c>
+      <c r="I2324">
+        <v>72.73</v>
+      </c>
+      <c r="J2324" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2324" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2324">
+        <v>4</v>
+      </c>
+      <c r="M2324">
+        <v>3</v>
+      </c>
+      <c r="N2324">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:14" ht="15" customHeight="1">
+      <c r="A2325" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2325" t="s">
+        <v>904</v>
+      </c>
+      <c r="C2325" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D2325">
+        <v>199</v>
+      </c>
+      <c r="E2325">
+        <v>30</v>
+      </c>
+      <c r="F2325">
+        <v>48.78</v>
+      </c>
+      <c r="G2325">
+        <v>27.59</v>
+      </c>
+      <c r="H2325">
+        <v>52</v>
+      </c>
+      <c r="I2325">
+        <v>40</v>
+      </c>
+      <c r="J2325" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2325" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2325">
+        <v>2</v>
+      </c>
+      <c r="M2325">
+        <v>1</v>
+      </c>
+      <c r="N2325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:14" ht="15" customHeight="1">
+      <c r="A2326" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2326" t="s">
+        <v>913</v>
+      </c>
+      <c r="C2326" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D2326">
+        <v>227</v>
+      </c>
+      <c r="E2326">
+        <v>30</v>
+      </c>
+      <c r="F2326">
+        <v>56.1</v>
+      </c>
+      <c r="G2326">
+        <v>24.14</v>
+      </c>
+      <c r="H2326">
+        <v>60</v>
+      </c>
+      <c r="I2326">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J2326" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2326" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2326">
+        <v>3</v>
+      </c>
+      <c r="M2326">
+        <v>1</v>
+      </c>
+      <c r="N2326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:14" ht="15" customHeight="1">
+      <c r="A2327" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2327" t="s">
+        <v>914</v>
+      </c>
+      <c r="C2327" t="s">
+        <v>915</v>
+      </c>
+      <c r="D2327">
+        <v>241</v>
+      </c>
+      <c r="E2327">
+        <v>30</v>
+      </c>
+      <c r="F2327">
+        <v>70.73</v>
+      </c>
+      <c r="G2327">
+        <v>37.93</v>
+      </c>
+      <c r="H2327">
+        <v>54</v>
+      </c>
+      <c r="I2327">
+        <v>47.27</v>
+      </c>
+      <c r="J2327" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2327" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2327">
+        <v>4</v>
+      </c>
+      <c r="M2327">
+        <v>1</v>
+      </c>
+      <c r="N2327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:14" ht="15" customHeight="1">
+      <c r="A2328" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2328" t="s">
+        <v>894</v>
+      </c>
+      <c r="C2328" t="s">
+        <v>895</v>
+      </c>
+      <c r="D2328">
+        <v>233</v>
+      </c>
+      <c r="E2328">
+        <v>26</v>
+      </c>
+      <c r="F2328">
+        <v>51.22</v>
+      </c>
+      <c r="G2328">
+        <v>43.1</v>
+      </c>
+      <c r="H2328">
+        <v>60</v>
+      </c>
+      <c r="I2328">
+        <v>63.64</v>
+      </c>
+      <c r="J2328" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2328" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2328">
+        <v>3</v>
+      </c>
+      <c r="M2328">
+        <v>1</v>
+      </c>
+      <c r="N2328">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:14" ht="15" customHeight="1">
+      <c r="A2329" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2329" t="s">
+        <v>916</v>
+      </c>
+      <c r="C2329" t="s">
+        <v>917</v>
+      </c>
+      <c r="D2329">
+        <v>309</v>
+      </c>
+      <c r="E2329">
+        <v>40</v>
+      </c>
+      <c r="F2329">
+        <v>78.05</v>
+      </c>
+      <c r="G2329">
+        <v>51.72</v>
+      </c>
+      <c r="H2329">
+        <v>70</v>
+      </c>
+      <c r="I2329">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="J2329" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2329" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2329">
+        <v>4</v>
+      </c>
+      <c r="M2329">
+        <v>2</v>
+      </c>
+      <c r="N2329">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:14" ht="15" customHeight="1">
+      <c r="A2330" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2330" t="s">
+        <v>793</v>
+      </c>
+      <c r="C2330" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D2330">
+        <v>208</v>
+      </c>
+      <c r="E2330">
+        <v>36</v>
+      </c>
+      <c r="F2330">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="G2330">
+        <v>48.28</v>
+      </c>
+      <c r="H2330">
+        <v>46</v>
+      </c>
+      <c r="I2330">
+        <v>40</v>
+      </c>
+      <c r="J2330" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2330" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2330">
+        <v>2</v>
+      </c>
+      <c r="M2330">
+        <v>2</v>
+      </c>
+      <c r="N2330">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:14" ht="15" customHeight="1">
+      <c r="A2331" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2331" t="s">
+        <v>905</v>
+      </c>
+      <c r="C2331" t="s">
+        <v>906</v>
+      </c>
+      <c r="D2331">
+        <v>298</v>
+      </c>
+      <c r="E2331">
+        <v>44</v>
+      </c>
+      <c r="F2331">
+        <v>60.98</v>
+      </c>
+      <c r="G2331">
+        <v>46.55</v>
+      </c>
+      <c r="H2331">
+        <v>78</v>
+      </c>
+      <c r="I2331">
+        <v>85.45</v>
+      </c>
+      <c r="J2331" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2331" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2331">
+        <v>3</v>
+      </c>
+      <c r="M2331">
+        <v>2</v>
+      </c>
+      <c r="N2331">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:14" ht="15" customHeight="1">
+      <c r="A2332" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2332" t="s">
+        <v>893</v>
+      </c>
+      <c r="C2332" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D2332">
+        <v>371</v>
+      </c>
+      <c r="E2332">
+        <v>66</v>
+      </c>
+      <c r="F2332">
+        <v>73.17</v>
+      </c>
+      <c r="G2332">
+        <v>72.41</v>
+      </c>
+      <c r="H2332">
+        <v>80</v>
+      </c>
+      <c r="I2332">
+        <v>89.09</v>
+      </c>
+      <c r="J2332" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2332" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2332">
+        <v>4</v>
+      </c>
+      <c r="M2332">
+        <v>3</v>
+      </c>
+      <c r="N2332">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:14" ht="15" customHeight="1">
+      <c r="A2333" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2333" t="s">
+        <v>907</v>
+      </c>
+      <c r="C2333" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D2333">
+        <v>306</v>
+      </c>
+      <c r="E2333">
+        <v>52</v>
+      </c>
+      <c r="F2333">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="G2333">
+        <v>55.17</v>
+      </c>
+      <c r="H2333">
+        <v>64</v>
+      </c>
+      <c r="I2333">
+        <v>83.64</v>
+      </c>
+      <c r="J2333" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2333" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2333">
+        <v>3</v>
+      </c>
+      <c r="M2333">
+        <v>3</v>
+      </c>
+      <c r="N2333">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:14" ht="15" customHeight="1">
+      <c r="A2334" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2334" t="s">
+        <v>891</v>
+      </c>
+      <c r="C2334" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2334">
+        <v>297</v>
+      </c>
+      <c r="E2334">
+        <v>52</v>
+      </c>
+      <c r="F2334">
+        <v>51.22</v>
+      </c>
+      <c r="G2334">
+        <v>50</v>
+      </c>
+      <c r="H2334">
+        <v>76</v>
+      </c>
+      <c r="I2334">
+        <v>83.64</v>
+      </c>
+      <c r="J2334" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K2334" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2334">
+        <v>3</v>
+      </c>
+      <c r="M2334">
+        <v>3</v>
+      </c>
+      <c r="N2334">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1825" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
